--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infosys_Monthly" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zensar_Monthly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coforge_Monthly" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY50_Monthly" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk_Free_Rate_Monthly" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk_Free_Rate_Annual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Infosys_Monthly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Zensar_Monthly" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coforge_Monthly" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NIFTY50_Monthly" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Risk_Free_Rate_Monthly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Risk_Free_Rate_Annual" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>80.88382720947266</v>
+        <v>80.88383483886719</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -456,10 +456,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>87.58747100830078</v>
+        <v>87.58748626708984</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08287990356177199</v>
+        <v>0.08287999006942903</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +467,10 @@
         <v>38412</v>
       </c>
       <c r="B4" t="n">
-        <v>88.256103515625</v>
+        <v>88.25608825683594</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007633883015766729</v>
+        <v>0.007633533261900638</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>73.77352905273438</v>
+        <v>73.77353668212891</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1640971432681322</v>
+        <v>-0.1640969123009514</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         <v>87.99215698242188</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1927334656787778</v>
+        <v>0.1927333423305613</v>
       </c>
     </row>
     <row r="7">
@@ -522,10 +522,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>93.17420196533203</v>
+        <v>93.1741943359375</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0474556986257757</v>
+        <v>0.04745561285683308</v>
       </c>
     </row>
     <row r="10">
@@ -533,10 +533,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>98.63265228271484</v>
+        <v>98.63261413574219</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05858327951565157</v>
+        <v>0.05858295678011949</v>
       </c>
     </row>
     <row r="11">
@@ -544,10 +544,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>99.14112854003906</v>
+        <v>99.14113616943359</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005155252804788679</v>
+        <v>0.005155718908469442</v>
       </c>
     </row>
     <row r="12">
@@ -555,10 +555,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>105.529167175293</v>
+        <v>105.5292053222656</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0644337897835614</v>
+        <v>0.06443409264459832</v>
       </c>
     </row>
     <row r="13">
@@ -566,10 +566,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>117.81005859375</v>
+        <v>117.8100433349609</v>
       </c>
       <c r="C13" t="n">
-        <v>0.116374380156506</v>
+        <v>0.1163738320135361</v>
       </c>
     </row>
     <row r="14">
@@ -577,10 +577,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>113.2283020019531</v>
+        <v>113.228271484375</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.03889104755983841</v>
+        <v>-0.03889118211729126</v>
       </c>
     </row>
     <row r="15">
@@ -588,10 +588,10 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>111.2096862792969</v>
+        <v>111.2096939086914</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.01782783709519398</v>
+        <v>-0.01782750499694896</v>
       </c>
     </row>
     <row r="16">
@@ -599,10 +599,10 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>117.2026672363281</v>
+        <v>117.2026901245117</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05388901954079994</v>
+        <v>0.05388915305117958</v>
       </c>
     </row>
     <row r="17">
@@ -613,7 +613,7 @@
         <v>249.8114318847656</v>
       </c>
       <c r="C17" t="n">
-        <v>1.131448351606576</v>
+        <v>1.131447935362024</v>
       </c>
     </row>
     <row r="18">
@@ -621,10 +621,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>115.9502868652344</v>
+        <v>115.9503173828125</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5358487560380321</v>
+        <v>-0.5358486338755759</v>
       </c>
     </row>
     <row r="19">
@@ -632,10 +632,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>122.6885070800781</v>
+        <v>122.6885375976562</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05811301029962435</v>
+        <v>0.05811299500455336</v>
       </c>
     </row>
     <row r="20">
@@ -643,10 +643,10 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>131.9391632080078</v>
+        <v>131.9391326904297</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07539953291543311</v>
+        <v>0.07539901668002402</v>
       </c>
     </row>
     <row r="21">
@@ -654,10 +654,10 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>143.9611053466797</v>
+        <v>143.9611511230469</v>
       </c>
       <c r="C21" t="n">
-        <v>0.09111731381620758</v>
+        <v>0.09111791314275641</v>
       </c>
     </row>
     <row r="22">
@@ -668,7 +668,7 @@
         <v>147.4079132080078</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0239426326508656</v>
+        <v>0.02394230706042988</v>
       </c>
     </row>
     <row r="23">
@@ -676,10 +676,10 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>167.4046783447266</v>
+        <v>167.4046630859375</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1356559814295808</v>
+        <v>0.1356558779155377</v>
       </c>
     </row>
     <row r="24">
@@ -687,10 +687,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>174.1311798095703</v>
+        <v>174.1312255859375</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04018108413309851</v>
+        <v>0.04018145239208115</v>
       </c>
     </row>
     <row r="25">
@@ -698,10 +698,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>179.0922241210938</v>
+        <v>179.0922393798828</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02849026990426884</v>
+        <v>0.02849008715841683</v>
       </c>
     </row>
     <row r="26">
@@ -709,10 +709,10 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>179.5316467285156</v>
+        <v>179.5315704345703</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002453610756013358</v>
+        <v>0.00245309934259974</v>
       </c>
     </row>
     <row r="27">
@@ -720,10 +720,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>165.9706878662109</v>
+        <v>165.9706573486328</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07553520011327763</v>
+        <v>-0.07553497723610525</v>
       </c>
     </row>
     <row r="28">
@@ -731,10 +731,10 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>161.2653045654297</v>
+        <v>161.2652740478516</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.028350688674462</v>
+        <v>-0.02835069388739764</v>
       </c>
     </row>
     <row r="29">
@@ -745,7 +745,7 @@
         <v>163.8377227783203</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01595146717902307</v>
+        <v>0.01595165943602606</v>
       </c>
     </row>
     <row r="30">
@@ -753,10 +753,10 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>153.6640014648438</v>
+        <v>153.6640319824219</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06209633008169957</v>
+        <v>-0.06209614381459572</v>
       </c>
     </row>
     <row r="31">
@@ -764,10 +764,10 @@
         <v>39234</v>
       </c>
       <c r="B31" t="n">
-        <v>154.6246032714844</v>
+        <v>154.6245574951172</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006251313238516687</v>
+        <v>0.006250815498614504</v>
       </c>
     </row>
     <row r="32">
@@ -775,10 +775,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>158.3718566894531</v>
+        <v>158.3718414306641</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02423452244135715</v>
+        <v>0.024234726981613</v>
       </c>
     </row>
     <row r="33">
@@ -786,10 +786,10 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>148.6529693603516</v>
+        <v>148.6529998779297</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.06136751524078587</v>
+        <v>-0.06136723210981498</v>
       </c>
     </row>
     <row r="34">
@@ -797,10 +797,10 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>151.7149200439453</v>
+        <v>151.7148895263672</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02059797861266555</v>
+        <v>0.0205975637958995</v>
       </c>
     </row>
     <row r="35">
@@ -808,10 +808,10 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>147.7512664794922</v>
+        <v>147.7512817382812</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02612566755665835</v>
+        <v>-0.02612537108559199</v>
       </c>
     </row>
     <row r="36">
@@ -819,10 +819,10 @@
         <v>39387</v>
       </c>
       <c r="B36" t="n">
-        <v>128.8587493896484</v>
+        <v>128.8586730957031</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1278670399246021</v>
+        <v>-0.1278676463602089</v>
       </c>
     </row>
     <row r="37">
@@ -830,10 +830,10 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>142.3195037841797</v>
+        <v>142.3195495605469</v>
       </c>
       <c r="C37" t="n">
-        <v>0.10446131487609</v>
+        <v>0.1044623240443145</v>
       </c>
     </row>
     <row r="38">
@@ -841,10 +841,10 @@
         <v>39448</v>
       </c>
       <c r="B38" t="n">
-        <v>120.5401992797852</v>
+        <v>120.5401916503906</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1530310598709067</v>
+        <v>-0.1530313859017006</v>
       </c>
     </row>
     <row r="39">
@@ -852,10 +852,10 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>124.4924240112305</v>
+        <v>124.4923629760742</v>
       </c>
       <c r="C39" t="n">
-        <v>0.03278760741279196</v>
+        <v>0.03278716643446433</v>
       </c>
     </row>
     <row r="40">
@@ -863,10 +863,10 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>115.7838973999023</v>
+        <v>115.7838592529297</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.06995226159740076</v>
+        <v>-0.06995211204094653</v>
       </c>
     </row>
     <row r="41">
@@ -874,10 +874,10 @@
         <v>39539</v>
       </c>
       <c r="B41" t="n">
-        <v>140.9686431884766</v>
+        <v>140.9685821533203</v>
       </c>
       <c r="C41" t="n">
-        <v>0.217515097989744</v>
+        <v>0.2175149719735514</v>
       </c>
     </row>
     <row r="42">
@@ -885,10 +885,10 @@
         <v>39569</v>
       </c>
       <c r="B42" t="n">
-        <v>160.11328125</v>
+        <v>160.1132354736328</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1358077770240496</v>
+        <v>0.1358079440672133</v>
       </c>
     </row>
     <row r="43">
@@ -896,10 +896,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>141.6775512695312</v>
+        <v>141.6775817871094</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1151417910902925</v>
+        <v>-0.1151413475093969</v>
       </c>
     </row>
     <row r="44">
@@ -907,10 +907,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>129.1681823730469</v>
+        <v>129.1681671142578</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.08829464360720218</v>
+        <v>-0.08829494769079793</v>
       </c>
     </row>
     <row r="45">
@@ -918,10 +918,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>142.680908203125</v>
+        <v>142.6809234619141</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1046134240013723</v>
+        <v>0.1046136726218567</v>
       </c>
     </row>
     <row r="46">
@@ -929,10 +929,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>114.0443878173828</v>
+        <v>114.0443801879883</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2007032387610986</v>
+        <v>-0.2007033777123665</v>
       </c>
     </row>
     <row r="47">
@@ -940,10 +940,10 @@
         <v>39722</v>
       </c>
       <c r="B47" t="n">
-        <v>114.1569061279297</v>
+        <v>114.1569137573242</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0009866185675619921</v>
+        <v>0.0009867524305049447</v>
       </c>
     </row>
     <row r="48">
@@ -951,10 +951,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>102.2312316894531</v>
+        <v>102.2312164306641</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1044673935461432</v>
+        <v>-0.104467587061892</v>
       </c>
     </row>
     <row r="49">
@@ -962,10 +962,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>91.67813110351562</v>
+        <v>91.67812347412109</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1032277554670823</v>
+        <v>-0.1032276962457974</v>
       </c>
     </row>
     <row r="50">
@@ -973,10 +973,10 @@
         <v>39814</v>
       </c>
       <c r="B50" t="n">
-        <v>107.392707824707</v>
+        <v>107.3927154541016</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1714103083476666</v>
+        <v>0.1714104890510373</v>
       </c>
     </row>
     <row r="51">
@@ -984,10 +984,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>101.1956481933594</v>
+        <v>101.195686340332</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05770465943984648</v>
+        <v>-0.05770437117234517</v>
       </c>
     </row>
     <row r="52">
@@ -995,10 +995,10 @@
         <v>39873</v>
       </c>
       <c r="B52" t="n">
-        <v>108.8105087280273</v>
+        <v>108.8105163574219</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0752488933132569</v>
+        <v>0.0752485633772999</v>
       </c>
     </row>
     <row r="53">
@@ -1006,10 +1006,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>124.0442428588867</v>
+        <v>124.044303894043</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1400024162090465</v>
+        <v>0.1400028972069298</v>
       </c>
     </row>
     <row r="54">
@@ -1020,7 +1020,7 @@
         <v>131.9221343994141</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06350872365345706</v>
+        <v>0.06350820036122129</v>
       </c>
     </row>
     <row r="55">
@@ -1028,10 +1028,10 @@
         <v>39965</v>
       </c>
       <c r="B55" t="n">
-        <v>147.2201232910156</v>
+        <v>147.2201538085938</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1159622603230828</v>
+        <v>0.115962491653316</v>
       </c>
     </row>
     <row r="56">
@@ -1039,10 +1039,10 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>171.0745697021484</v>
+        <v>171.0745544433594</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1620325121177817</v>
+        <v>0.162032167591535</v>
       </c>
     </row>
     <row r="57">
@@ -1050,10 +1050,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>176.6103057861328</v>
+        <v>176.6103210449219</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03235861468845092</v>
+        <v>0.03235879596223246</v>
       </c>
     </row>
     <row r="58">
@@ -1061,10 +1061,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>191.1334838867188</v>
+        <v>191.1334686279297</v>
       </c>
       <c r="C58" t="n">
-        <v>0.08223290275128603</v>
+        <v>0.08223272285040339</v>
       </c>
     </row>
     <row r="59">
@@ -1072,10 +1072,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>183.6438903808594</v>
+        <v>183.6438446044922</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.03918514617929691</v>
+        <v>-0.03918530897389405</v>
       </c>
     </row>
     <row r="60">
@@ -1083,10 +1083,10 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>198.0568695068359</v>
+        <v>198.056884765625</v>
       </c>
       <c r="C60" t="n">
-        <v>0.07848330318033159</v>
+        <v>0.07848365509975963</v>
       </c>
     </row>
     <row r="61">
@@ -1094,10 +1094,10 @@
         <v>40148</v>
       </c>
       <c r="B61" t="n">
-        <v>216.5152893066406</v>
+        <v>216.5152740478516</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0931975742410065</v>
+        <v>0.0931974129759221</v>
       </c>
     </row>
     <row r="62">
@@ -1105,10 +1105,10 @@
         <v>40179</v>
       </c>
       <c r="B62" t="n">
-        <v>206.0604858398438</v>
+        <v>206.0603942871094</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.04828667527488195</v>
+        <v>-0.04828703104997378</v>
       </c>
     </row>
     <row r="63">
@@ -1119,7 +1119,7 @@
         <v>216.5860443115234</v>
       </c>
       <c r="C63" t="n">
-        <v>0.05107994591384424</v>
+        <v>0.05108041290918042</v>
       </c>
     </row>
     <row r="64">
@@ -1127,10 +1127,10 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>217.7514190673828</v>
+        <v>217.7514038085938</v>
       </c>
       <c r="C64" t="n">
-        <v>0.005380654878128555</v>
+        <v>0.00538058442673317</v>
       </c>
     </row>
     <row r="65">
@@ -1138,10 +1138,10 @@
         <v>40269</v>
       </c>
       <c r="B65" t="n">
-        <v>227.92333984375</v>
+        <v>227.9233245849609</v>
       </c>
       <c r="C65" t="n">
-        <v>0.04671345344123568</v>
+        <v>0.04671345671465077</v>
       </c>
     </row>
     <row r="66">
@@ -1149,10 +1149,10 @@
         <v>40299</v>
       </c>
       <c r="B66" t="n">
-        <v>222.5694580078125</v>
+        <v>222.5694427490234</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.02348983583518827</v>
+        <v>-0.02348983740776289</v>
       </c>
     </row>
     <row r="67">
@@ -1160,10 +1160,10 @@
         <v>40330</v>
       </c>
       <c r="B67" t="n">
-        <v>233.706298828125</v>
+        <v>233.7063751220703</v>
       </c>
       <c r="C67" t="n">
-        <v>0.05003759689220955</v>
+        <v>0.05003801166724053</v>
       </c>
     </row>
     <row r="68">
@@ -1174,7 +1174,7 @@
         <v>233.4886322021484</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0009313682475312612</v>
+        <v>-0.0009316943956199086</v>
       </c>
     </row>
     <row r="69">
@@ -1182,10 +1182,10 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>227.2461547851562</v>
+        <v>227.2460784912109</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.02673568026895468</v>
+        <v>-0.0267360070255277</v>
       </c>
     </row>
     <row r="70">
@@ -1193,10 +1193,10 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>255.4357452392578</v>
+        <v>255.4357757568359</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1240487016414102</v>
+        <v>0.1240492133144346</v>
       </c>
     </row>
     <row r="71">
@@ -1204,10 +1204,10 @@
         <v>40452</v>
       </c>
       <c r="B71" t="n">
-        <v>252.1789703369141</v>
+        <v>252.1790008544922</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.01274987922811366</v>
+        <v>-0.01274987770485236</v>
       </c>
     </row>
     <row r="72">
@@ -1215,10 +1215,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>258.9083862304688</v>
+        <v>258.9084777832031</v>
       </c>
       <c r="C72" t="n">
-        <v>0.02668507958678745</v>
+        <v>0.02668531838855959</v>
       </c>
     </row>
     <row r="73">
@@ -1229,7 +1229,7 @@
         <v>292.1523742675781</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1284005841646128</v>
+        <v>0.1284001851504135</v>
       </c>
     </row>
     <row r="74">
@@ -1237,10 +1237,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>264.5686340332031</v>
+        <v>264.5686645507812</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.09441559495632046</v>
+        <v>-0.09441549049857578</v>
       </c>
     </row>
     <row r="75">
@@ -1248,10 +1248,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>254.3343963623047</v>
+        <v>254.33447265625</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.03868273239681941</v>
+        <v>-0.0386825549121933</v>
       </c>
     </row>
     <row r="76">
@@ -1259,10 +1259,10 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>275.0572814941406</v>
+        <v>275.0573425292969</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08147889325325752</v>
+        <v>0.08147880881666891</v>
       </c>
     </row>
     <row r="77">
@@ -1270,10 +1270,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>246.6249389648438</v>
+        <v>246.6249847412109</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1033688051261517</v>
+        <v>-0.1033688376635775</v>
       </c>
     </row>
     <row r="78">
@@ -1281,10 +1281,10 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>238.098388671875</v>
+        <v>238.0983734130859</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.03457294436141434</v>
+        <v>-0.0345731854259298</v>
       </c>
     </row>
     <row r="79">
@@ -1292,10 +1292,10 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>248.7654724121094</v>
+        <v>248.7655029296875</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04480115888114966</v>
+        <v>0.04480135401049035</v>
       </c>
     </row>
     <row r="80">
@@ -1303,10 +1303,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>237.2650299072266</v>
+        <v>237.2650146484375</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.04623005915318901</v>
+        <v>-0.04623023749599464</v>
       </c>
     </row>
     <row r="81">
@@ -1314,10 +1314,10 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>200.2593688964844</v>
+        <v>200.2594299316406</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1559676157300207</v>
+        <v>-0.1559673042046639</v>
       </c>
     </row>
     <row r="82">
@@ -1325,10 +1325,10 @@
         <v>40787</v>
       </c>
       <c r="B82" t="n">
-        <v>216.5079345703125</v>
+        <v>216.5078582763672</v>
       </c>
       <c r="C82" t="n">
-        <v>0.08113760551311411</v>
+        <v>0.08113689502797961</v>
       </c>
     </row>
     <row r="83">
@@ -1336,10 +1336,10 @@
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>247.3133697509766</v>
+        <v>247.3135223388672</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1422831696297937</v>
+        <v>0.1422842769206893</v>
       </c>
     </row>
     <row r="84">
@@ -1347,10 +1347,10 @@
         <v>40848</v>
       </c>
       <c r="B84" t="n">
-        <v>224.0478515625</v>
+        <v>224.0478363037109</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.09407303055189842</v>
+        <v>-0.09407365119032096</v>
       </c>
     </row>
     <row r="85">
@@ -1358,10 +1358,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>237.8678894042969</v>
+        <v>237.867919921875</v>
       </c>
       <c r="C85" t="n">
-        <v>0.06168342050779119</v>
+        <v>0.06168362902389313</v>
       </c>
     </row>
     <row r="86">
@@ -1369,10 +1369,10 @@
         <v>40909</v>
       </c>
       <c r="B86" t="n">
-        <v>236.0072174072266</v>
+        <v>236.0071868896484</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.007822291616283672</v>
+        <v>-0.00782254720534703</v>
       </c>
     </row>
     <row r="87">
@@ -1380,10 +1380,10 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>247.8204498291016</v>
+        <v>247.8204956054688</v>
       </c>
       <c r="C87" t="n">
-        <v>0.05005453880459698</v>
+        <v>0.05005486854662577</v>
       </c>
     </row>
     <row r="88">
@@ -1391,10 +1391,10 @@
         <v>40969</v>
       </c>
       <c r="B88" t="n">
-        <v>246.3465270996094</v>
+        <v>246.3465118408203</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.005947542789582538</v>
+        <v>-0.005947787978743402</v>
       </c>
     </row>
     <row r="89">
@@ -1402,10 +1402,10 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>211.6072845458984</v>
+        <v>211.6072387695312</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1410177888956569</v>
+        <v>-0.1410179215110472</v>
       </c>
     </row>
     <row r="90">
@@ -1413,10 +1413,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>211.6771087646484</v>
+        <v>211.6771697998047</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0003299707706181376</v>
+        <v>0.000330475605088365</v>
       </c>
     </row>
     <row r="91">
@@ -1424,10 +1424,10 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>218.6346435546875</v>
+        <v>218.6347198486328</v>
       </c>
       <c r="C91" t="n">
-        <v>0.03286862160317372</v>
+        <v>0.03286868421100064</v>
       </c>
     </row>
     <row r="92">
@@ -1438,7 +1438,7 @@
         <v>194.0413208007812</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.1124859370594427</v>
+        <v>-0.1124862467629949</v>
       </c>
     </row>
     <row r="93">
@@ -1446,10 +1446,10 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>205.7781372070312</v>
+        <v>205.7782135009766</v>
       </c>
       <c r="C93" t="n">
-        <v>0.06048617046005367</v>
+        <v>0.06048656364406724</v>
       </c>
     </row>
     <row r="94">
@@ -1457,10 +1457,10 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>220.8784027099609</v>
+        <v>220.8783721923828</v>
       </c>
       <c r="C94" t="n">
-        <v>0.07338129165654506</v>
+        <v>0.07338074538845474</v>
       </c>
     </row>
     <row r="95">
@@ -1468,10 +1468,10 @@
         <v>41183</v>
       </c>
       <c r="B95" t="n">
-        <v>207.2071685791016</v>
+        <v>207.2071533203125</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.06189484333065964</v>
+        <v>-0.06189478280002358</v>
       </c>
     </row>
     <row r="96">
@@ -1479,10 +1479,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>213.6829681396484</v>
+        <v>213.6829528808594</v>
       </c>
       <c r="C96" t="n">
-        <v>0.03125277761842837</v>
+        <v>0.03125277991989117</v>
       </c>
     </row>
     <row r="97">
@@ -1490,10 +1490,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>203.3226318359375</v>
+        <v>203.3225555419922</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.04848461435138873</v>
+        <v>-0.04848490344779033</v>
       </c>
     </row>
     <row r="98">
@@ -1501,10 +1501,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>244.6060943603516</v>
+        <v>244.6061706542969</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2030441085266199</v>
+        <v>0.2030449351881098</v>
       </c>
     </row>
     <row r="99">
@@ -1512,10 +1512,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>254.9095458984375</v>
+        <v>254.9094696044922</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04212262807690714</v>
+        <v>0.04212199112816739</v>
       </c>
     </row>
     <row r="100">
@@ -1523,10 +1523,10 @@
         <v>41334</v>
       </c>
       <c r="B100" t="n">
-        <v>253.3618469238281</v>
+        <v>253.3618621826172</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.006071561459789376</v>
+        <v>-0.006071204119157292</v>
       </c>
     </row>
     <row r="101">
@@ -1534,10 +1534,10 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>196.0225067138672</v>
+        <v>196.0225372314453</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.2263140283596042</v>
+        <v>-0.2263139545044986</v>
       </c>
     </row>
     <row r="102">
@@ -1545,10 +1545,10 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>213.9329681396484</v>
+        <v>213.9330139160156</v>
       </c>
       <c r="C102" t="n">
-        <v>0.09136941326806425</v>
+        <v>0.09136947688531993</v>
       </c>
     </row>
     <row r="103">
@@ -1556,10 +1556,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>221.6637573242188</v>
+        <v>221.6637878417969</v>
       </c>
       <c r="C103" t="n">
-        <v>0.03613650225019982</v>
+        <v>0.0361364231928043</v>
       </c>
     </row>
     <row r="104">
@@ -1567,10 +1567,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>263.4266967773438</v>
+        <v>263.4266357421875</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1884067109448118</v>
+        <v>0.1884062719806858</v>
       </c>
     </row>
     <row r="105">
@@ -1578,10 +1578,10 @@
         <v>41487</v>
       </c>
       <c r="B105" t="n">
-        <v>275.5085144042969</v>
+        <v>275.508544921875</v>
       </c>
       <c r="C105" t="n">
-        <v>0.045864059242124</v>
+        <v>0.04586441741415981</v>
       </c>
     </row>
     <row r="106">
@@ -1589,10 +1589,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>267.2721557617188</v>
+        <v>267.2720947265625</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.02989511471319406</v>
+        <v>-0.02989544370628539</v>
       </c>
     </row>
     <row r="107">
@@ -1600,10 +1600,10 @@
         <v>41548</v>
       </c>
       <c r="B107" t="n">
-        <v>295.369873046875</v>
+        <v>295.3699035644531</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1051277384472711</v>
+        <v>0.1051281049996506</v>
       </c>
     </row>
     <row r="108">
@@ -1611,10 +1611,10 @@
         <v>41579</v>
       </c>
       <c r="B108" t="n">
-        <v>299.3544006347656</v>
+        <v>299.3544311523438</v>
       </c>
       <c r="C108" t="n">
-        <v>0.01348995937462538</v>
+        <v>0.01348995798084474</v>
       </c>
     </row>
     <row r="109">
@@ -1622,10 +1622,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>311.0535583496094</v>
+        <v>311.0535278320312</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03908129524749349</v>
+        <v>0.03908108737409588</v>
       </c>
     </row>
     <row r="110">
@@ -1636,7 +1636,7 @@
         <v>330.2799682617188</v>
       </c>
       <c r="C110" t="n">
-        <v>0.06181060912506853</v>
+        <v>0.061810713299705</v>
       </c>
     </row>
     <row r="111">
@@ -1644,10 +1644,10 @@
         <v>41671</v>
       </c>
       <c r="B111" t="n">
-        <v>341.3232116699219</v>
+        <v>341.3231811523438</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03343600723448148</v>
+        <v>0.03343591483536223</v>
       </c>
     </row>
     <row r="112">
@@ -1658,7 +1658,7 @@
         <v>292.9515686035156</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.1417180004540221</v>
+        <v>-0.1417179237153491</v>
       </c>
     </row>
     <row r="113">
@@ -1666,10 +1666,10 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>283.8492736816406</v>
+        <v>283.8492126464844</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.03107098885070025</v>
+        <v>-0.03107119719625229</v>
       </c>
     </row>
     <row r="114">
@@ -1677,10 +1677,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>265.9103393554688</v>
+        <v>265.9103698730469</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.06319880298968739</v>
+        <v>-0.06319849403908384</v>
       </c>
     </row>
     <row r="115">
@@ -1688,10 +1688,10 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>294.5106506347656</v>
+        <v>294.5105590820312</v>
       </c>
       <c r="C115" t="n">
-        <v>0.107556221200801</v>
+        <v>0.107555749791326</v>
       </c>
     </row>
     <row r="116">
@@ -1699,10 +1699,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>304.6516418457031</v>
+        <v>304.651611328125</v>
       </c>
       <c r="C116" t="n">
-        <v>0.03443335984311724</v>
+        <v>0.03443357778988543</v>
       </c>
     </row>
     <row r="117">
@@ -1710,10 +1710,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>325.5623779296875</v>
+        <v>325.5624084472656</v>
       </c>
       <c r="C117" t="n">
-        <v>0.06863818608460037</v>
+        <v>0.06863839330433952</v>
       </c>
     </row>
     <row r="118">
@@ -1721,10 +1721,10 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>339.0371398925781</v>
+        <v>339.0369873046875</v>
       </c>
       <c r="C118" t="n">
-        <v>0.04138918645507861</v>
+        <v>0.04138862014717049</v>
       </c>
     </row>
     <row r="119">
@@ -1735,7 +1735,7 @@
         <v>369.3205871582031</v>
       </c>
       <c r="C119" t="n">
-        <v>0.08932191698885883</v>
+        <v>0.08932240725198581</v>
       </c>
     </row>
     <row r="120">
@@ -1776,10 +1776,10 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>413.1012573242188</v>
+        <v>413.1012878417969</v>
       </c>
       <c r="C123" t="n">
-        <v>0.05782251684279194</v>
+        <v>0.05782259498872033</v>
       </c>
     </row>
     <row r="124">
@@ -1787,10 +1787,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>404.4590148925781</v>
+        <v>404.4589538574219</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.02092039730796036</v>
+        <v>-0.02092061738545026</v>
       </c>
     </row>
     <row r="125">
@@ -1798,10 +1798,10 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>354.1193542480469</v>
+        <v>354.1192932128906</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.1244617100644948</v>
+        <v>-0.1244617288464747</v>
       </c>
     </row>
     <row r="126">
@@ -1809,10 +1809,10 @@
         <v>42125</v>
       </c>
       <c r="B126" t="n">
-        <v>368.8693237304688</v>
+        <v>368.8693542480469</v>
       </c>
       <c r="C126" t="n">
-        <v>0.04165253693558379</v>
+        <v>0.0416528026511358</v>
       </c>
     </row>
     <row r="127">
@@ -1820,10 +1820,10 @@
         <v>42156</v>
       </c>
       <c r="B127" t="n">
-        <v>364.3843383789062</v>
+        <v>364.3843688964844</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.01215873769660403</v>
+        <v>-0.01215873669067824</v>
       </c>
     </row>
     <row r="128">
@@ -1834,7 +1834,7 @@
         <v>398.6998291015625</v>
       </c>
       <c r="C128" t="n">
-        <v>0.09417389033601431</v>
+        <v>0.09417379869778819</v>
       </c>
     </row>
     <row r="129">
@@ -1842,10 +1842,10 @@
         <v>42217</v>
       </c>
       <c r="B129" t="n">
-        <v>405.1224060058594</v>
+        <v>405.1223449707031</v>
       </c>
       <c r="C129" t="n">
-        <v>0.01610880275210969</v>
+        <v>0.01610864966662584</v>
       </c>
     </row>
     <row r="130">
@@ -1853,10 +1853,10 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>430.1278686523438</v>
+        <v>430.1277770996094</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0617232280312896</v>
+        <v>0.0617231620011347</v>
       </c>
     </row>
     <row r="131">
@@ -1864,10 +1864,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>424.1836853027344</v>
+        <v>424.1837768554688</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.01381957269644818</v>
+        <v>-0.01381914993777322</v>
       </c>
     </row>
     <row r="132">
@@ -1875,10 +1875,10 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>406.4198913574219</v>
+        <v>406.4198608398438</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.04187759822171078</v>
+        <v>-0.0418778769601027</v>
       </c>
     </row>
     <row r="133">
@@ -1886,10 +1886,10 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>412.9576721191406</v>
+        <v>412.9575805664062</v>
       </c>
       <c r="C133" t="n">
-        <v>0.01608627161402687</v>
+        <v>0.01608612264433296</v>
       </c>
     </row>
     <row r="134">
@@ -1900,7 +1900,7 @@
         <v>435.1858215332031</v>
       </c>
       <c r="C134" t="n">
-        <v>0.05382670165684567</v>
+        <v>0.05382693529032445</v>
       </c>
     </row>
     <row r="135">
@@ -1908,10 +1908,10 @@
         <v>42401</v>
       </c>
       <c r="B135" t="n">
-        <v>404.9816589355469</v>
+        <v>404.9815979003906</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.06940520831134611</v>
+        <v>-0.06940534856213831</v>
       </c>
     </row>
     <row r="136">
@@ -1919,10 +1919,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>455.1349792480469</v>
+        <v>455.1349487304688</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1238409671300249</v>
+        <v>0.1238410611496819</v>
       </c>
     </row>
     <row r="137">
@@ -1933,7 +1933,7 @@
         <v>451.3244018554688</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.008372411628026932</v>
+        <v>-0.008372345137698023</v>
       </c>
     </row>
     <row r="138">
@@ -1941,10 +1941,10 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>466.47314453125</v>
+        <v>466.4731750488281</v>
       </c>
       <c r="C138" t="n">
-        <v>0.03356508669485248</v>
+        <v>0.03356515431268559</v>
       </c>
     </row>
     <row r="139">
@@ -1952,10 +1952,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>442.4826354980469</v>
+        <v>442.482666015625</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.05142956098214557</v>
+        <v>-0.0514295576175241</v>
       </c>
     </row>
     <row r="140">
@@ -1963,10 +1963,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>405.8421020507812</v>
+        <v>405.8421630859375</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.08280671490311475</v>
+        <v>-0.08280664022304018</v>
       </c>
     </row>
     <row r="141">
@@ -1974,10 +1974,10 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>391.480712890625</v>
+        <v>391.4807434082031</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.03538664196638541</v>
+        <v>-0.0353867118402218</v>
       </c>
     </row>
     <row r="142">
@@ -1985,10 +1985,10 @@
         <v>42614</v>
       </c>
       <c r="B142" t="n">
-        <v>391.5563049316406</v>
+        <v>391.5563659667969</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0001930926314541725</v>
+        <v>0.0001931705706272879</v>
       </c>
     </row>
     <row r="143">
@@ -1999,7 +1999,7 @@
         <v>381.0301818847656</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.02688278266573363</v>
+        <v>-0.02688293435362976</v>
       </c>
     </row>
     <row r="144">
@@ -2007,10 +2007,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>372.6455688476562</v>
+        <v>372.6455993652344</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.02200511517390802</v>
+        <v>-0.02200503508162244</v>
       </c>
     </row>
     <row r="145">
@@ -2018,10 +2018,10 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>386.0341491699219</v>
+        <v>386.0342102050781</v>
       </c>
       <c r="C145" t="n">
-        <v>0.03592845706891823</v>
+        <v>0.03592853602095381</v>
       </c>
     </row>
     <row r="146">
@@ -2032,7 +2032,7 @@
         <v>354.7113952636719</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.08113985245502875</v>
+        <v>-0.08113999773431013</v>
       </c>
     </row>
     <row r="147">
@@ -2040,10 +2040,10 @@
         <v>42767</v>
       </c>
       <c r="B147" t="n">
-        <v>386.7218017578125</v>
+        <v>386.7217407226562</v>
       </c>
       <c r="C147" t="n">
-        <v>0.09024352451475637</v>
+        <v>0.09024335244485093</v>
       </c>
     </row>
     <row r="148">
@@ -2054,7 +2054,7 @@
         <v>390.4843444824219</v>
       </c>
       <c r="C148" t="n">
-        <v>0.009729326630945057</v>
+        <v>0.009729485993558384</v>
       </c>
     </row>
     <row r="149">
@@ -2062,10 +2062,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>351.0253295898438</v>
+        <v>351.0252380371094</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.1010514645468825</v>
+        <v>-0.1010516990063063</v>
       </c>
     </row>
     <row r="150">
@@ -2073,10 +2073,10 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>373.2185668945312</v>
+        <v>373.2185974121094</v>
       </c>
       <c r="C150" t="n">
-        <v>0.06322403380582031</v>
+        <v>0.06322439804927593</v>
       </c>
     </row>
     <row r="151">
@@ -2084,10 +2084,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>362.8438720703125</v>
+        <v>362.8438415527344</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.02779790649362457</v>
+        <v>-0.02779806775791283</v>
       </c>
     </row>
     <row r="152">
@@ -2095,10 +2095,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>392.1839904785156</v>
+        <v>392.1840515136719</v>
       </c>
       <c r="C152" t="n">
-        <v>0.08086155139066964</v>
+        <v>0.08086181051159791</v>
       </c>
     </row>
     <row r="153">
@@ -2106,10 +2106,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>354.8544006347656</v>
+        <v>354.8543395996094</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.09518386968882397</v>
+        <v>-0.09518416613318392</v>
       </c>
     </row>
     <row r="154">
@@ -2117,10 +2117,10 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>349.0173645019531</v>
+        <v>349.0173950195312</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.01644910172276626</v>
+        <v>-0.01644884655113443</v>
       </c>
     </row>
     <row r="155">
@@ -2128,10 +2128,10 @@
         <v>43009</v>
       </c>
       <c r="B155" t="n">
-        <v>362.5223083496094</v>
+        <v>362.5222778320312</v>
       </c>
       <c r="C155" t="n">
-        <v>0.03869418894652354</v>
+        <v>0.03869401068604117</v>
       </c>
     </row>
     <row r="156">
@@ -2139,10 +2139,10 @@
         <v>43040</v>
       </c>
       <c r="B156" t="n">
-        <v>383.8564453125</v>
+        <v>383.8563842773438</v>
       </c>
       <c r="C156" t="n">
-        <v>0.05884917002767298</v>
+        <v>0.05884909080042067</v>
       </c>
     </row>
     <row r="157">
@@ -2153,7 +2153,7 @@
         <v>409.7915649414062</v>
       </c>
       <c r="C157" t="n">
-        <v>0.06756463241822686</v>
+        <v>0.06756480216654115</v>
       </c>
     </row>
     <row r="158">
@@ -2161,10 +2161,10 @@
         <v>43101</v>
       </c>
       <c r="B158" t="n">
-        <v>452.3418579101562</v>
+        <v>452.341796875</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1038339892985207</v>
+        <v>0.1038338403565671</v>
       </c>
     </row>
     <row r="159">
@@ -2172,10 +2172,10 @@
         <v>43132</v>
       </c>
       <c r="B159" t="n">
-        <v>461.1311340332031</v>
+        <v>461.1310424804688</v>
       </c>
       <c r="C159" t="n">
-        <v>0.01943060534714558</v>
+        <v>0.01943054050319737</v>
       </c>
     </row>
     <row r="160">
@@ -2183,10 +2183,10 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>445.0862426757812</v>
+        <v>445.0862121582031</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.03479463903703062</v>
+        <v>-0.03479451358546348</v>
       </c>
     </row>
     <row r="161">
@@ -2194,10 +2194,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>471.7095947265625</v>
+        <v>471.7096557617188</v>
       </c>
       <c r="C161" t="n">
-        <v>0.05981616481948815</v>
+        <v>0.05981637461744715</v>
       </c>
     </row>
     <row r="162">
@@ -2205,10 +2205,10 @@
         <v>43221</v>
       </c>
       <c r="B162" t="n">
-        <v>484.4118347167969</v>
+        <v>484.4118041992188</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02692809332741586</v>
+        <v>0.02692789575610566</v>
       </c>
     </row>
     <row r="163">
@@ -2216,10 +2216,10 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>526.663818359375</v>
+        <v>526.6638793945312</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08722326874462105</v>
+        <v>0.08722346323735741</v>
       </c>
     </row>
     <row r="164">
@@ -2227,10 +2227,10 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>549.9912719726562</v>
+        <v>549.9915161132812</v>
       </c>
       <c r="C164" t="n">
-        <v>0.04429287298669804</v>
+        <v>0.04429321552404186</v>
       </c>
     </row>
     <row r="165">
@@ -2238,10 +2238,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>580.6114501953125</v>
+        <v>580.611328125</v>
       </c>
       <c r="C165" t="n">
-        <v>0.05567393481142102</v>
+        <v>0.05567324424948406</v>
       </c>
     </row>
     <row r="166">
@@ -2249,10 +2249,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>588.2664184570312</v>
+        <v>588.266357421875</v>
       </c>
       <c r="C166" t="n">
-        <v>0.013184321906059</v>
+        <v>0.01318442980021728</v>
       </c>
     </row>
     <row r="167">
@@ -2260,10 +2260,10 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>559.1167602539062</v>
+        <v>559.1168212890625</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.04955179709149793</v>
+        <v>-0.04955159472413606</v>
       </c>
     </row>
     <row r="168">
@@ -2271,10 +2271,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>543.6807861328125</v>
+        <v>543.6807250976562</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.02760778287898924</v>
+        <v>-0.02760799819225224</v>
       </c>
     </row>
     <row r="169">
@@ -2285,7 +2285,7 @@
         <v>536.7570190429688</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.01273498579762644</v>
+        <v>-0.01273487496442671</v>
       </c>
     </row>
     <row r="170">
@@ -2293,10 +2293,10 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>613.9127197265625</v>
+        <v>613.9127807617188</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1437441858164452</v>
+        <v>0.1437442995274059</v>
       </c>
     </row>
     <row r="171">
@@ -2304,10 +2304,10 @@
         <v>43497</v>
       </c>
       <c r="B171" t="n">
-        <v>601.4224853515625</v>
+        <v>601.4224243164062</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.02034529335141189</v>
+        <v>-0.02034549016851372</v>
       </c>
     </row>
     <row r="172">
@@ -2315,10 +2315,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>609.2442626953125</v>
+        <v>609.244384765625</v>
       </c>
       <c r="C172" t="n">
-        <v>0.01300546210735321</v>
+        <v>0.01300576788121832</v>
       </c>
     </row>
     <row r="173">
@@ -2326,10 +2326,10 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>615.3870239257812</v>
+        <v>615.3870849609375</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01008259183811266</v>
+        <v>0.01008248963620018</v>
       </c>
     </row>
     <row r="174">
@@ -2337,10 +2337,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>604.2481689453125</v>
+        <v>604.2482299804688</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.01810056849981967</v>
+        <v>-0.01810056670457394</v>
       </c>
     </row>
     <row r="175">
@@ -2351,7 +2351,7 @@
         <v>608.0078735351562</v>
       </c>
       <c r="C175" t="n">
-        <v>0.006222119955127337</v>
+        <v>0.006222018316559996</v>
       </c>
     </row>
     <row r="176">
@@ -2359,10 +2359,10 @@
         <v>43647</v>
       </c>
       <c r="B176" t="n">
-        <v>659.215087890625</v>
+        <v>659.2150268554688</v>
       </c>
       <c r="C176" t="n">
-        <v>0.08422130137515049</v>
+        <v>0.08422120098968033</v>
       </c>
     </row>
     <row r="177">
@@ -2370,10 +2370,10 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>676.8656005859375</v>
+        <v>676.8655395507812</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0267750435624754</v>
+        <v>0.02677504604151304</v>
       </c>
     </row>
     <row r="178">
@@ -2384,7 +2384,7 @@
         <v>669.182373046875</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.01135118630997267</v>
+        <v>-0.01135109716030958</v>
       </c>
     </row>
     <row r="179">
@@ -2392,10 +2392,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>576.6356201171875</v>
+        <v>576.6357421875</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.1382982526994996</v>
+        <v>-0.1382980702823926</v>
       </c>
     </row>
     <row r="180">
@@ -2406,7 +2406,7 @@
         <v>585.6770629882812</v>
       </c>
       <c r="C180" t="n">
-        <v>0.01567964682663248</v>
+        <v>0.01567943181337061</v>
       </c>
     </row>
     <row r="181">
@@ -2414,10 +2414,10 @@
         <v>43800</v>
       </c>
       <c r="B181" t="n">
-        <v>614.9461669921875</v>
+        <v>614.9462890625</v>
       </c>
       <c r="C181" t="n">
-        <v>0.04997481693165073</v>
+        <v>0.04997502535762521</v>
       </c>
     </row>
     <row r="182">
@@ -2428,7 +2428,7 @@
         <v>652.6260375976562</v>
       </c>
       <c r="C182" t="n">
-        <v>0.06127344575504523</v>
+        <v>0.06127323508627058</v>
       </c>
     </row>
     <row r="183">
@@ -2447,10 +2447,10 @@
         <v>43891</v>
       </c>
       <c r="B184" t="n">
-        <v>539.5445556640625</v>
+        <v>539.544677734375</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.1232745715550095</v>
+        <v>-0.1232743731985514</v>
       </c>
     </row>
     <row r="185">
@@ -2458,10 +2458,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>601.7835083007812</v>
+        <v>601.7835693359375</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1153546115577351</v>
+        <v>0.1153544723356599</v>
       </c>
     </row>
     <row r="186">
@@ -2472,7 +2472,7 @@
         <v>589.0885620117188</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.02109553703940548</v>
+        <v>-0.02109563632358324</v>
       </c>
     </row>
     <row r="187">
@@ -2480,10 +2480,10 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>627.4090576171875</v>
+        <v>627.4091796875</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06505048319832496</v>
+        <v>0.06505069041727363</v>
       </c>
     </row>
     <row r="188">
@@ -2491,10 +2491,10 @@
         <v>44013</v>
       </c>
       <c r="B188" t="n">
-        <v>823.5304565429688</v>
+        <v>823.5302734375</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3125893650159006</v>
+        <v>0.3125888177914196</v>
       </c>
     </row>
     <row r="189">
@@ -2502,10 +2502,10 @@
         <v>44044</v>
       </c>
       <c r="B189" t="n">
-        <v>791.646240234375</v>
+        <v>791.6463012695312</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.03871649925667342</v>
+        <v>-0.03871621140881898</v>
       </c>
     </row>
     <row r="190">
@@ -2516,7 +2516,7 @@
         <v>859.5492553710938</v>
       </c>
       <c r="C190" t="n">
-        <v>0.08577444278218938</v>
+        <v>0.08577435907004083</v>
       </c>
     </row>
     <row r="191">
@@ -2535,10 +2535,10 @@
         <v>44136</v>
       </c>
       <c r="B192" t="n">
-        <v>947.8416137695312</v>
+        <v>947.841552734375</v>
       </c>
       <c r="C192" t="n">
-        <v>0.03714883925947698</v>
+        <v>0.03714877247348602</v>
       </c>
     </row>
     <row r="193">
@@ -2549,7 +2549,7 @@
         <v>1082.09033203125</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1416362357502079</v>
+        <v>0.1416363092645476</v>
       </c>
     </row>
     <row r="194">
@@ -2557,10 +2557,10 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>1067.657348632812</v>
+        <v>1067.657470703125</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.0133380578046054</v>
+        <v>-0.01333794499488072</v>
       </c>
     </row>
     <row r="195">
@@ -2571,7 +2571,7 @@
         <v>1079.936401367188</v>
       </c>
       <c r="C195" t="n">
-        <v>0.01150093028451393</v>
+        <v>0.01150081463484343</v>
       </c>
     </row>
     <row r="196">
@@ -2579,10 +2579,10 @@
         <v>44256</v>
       </c>
       <c r="B196" t="n">
-        <v>1178.813232421875</v>
+        <v>1178.813354492188</v>
       </c>
       <c r="C196" t="n">
-        <v>0.09155801298068167</v>
+        <v>0.09155812601540503</v>
       </c>
     </row>
     <row r="197">
@@ -2593,7 +2593,7 @@
         <v>1167.008422851562</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01001414748802865</v>
+        <v>-0.01001425000458223</v>
       </c>
     </row>
     <row r="198">
@@ -2601,10 +2601,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>1213.918090820312</v>
+        <v>1213.917846679688</v>
       </c>
       <c r="C198" t="n">
-        <v>0.04019651191045148</v>
+        <v>0.04019630270834096</v>
       </c>
     </row>
     <row r="199">
@@ -2615,7 +2615,7 @@
         <v>1376.833374023438</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1342061580885032</v>
+        <v>0.1342063861976799</v>
       </c>
     </row>
     <row r="200">
@@ -2623,10 +2623,10 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>1402.701049804688</v>
+        <v>1402.701293945312</v>
       </c>
       <c r="C200" t="n">
-        <v>0.01878780415211634</v>
+        <v>0.01878798147250227</v>
       </c>
     </row>
     <row r="201">
@@ -2634,10 +2634,10 @@
         <v>44409</v>
       </c>
       <c r="B201" t="n">
-        <v>1486.271240234375</v>
+        <v>1486.271118164062</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05957804796775745</v>
+        <v>0.05957777652268148</v>
       </c>
     </row>
     <row r="202">
@@ -2648,7 +2648,7 @@
         <v>1459.053100585938</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.01831303661917416</v>
+        <v>-0.01831295599133109</v>
       </c>
     </row>
     <row r="203">
@@ -2667,10 +2667,10 @@
         <v>44501</v>
       </c>
       <c r="B204" t="n">
-        <v>1504.890991210938</v>
+        <v>1504.890869140625</v>
       </c>
       <c r="C204" t="n">
-        <v>0.02692267067748544</v>
+        <v>0.0269225873779162</v>
       </c>
     </row>
     <row r="205">
@@ -2681,7 +2681,7 @@
         <v>1658.749755859375</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1022391426003768</v>
+        <v>0.1022392320093031</v>
       </c>
     </row>
     <row r="206">
@@ -2689,10 +2689,10 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>1525.583984375</v>
+        <v>1525.583740234375</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.08028080849084052</v>
+        <v>-0.08028095567435878</v>
       </c>
     </row>
     <row r="207">
@@ -2700,10 +2700,10 @@
         <v>44593</v>
       </c>
       <c r="B207" t="n">
-        <v>1507.483154296875</v>
+        <v>1507.48291015625</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.01186485323883402</v>
+        <v>-0.01186485513757785</v>
       </c>
     </row>
     <row r="208">
@@ -2711,10 +2711,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>1675.532592773438</v>
+        <v>1675.53271484375</v>
       </c>
       <c r="C208" t="n">
-        <v>0.1114768267874573</v>
+        <v>0.111477087770157</v>
       </c>
     </row>
     <row r="209">
@@ -2725,7 +2725,7 @@
         <v>1377.392822265625</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.1779373148536099</v>
+        <v>-0.177937374744681</v>
       </c>
     </row>
     <row r="210">
@@ -2755,10 +2755,10 @@
         <v>44743</v>
       </c>
       <c r="B212" t="n">
-        <v>1376.129272460938</v>
+        <v>1376.129150390625</v>
       </c>
       <c r="C212" t="n">
-        <v>0.06005885344300355</v>
+        <v>0.06005875940989336</v>
       </c>
     </row>
     <row r="213">
@@ -2766,10 +2766,10 @@
         <v>44774</v>
       </c>
       <c r="B213" t="n">
-        <v>1325.735473632812</v>
+        <v>1325.735229492188</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.03661995993879674</v>
+        <v>-0.03662005189275497</v>
       </c>
     </row>
     <row r="214">
@@ -2777,10 +2777,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>1255.139526367188</v>
+        <v>1255.1396484375</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.05325040226326316</v>
+        <v>-0.05325013583725058</v>
       </c>
     </row>
     <row r="215">
@@ -2788,10 +2788,10 @@
         <v>44835</v>
       </c>
       <c r="B215" t="n">
-        <v>1380.350830078125</v>
+        <v>1380.350952148438</v>
       </c>
       <c r="C215" t="n">
-        <v>0.09975887228517366</v>
+        <v>0.09975886258298883</v>
       </c>
     </row>
     <row r="216">
@@ -2799,10 +2799,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>1467.697509765625</v>
+        <v>1467.697387695312</v>
       </c>
       <c r="C216" t="n">
-        <v>0.06327860844083855</v>
+        <v>0.06327842597632527</v>
       </c>
     </row>
     <row r="217">
@@ -2810,10 +2810,10 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>1353.91357421875</v>
+        <v>1353.913696289062</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.07752546746846023</v>
+        <v>-0.07752530757373743</v>
       </c>
     </row>
     <row r="218">
@@ -2824,7 +2824,7 @@
         <v>1376.849975585938</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0169408164626923</v>
+        <v>0.01694072477421638</v>
       </c>
     </row>
     <row r="219">
@@ -2854,10 +2854,10 @@
         <v>45017</v>
       </c>
       <c r="B221" t="n">
-        <v>1124.595825195312</v>
+        <v>1124.595703125</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1226932901531115</v>
+        <v>-0.1226933853811942</v>
       </c>
     </row>
     <row r="222">
@@ -2868,7 +2868,7 @@
         <v>1183.440307617188</v>
       </c>
       <c r="C222" t="n">
-        <v>0.05232500521834615</v>
+        <v>0.05232511944396689</v>
       </c>
     </row>
     <row r="223">
@@ -2887,10 +2887,10 @@
         <v>45108</v>
       </c>
       <c r="B224" t="n">
-        <v>1233.371826171875</v>
+        <v>1233.371948242188</v>
       </c>
       <c r="C224" t="n">
-        <v>0.01512533210304667</v>
+        <v>0.01512543257288379</v>
       </c>
     </row>
     <row r="225">
@@ -2898,10 +2898,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>1305.92578125</v>
+        <v>1305.926025390625</v>
       </c>
       <c r="C225" t="n">
-        <v>0.05882569517038272</v>
+        <v>0.05882578832106744</v>
       </c>
     </row>
     <row r="226">
@@ -2909,7 +2909,7 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>1305.92578125</v>
+        <v>1305.926025390625</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>45200</v>
       </c>
       <c r="B227" t="n">
-        <v>1261.039672851562</v>
+        <v>1261.039794921875</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.0343711021276214</v>
+        <v>-0.03437118917614324</v>
       </c>
     </row>
     <row r="228">
@@ -2934,7 +2934,7 @@
         <v>1340.983642578125</v>
       </c>
       <c r="C228" t="n">
-        <v>0.06339528521397497</v>
+        <v>0.06339518227591134</v>
       </c>
     </row>
     <row r="229">
@@ -2975,10 +2975,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>1380.517944335938</v>
+        <v>1380.517700195312</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.1050540392366894</v>
+        <v>-0.1050541975053068</v>
       </c>
     </row>
     <row r="233">
@@ -2986,10 +2986,10 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>1309.098388671875</v>
+        <v>1309.098266601562</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.05173388434180548</v>
+        <v>-0.05173380506721914</v>
       </c>
     </row>
     <row r="234">
@@ -2997,10 +2997,10 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>1322.459716796875</v>
+        <v>1322.459838867188</v>
       </c>
       <c r="C234" t="n">
-        <v>0.01020651177987886</v>
+        <v>0.01020669922687456</v>
       </c>
     </row>
     <row r="235">
@@ -3011,7 +3011,7 @@
         <v>1472.715698242188</v>
       </c>
       <c r="C235" t="n">
-        <v>0.1136185696523497</v>
+        <v>0.1136184668592344</v>
       </c>
     </row>
     <row r="236">
@@ -3019,10 +3019,10 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>1756.1201171875</v>
+        <v>1756.119995117188</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1924366116851881</v>
+        <v>0.1924365287972873</v>
       </c>
     </row>
     <row r="237">
@@ -3030,10 +3030,10 @@
         <v>45505</v>
       </c>
       <c r="B237" t="n">
-        <v>1827.041625976562</v>
+        <v>1827.041748046875</v>
       </c>
       <c r="C237" t="n">
-        <v>0.04038534044165853</v>
+        <v>0.04038548227164562</v>
       </c>
     </row>
     <row r="238">
@@ -3041,10 +3041,10 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>1763.029052734375</v>
+        <v>1763.028930664062</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.03503618764458771</v>
+        <v>-0.03503631892990011</v>
       </c>
     </row>
     <row r="239">
@@ -3052,10 +3052,10 @@
         <v>45566</v>
       </c>
       <c r="B239" t="n">
-        <v>1670.589599609375</v>
+        <v>1670.589721679688</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.05243217800729416</v>
+        <v>-0.0524320431596984</v>
       </c>
     </row>
     <row r="240">
@@ -3066,7 +3066,7 @@
         <v>1766.228393554688</v>
       </c>
       <c r="C240" t="n">
-        <v>0.05724852708748762</v>
+        <v>0.05724844983413435</v>
       </c>
     </row>
     <row r="241">
@@ -3074,10 +3074,10 @@
         <v>45627</v>
       </c>
       <c r="B241" t="n">
-        <v>1787.286010742188</v>
+        <v>1787.2861328125</v>
       </c>
       <c r="C241" t="n">
-        <v>0.01192236364466992</v>
+        <v>0.0119224327582188</v>
       </c>
     </row>
     <row r="242">
@@ -3088,7 +3088,7 @@
         <v>1787.095947265625</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.0001063419483060546</v>
+        <v>-0.0001064102402986711</v>
       </c>
     </row>
     <row r="243">
@@ -3096,10 +3096,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>1604.469604492188</v>
+        <v>1604.469482421875</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1021916831342312</v>
+        <v>-0.1021917514407553</v>
       </c>
     </row>
     <row r="244">
@@ -3107,10 +3107,10 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>1493.192016601562</v>
+        <v>1493.19189453125</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.06935474974351052</v>
+        <v>-0.06935475502011823</v>
       </c>
     </row>
     <row r="245">
@@ -3118,10 +3118,10 @@
         <v>45748</v>
       </c>
       <c r="B245" t="n">
-        <v>1426.12109375</v>
+        <v>1426.121215820312</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.04491781506052572</v>
+        <v>-0.04491765523010194</v>
       </c>
     </row>
     <row r="246">
@@ -3132,7 +3132,7 @@
         <v>1506.536987304688</v>
       </c>
       <c r="C246" t="n">
-        <v>0.05638784385639584</v>
+        <v>0.05638775343379177</v>
       </c>
     </row>
     <row r="247">
@@ -3259,7 +3259,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>12.135817527771</v>
+        <v>12.13581848144531</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -3268,10 +3268,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92464447021484</v>
+        <v>11.92464351654053</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01740081021100681</v>
+        <v>-0.01740096601046359</v>
       </c>
     </row>
     <row r="4">
@@ -3282,7 +3282,7 @@
         <v>13.33685970306396</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1184282882711116</v>
+        <v>0.1184283777175033</v>
       </c>
     </row>
     <row r="5">
@@ -3290,10 +3290,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>12.57795715332031</v>
+        <v>12.57795906066895</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.05690264174926463</v>
+        <v>-0.056902498735941</v>
       </c>
     </row>
     <row r="6">
@@ -3301,10 +3301,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>11.50229930877686</v>
+        <v>11.50230026245117</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.08551928039121248</v>
+        <v>-0.08551934324395594</v>
       </c>
     </row>
     <row r="7">
@@ -3312,10 +3312,10 @@
         <v>38504</v>
       </c>
       <c r="B7" t="n">
-        <v>11.08325386047363</v>
+        <v>11.08325576782227</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.03643145053471775</v>
+        <v>-0.03643136460251006</v>
       </c>
     </row>
     <row r="8">
@@ -3323,10 +3323,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>11.69411849975586</v>
+        <v>11.69411659240723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05511600176016551</v>
+        <v>0.05511564808947722</v>
       </c>
     </row>
     <row r="9">
@@ -3334,10 +3334,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64409828186035</v>
+        <v>12.64410018920898</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08123568972935624</v>
+        <v>0.08123602918569883</v>
       </c>
     </row>
     <row r="10">
@@ -3345,10 +3345,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>11.85802459716797</v>
+        <v>11.8580207824707</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06216921659175256</v>
+        <v>-0.06216965976030109</v>
       </c>
     </row>
     <row r="11">
@@ -3356,10 +3356,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>10.6404447555542</v>
+        <v>10.64044284820557</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1026798208788133</v>
+        <v>-0.1026796930618505</v>
       </c>
     </row>
     <row r="12">
@@ -3367,10 +3367,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>11.64394283294678</v>
+        <v>11.64394187927246</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09430978689765412</v>
+        <v>0.09430989343043428</v>
       </c>
     </row>
     <row r="13">
@@ -3378,10 +3378,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>12.43336009979248</v>
+        <v>12.4333610534668</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06779638805955246</v>
+        <v>0.06779655741837676</v>
       </c>
     </row>
     <row r="14">
@@ -3389,10 +3389,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>13.68773365020752</v>
+        <v>13.6877384185791</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1008877359255425</v>
+        <v>0.1008880349985932</v>
       </c>
     </row>
     <row r="15">
@@ -3400,10 +3400,10 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>13.29971790313721</v>
+        <v>13.29971504211426</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.02834769852965613</v>
+        <v>-0.02834824604320019</v>
       </c>
     </row>
     <row r="16">
@@ -3411,10 +3411,10 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>14.08244705200195</v>
+        <v>14.08244800567627</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0588530639946967</v>
+        <v>0.05885336348060433</v>
       </c>
     </row>
     <row r="17">
@@ -3425,7 +3425,7 @@
         <v>17.95930099487305</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752968946771195</v>
+        <v>0.2752968083130234</v>
       </c>
     </row>
     <row r="18">
@@ -3433,10 +3433,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>15.05584239959717</v>
+        <v>15.05584049224854</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1616687974718363</v>
+        <v>-0.1616689036757822</v>
       </c>
     </row>
     <row r="19">
@@ -3444,10 +3444,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>13.09233093261719</v>
+        <v>13.09232807159424</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1304152510943204</v>
+        <v>-0.1304153309584547</v>
       </c>
     </row>
     <row r="20">
@@ -3455,10 +3455,10 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>13.90186309814453</v>
+        <v>13.90186405181885</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06183254683171358</v>
+        <v>0.06183285171267738</v>
       </c>
     </row>
     <row r="21">
@@ -3466,10 +3466,10 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>14.79318428039551</v>
+        <v>14.79318714141846</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06411523232234528</v>
+        <v>0.06411536512493754</v>
       </c>
     </row>
     <row r="22">
@@ -3480,7 +3480,7 @@
         <v>14.84402179718018</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00343654995578202</v>
+        <v>0.003436355889758991</v>
       </c>
     </row>
     <row r="23">
@@ -3488,10 +3488,10 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>16.54192924499512</v>
+        <v>16.54193496704102</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1143832494329455</v>
+        <v>0.1143836349110847</v>
       </c>
     </row>
     <row r="24">
@@ -3499,10 +3499,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>15.37610149383545</v>
+        <v>15.37610244750977</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07047713322268001</v>
+        <v>-0.07047739710342915</v>
       </c>
     </row>
     <row r="25">
@@ -3510,10 +3510,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>15.40999221801758</v>
+        <v>15.40998840332031</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002204116836489245</v>
+        <v>0.00220380658403041</v>
       </c>
     </row>
     <row r="26">
@@ -3521,10 +3521,10 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>16.59954833984375</v>
+        <v>16.59954643249512</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0771938171672355</v>
+        <v>0.0771939600498659</v>
       </c>
     </row>
     <row r="27">
@@ -3532,10 +3532,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>16.04712677001953</v>
+        <v>16.04713439941406</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.03327931329903999</v>
+        <v>-0.0332787426046568</v>
       </c>
     </row>
     <row r="28">
@@ -3543,10 +3543,10 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>16.52837944030762</v>
+        <v>16.52837562561035</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02998995877487554</v>
+        <v>0.02998923136169784</v>
       </c>
     </row>
     <row r="29">
@@ -3557,7 +3557,7 @@
         <v>20.55117607116699</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2433872386211691</v>
+        <v>0.2433875255910447</v>
       </c>
     </row>
     <row r="30">
@@ -3565,10 +3565,10 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>24.74002647399902</v>
+        <v>24.74003791809082</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2038253376997208</v>
+        <v>0.2038258945579636</v>
       </c>
     </row>
     <row r="31">
@@ -3576,10 +3576,10 @@
         <v>39234</v>
       </c>
       <c r="B31" t="n">
-        <v>22.88961601257324</v>
+        <v>22.88962554931641</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07479419892175554</v>
+        <v>-0.07479424141954627</v>
       </c>
     </row>
     <row r="32">
@@ -3587,10 +3587,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>18.21877098083496</v>
+        <v>18.21876525878906</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2040595626057069</v>
+        <v>-0.2040601442109147</v>
       </c>
     </row>
     <row r="33">
@@ -3598,10 +3598,10 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>14.4291820526123</v>
+        <v>14.42918014526367</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2080046415978922</v>
+        <v>-0.208004497543939</v>
       </c>
     </row>
     <row r="34">
@@ -3609,10 +3609,10 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>13.58362770080566</v>
+        <v>13.58362579345703</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.05860029686530699</v>
+        <v>-0.05860030461149868</v>
       </c>
     </row>
     <row r="35">
@@ -3620,10 +3620,10 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>12.34097290039062</v>
+        <v>12.34097194671631</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09148180646480286</v>
+        <v>-0.09148174910260598</v>
       </c>
     </row>
     <row r="36">
@@ -3631,10 +3631,10 @@
         <v>39387</v>
       </c>
       <c r="B36" t="n">
-        <v>11.43379974365234</v>
+        <v>11.43380165100098</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.07350904698199012</v>
+        <v>-0.07350882083130517</v>
       </c>
     </row>
     <row r="37">
@@ -3645,7 +3645,7 @@
         <v>13.05301952362061</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1416169441717918</v>
+        <v>0.1416167537310631</v>
       </c>
     </row>
     <row r="38">
@@ -3653,10 +3653,10 @@
         <v>39448</v>
       </c>
       <c r="B38" t="n">
-        <v>9.937819480895996</v>
+        <v>9.937821388244629</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.238657426129439</v>
+        <v>-0.2386572800062657</v>
       </c>
     </row>
     <row r="39">
@@ -3667,7 +3667,7 @@
         <v>8.74309253692627</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1202202300279668</v>
+        <v>-0.1202203988825553</v>
       </c>
     </row>
     <row r="40">
@@ -3675,10 +3675,10 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>7.606559276580811</v>
+        <v>7.60655689239502</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1299921344244425</v>
+        <v>-0.1299924071180896</v>
       </c>
     </row>
     <row r="41">
@@ -3686,10 +3686,10 @@
         <v>39539</v>
       </c>
       <c r="B41" t="n">
-        <v>10.82102870941162</v>
+        <v>10.82103157043457</v>
       </c>
       <c r="C41" t="n">
-        <v>0.422591781112857</v>
+        <v>0.4225926031334044</v>
       </c>
     </row>
     <row r="42">
@@ -3700,7 +3700,7 @@
         <v>9.670804977416992</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1062952296757348</v>
+        <v>-0.1062954659665026</v>
       </c>
     </row>
     <row r="43">
@@ -3708,10 +3708,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>8.078972816467285</v>
+        <v>8.078969955444336</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.164601826287151</v>
+        <v>-0.1646021221283923</v>
       </c>
     </row>
     <row r="44">
@@ -3719,10 +3719,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>9.917247772216797</v>
+        <v>9.91724681854248</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2275382028768032</v>
+        <v>0.2275385195434907</v>
       </c>
     </row>
     <row r="45">
@@ -3730,10 +3730,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>9.730194091796875</v>
+        <v>9.730195045471191</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.01886145074886136</v>
+        <v>-0.01886126023621337</v>
       </c>
     </row>
     <row r="46">
@@ -3741,10 +3741,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>7.729100227355957</v>
+        <v>7.729098796844482</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2056581652495461</v>
+        <v>-0.20565839012221</v>
       </c>
     </row>
     <row r="47">
@@ -3752,10 +3752,10 @@
         <v>39722</v>
       </c>
       <c r="B47" t="n">
-        <v>7.076184749603271</v>
+        <v>7.076185703277588</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.08447496584942604</v>
+        <v>-0.08447467301536571</v>
       </c>
     </row>
     <row r="48">
@@ -3763,10 +3763,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>6.052695274353027</v>
+        <v>6.052697658538818</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1446386027876995</v>
+        <v>-0.1446383811358575</v>
       </c>
     </row>
     <row r="49">
@@ -3774,10 +3774,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>5.435073375701904</v>
+        <v>5.435073852539062</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1020408050721074</v>
+        <v>-0.1020410800014843</v>
       </c>
     </row>
     <row r="50">
@@ -3785,10 +3785,10 @@
         <v>39814</v>
       </c>
       <c r="B50" t="n">
-        <v>5.08214807510376</v>
+        <v>5.082147598266602</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.06493478122594187</v>
+        <v>-0.06493495099566804</v>
       </c>
     </row>
     <row r="51">
@@ -3796,10 +3796,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>4.813923835754395</v>
+        <v>4.813923358917236</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05277773008294118</v>
+        <v>-0.05277773503486005</v>
       </c>
     </row>
     <row r="52">
@@ -3810,7 +3810,7 @@
         <v>5.463307857513428</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1348970286849724</v>
+        <v>0.1348971411007784</v>
       </c>
     </row>
     <row r="53">
@@ -3818,10 +3818,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>6.860900402069092</v>
+        <v>6.860897541046143</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2558143492927314</v>
+        <v>0.2558138256131175</v>
       </c>
     </row>
     <row r="54">
@@ -3829,10 +3829,10 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>8.459657669067383</v>
+        <v>8.459656715393066</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2330244098159684</v>
+        <v>0.2330247849909075</v>
       </c>
     </row>
     <row r="55">
@@ -3840,10 +3840,10 @@
         <v>39965</v>
       </c>
       <c r="B55" t="n">
-        <v>8.685530662536621</v>
+        <v>8.685532569885254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.02670001580502945</v>
+        <v>0.02670035701108153</v>
       </c>
     </row>
     <row r="56">
@@ -3851,10 +3851,10 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>12.77095699310303</v>
+        <v>12.77095794677734</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4703715281540728</v>
+        <v>0.4703713150598505</v>
       </c>
     </row>
     <row r="57">
@@ -3862,10 +3862,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>15.62240123748779</v>
+        <v>15.62240600585938</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2232756907665332</v>
+        <v>0.2232759727943174</v>
       </c>
     </row>
     <row r="58">
@@ -3873,10 +3873,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>17.03528213500977</v>
+        <v>17.03528022766113</v>
       </c>
       <c r="C58" t="n">
-        <v>0.09043941939806266</v>
+        <v>0.09043896447652444</v>
       </c>
     </row>
     <row r="59">
@@ -3884,10 +3884,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>17.28482818603516</v>
+        <v>17.28483009338379</v>
       </c>
       <c r="C59" t="n">
-        <v>0.01464877711138923</v>
+        <v>0.01464900268076885</v>
       </c>
     </row>
     <row r="60">
@@ -3898,7 +3898,7 @@
         <v>21.82072448730469</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2624206762398826</v>
+        <v>0.262420536934125</v>
       </c>
     </row>
     <row r="61">
@@ -3928,10 +3928,10 @@
         <v>40210</v>
       </c>
       <c r="B63" t="n">
-        <v>20.9252872467041</v>
+        <v>20.92528343200684</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.07178897231309467</v>
+        <v>-0.07178914152673688</v>
       </c>
     </row>
     <row r="64">
@@ -3939,10 +3939,10 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>19.9931526184082</v>
+        <v>19.99315643310547</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.04454584624365032</v>
+        <v>-0.04454548976266703</v>
       </c>
     </row>
     <row r="65">
@@ -3950,10 +3950,10 @@
         <v>40269</v>
       </c>
       <c r="B65" t="n">
-        <v>23.54553604125977</v>
+        <v>23.5455379486084</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1776800032817631</v>
+        <v>0.1776798739803163</v>
       </c>
     </row>
     <row r="66">
@@ -3964,7 +3964,7 @@
         <v>21.75833892822266</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.07590386177258113</v>
+        <v>-0.0759039366306502</v>
       </c>
     </row>
     <row r="67">
@@ -3983,10 +3983,10 @@
         <v>40360</v>
       </c>
       <c r="B68" t="n">
-        <v>26.87248992919922</v>
+        <v>26.87249565124512</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1088088170018793</v>
+        <v>0.1088090531041148</v>
       </c>
     </row>
     <row r="69">
@@ -3994,10 +3994,10 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>25.54555130004883</v>
+        <v>25.54555320739746</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.0493790725253398</v>
+        <v>-0.04937920396634887</v>
       </c>
     </row>
     <row r="70">
@@ -4005,10 +4005,10 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>24.87829208374023</v>
+        <v>24.8782958984375</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.02612036861022127</v>
+        <v>-0.0261202919953496</v>
       </c>
     </row>
     <row r="71">
@@ -4016,10 +4016,10 @@
         <v>40452</v>
       </c>
       <c r="B71" t="n">
-        <v>23.16463661193848</v>
+        <v>23.16464042663574</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.06888155609852964</v>
+        <v>-0.06888154553662118</v>
       </c>
     </row>
     <row r="72">
@@ -4027,10 +4027,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>24.43850326538086</v>
+        <v>24.43850135803223</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05499186863073269</v>
+        <v>0.05499161255841223</v>
       </c>
     </row>
     <row r="73">
@@ -4038,10 +4038,10 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>25.43181610107422</v>
+        <v>25.43181228637695</v>
       </c>
       <c r="C73" t="n">
-        <v>0.04064540389019933</v>
+        <v>0.04064532901557216</v>
       </c>
     </row>
     <row r="74">
@@ -4049,10 +4049,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>24.33234596252441</v>
+        <v>24.33235168457031</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.04323207332815548</v>
+        <v>-0.0432317048201708</v>
       </c>
     </row>
     <row r="75">
@@ -4060,10 +4060,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>23.9683895111084</v>
+        <v>23.96838569641113</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.01495772137945783</v>
+        <v>-0.01495810979873269</v>
       </c>
     </row>
     <row r="76">
@@ -4071,10 +4071,10 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>23.73332786560059</v>
+        <v>23.73332977294922</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.009807152266065766</v>
+        <v>-0.009806915093873436</v>
       </c>
     </row>
     <row r="77">
@@ -4082,10 +4082,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>26.64502143859863</v>
+        <v>26.64502716064453</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1226837462275274</v>
+        <v>0.1226838970995974</v>
       </c>
     </row>
     <row r="78">
@@ -4093,7 +4093,7 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>26.64502143859863</v>
+        <v>26.64502716064453</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>24.53707885742188</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.07911206174235386</v>
+        <v>-0.07911225950394818</v>
       </c>
     </row>
     <row r="80">
@@ -4115,10 +4115,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>22.57290840148926</v>
+        <v>22.57290649414062</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.08004907460035748</v>
+        <v>-0.08004915233367871</v>
       </c>
     </row>
     <row r="81">
@@ -4126,10 +4126,10 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>19.41130447387695</v>
+        <v>19.41130828857422</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1400618773345005</v>
+        <v>-0.1400616356775801</v>
       </c>
     </row>
     <row r="82">
@@ -4140,7 +4140,7 @@
         <v>18.56666374206543</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.04351282691733627</v>
+        <v>-0.04351301488555304</v>
       </c>
     </row>
     <row r="83">
@@ -4148,10 +4148,10 @@
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>20.52716636657715</v>
+        <v>20.52716827392578</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1055926175939688</v>
+        <v>0.1055927203237137</v>
       </c>
     </row>
     <row r="84">
@@ -4159,10 +4159,10 @@
         <v>40848</v>
       </c>
       <c r="B84" t="n">
-        <v>19.51204490661621</v>
+        <v>19.51205062866211</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.04945258599422586</v>
+        <v>-0.04945239556267023</v>
       </c>
     </row>
     <row r="85">
@@ -4170,10 +4170,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>22.084716796875</v>
+        <v>22.08472061157227</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1318504494311838</v>
+        <v>0.1318503130127722</v>
       </c>
     </row>
     <row r="86">
@@ -4181,10 +4181,10 @@
         <v>40909</v>
       </c>
       <c r="B86" t="n">
-        <v>26.91236686706543</v>
+        <v>26.91236114501953</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2185968746890856</v>
+        <v>0.2185964051054199</v>
       </c>
     </row>
     <row r="87">
@@ -4192,10 +4192,10 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>28.34204483032227</v>
+        <v>28.34204292297363</v>
       </c>
       <c r="C87" t="n">
-        <v>0.05312345697124221</v>
+        <v>0.05312361001140475</v>
       </c>
     </row>
     <row r="88">
@@ -4203,10 +4203,10 @@
         <v>40969</v>
       </c>
       <c r="B88" t="n">
-        <v>28.38147354125977</v>
+        <v>28.3814754486084</v>
       </c>
       <c r="C88" t="n">
-        <v>0.001391173825796566</v>
+        <v>0.001391308514419043</v>
       </c>
     </row>
     <row r="89">
@@ -4214,10 +4214,10 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>34.39055633544922</v>
+        <v>34.39056396484375</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2117255393894086</v>
+        <v>0.2117257267726012</v>
       </c>
     </row>
     <row r="90">
@@ -4225,10 +4225,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>34.75331115722656</v>
+        <v>34.75331497192383</v>
       </c>
       <c r="C90" t="n">
-        <v>0.01054809402438828</v>
+        <v>0.01054798076155139</v>
       </c>
     </row>
     <row r="91">
@@ -4236,10 +4236,10 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>41.0305061340332</v>
+        <v>41.03051376342773</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1806214938314263</v>
+        <v>0.1806215837704999</v>
       </c>
     </row>
     <row r="92">
@@ -4247,10 +4247,10 @@
         <v>41091</v>
       </c>
       <c r="B92" t="n">
-        <v>43.07243728637695</v>
+        <v>43.07244873046875</v>
       </c>
       <c r="C92" t="n">
-        <v>0.04976617021670249</v>
+        <v>0.04976625393516465</v>
       </c>
     </row>
     <row r="93">
@@ -4258,10 +4258,10 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>39.47638702392578</v>
+        <v>39.47639846801758</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.0834884322552264</v>
+        <v>-0.08348841007284979</v>
       </c>
     </row>
     <row r="94">
@@ -4269,10 +4269,10 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>44.53007507324219</v>
+        <v>44.53007888793945</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1280179983607284</v>
+        <v>0.1280177679839813</v>
       </c>
     </row>
     <row r="95">
@@ -4283,7 +4283,7 @@
         <v>36.88147354125977</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1717626013295992</v>
+        <v>-0.1717626722810779</v>
       </c>
     </row>
     <row r="96">
@@ -4291,10 +4291,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>41.75095367431641</v>
+        <v>41.75096130371094</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1320305200823686</v>
+        <v>0.1320307269448877</v>
       </c>
     </row>
     <row r="97">
@@ -4302,10 +4302,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>45.0106201171875</v>
+        <v>45.01061630249023</v>
       </c>
       <c r="C97" t="n">
-        <v>0.07807405953642488</v>
+        <v>0.07807377116582881</v>
       </c>
     </row>
     <row r="98">
@@ -4313,10 +4313,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>41.19828414916992</v>
+        <v>41.19828033447266</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.08469858797972485</v>
+        <v>-0.08469859515801959</v>
       </c>
     </row>
     <row r="99">
@@ -4324,10 +4324,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>36.56113815307617</v>
+        <v>36.5611457824707</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.1125567749206172</v>
+        <v>-0.1125565075618419</v>
       </c>
     </row>
     <row r="100">
@@ -4338,7 +4338,7 @@
         <v>39.39540100097656</v>
       </c>
       <c r="C100" t="n">
-        <v>0.07752118755257964</v>
+        <v>0.07752096270092146</v>
       </c>
     </row>
     <row r="101">
@@ -4346,10 +4346,10 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>39.82582855224609</v>
+        <v>39.82582092285156</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01092583246605017</v>
+        <v>0.01092563880398956</v>
       </c>
     </row>
     <row r="102">
@@ -4357,10 +4357,10 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>40.36993026733398</v>
+        <v>40.36992263793945</v>
       </c>
       <c r="C102" t="n">
-        <v>0.01366203127134202</v>
+        <v>0.01366203388856424</v>
       </c>
     </row>
     <row r="103">
@@ -4368,10 +4368,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>40.66228866577148</v>
+        <v>40.66228485107422</v>
       </c>
       <c r="C103" t="n">
-        <v>0.007241984231864507</v>
+        <v>0.007242080094055137</v>
       </c>
     </row>
     <row r="104">
@@ -4379,10 +4379,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>36.62063598632812</v>
+        <v>36.62065124511719</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.09939560246262091</v>
+        <v>-0.09939514271663608</v>
       </c>
     </row>
     <row r="105">
@@ -4393,7 +4393,7 @@
         <v>37.59609603881836</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0266368954611933</v>
+        <v>0.0266364676906512</v>
       </c>
     </row>
     <row r="106">
@@ -4401,10 +4401,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>38.14995956420898</v>
+        <v>38.14994812011719</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01473194250857213</v>
+        <v>0.01473163811282352</v>
       </c>
     </row>
     <row r="107">
@@ -4412,10 +4412,10 @@
         <v>41548</v>
       </c>
       <c r="B107" t="n">
-        <v>44.48210906982422</v>
+        <v>44.48210525512695</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1659805037265583</v>
+        <v>0.165980753501227</v>
       </c>
     </row>
     <row r="108">
@@ -4426,7 +4426,7 @@
         <v>53.40994262695312</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2007061657781279</v>
+        <v>0.2007062687483112</v>
       </c>
     </row>
     <row r="109">
@@ -4434,10 +4434,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>58.94850921630859</v>
+        <v>58.94850158691406</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1036991675508832</v>
+        <v>0.1036990247049232</v>
       </c>
     </row>
     <row r="110">
@@ -4445,10 +4445,10 @@
         <v>41640</v>
       </c>
       <c r="B110" t="n">
-        <v>64.0001220703125</v>
+        <v>64.00011444091797</v>
       </c>
       <c r="C110" t="n">
-        <v>0.08569534533040124</v>
+        <v>0.08569535642149906</v>
       </c>
     </row>
     <row r="111">
@@ -4459,7 +4459,7 @@
         <v>66.16522979736328</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03382974371005298</v>
+        <v>0.0338298669519419</v>
       </c>
     </row>
     <row r="112">
@@ -4467,10 +4467,10 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>62.7127571105957</v>
+        <v>62.7127685546875</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.05217956164198434</v>
+        <v>-0.0521793886796621</v>
       </c>
     </row>
     <row r="113">
@@ -4478,10 +4478,10 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>60.44735336303711</v>
+        <v>60.44734954833984</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.03612349148616589</v>
+        <v>-0.03612372820651566</v>
       </c>
     </row>
     <row r="114">
@@ -4489,10 +4489,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>61.08265686035156</v>
+        <v>61.08266448974609</v>
       </c>
       <c r="C114" t="n">
-        <v>0.01051003000079964</v>
+        <v>0.0105102199873659</v>
       </c>
     </row>
     <row r="115">
@@ -4503,7 +4503,7 @@
         <v>73.29585266113281</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1999453924982881</v>
+        <v>0.1999452426217743</v>
       </c>
     </row>
     <row r="116">
@@ -4511,10 +4511,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>71.43006134033203</v>
+        <v>71.43006896972656</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.02545561928895013</v>
+        <v>-0.02545551519855138</v>
       </c>
     </row>
     <row r="117">
@@ -4522,10 +4522,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>75.32070922851562</v>
+        <v>75.32069396972656</v>
       </c>
       <c r="C117" t="n">
-        <v>0.05446793430074792</v>
+        <v>0.05446760805521444</v>
       </c>
     </row>
     <row r="118">
@@ -4536,7 +4536,7 @@
         <v>104.4030075073242</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3861129107344934</v>
+        <v>0.3861131915391889</v>
       </c>
     </row>
     <row r="119">
@@ -4544,10 +4544,10 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>102.945068359375</v>
+        <v>102.9450912475586</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.01396453208349324</v>
+        <v>-0.01396431285433375</v>
       </c>
     </row>
     <row r="120">
@@ -4555,10 +4555,10 @@
         <v>41944</v>
       </c>
       <c r="B120" t="n">
-        <v>100.1139984130859</v>
+        <v>100.1139678955078</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.02750078261550104</v>
+        <v>-0.02750129528024414</v>
       </c>
     </row>
     <row r="121">
@@ -4566,10 +4566,10 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>102.4619293212891</v>
+        <v>102.4619369506836</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0234525735203901</v>
+        <v>0.02345296170486844</v>
       </c>
     </row>
     <row r="122">
@@ -4577,10 +4577,10 @@
         <v>42005</v>
       </c>
       <c r="B122" t="n">
-        <v>111.3580856323242</v>
+        <v>111.3580627441406</v>
       </c>
       <c r="C122" t="n">
-        <v>0.08682401717363275</v>
+        <v>0.08682371286557733</v>
       </c>
     </row>
     <row r="123">
@@ -4588,10 +4588,10 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>123.2124786376953</v>
+        <v>123.2124481201172</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1064529166253023</v>
+        <v>0.1064528699930201</v>
       </c>
     </row>
     <row r="124">
@@ -4599,10 +4599,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>109.7706604003906</v>
+        <v>109.7706527709961</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.1090946175738431</v>
+        <v>-0.1090944588327388</v>
       </c>
     </row>
     <row r="125">
@@ -4610,10 +4610,10 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>119.2354049682617</v>
+        <v>119.2354125976562</v>
       </c>
       <c r="C125" t="n">
-        <v>0.08622289902737457</v>
+        <v>0.08622304402621683</v>
       </c>
     </row>
     <row r="126">
@@ -4621,10 +4621,10 @@
         <v>42125</v>
       </c>
       <c r="B126" t="n">
-        <v>132.1310119628906</v>
+        <v>132.1310424804688</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1081524988157794</v>
+        <v>0.108152683853471</v>
       </c>
     </row>
     <row r="127">
@@ -4632,10 +4632,10 @@
         <v>42156</v>
       </c>
       <c r="B127" t="n">
-        <v>112.3053817749023</v>
+        <v>112.3053665161133</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1500452459529816</v>
+        <v>-0.1500455577445856</v>
       </c>
     </row>
     <row r="128">
@@ -4643,10 +4643,10 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>164.6190185546875</v>
+        <v>164.6190032958984</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4658159382302731</v>
+        <v>0.4658160015200996</v>
       </c>
     </row>
     <row r="129">
@@ -4657,7 +4657,7 @@
         <v>144.1385650634766</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.1244112233873342</v>
+        <v>-0.1244111422276614</v>
       </c>
     </row>
     <row r="130">
@@ -4676,10 +4676,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>165.9803619384766</v>
+        <v>165.9804077148438</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1921529804621824</v>
+        <v>0.1921533092506724</v>
       </c>
     </row>
     <row r="132">
@@ -4687,10 +4687,10 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>188.0031127929688</v>
+        <v>188.0030517578125</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1326828704148464</v>
+        <v>0.1326821903028694</v>
       </c>
     </row>
     <row r="133">
@@ -4701,7 +4701,7 @@
         <v>187.7359771728516</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.001420910622960569</v>
+        <v>-0.001420586434442539</v>
       </c>
     </row>
     <row r="134">
@@ -4709,10 +4709,10 @@
         <v>42370</v>
       </c>
       <c r="B134" t="n">
-        <v>156.7057189941406</v>
+        <v>156.7057037353516</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1652866895626557</v>
+        <v>-0.1652867708405722</v>
       </c>
     </row>
     <row r="135">
@@ -4720,10 +4720,10 @@
         <v>42401</v>
       </c>
       <c r="B135" t="n">
-        <v>146.0663299560547</v>
+        <v>146.0663604736328</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.0678940698934144</v>
+        <v>-0.06789378438762339</v>
       </c>
     </row>
     <row r="136">
@@ -4731,10 +4731,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>163.0665893554688</v>
+        <v>163.0666198730469</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1163872564233575</v>
+        <v>0.1163872321066208</v>
       </c>
     </row>
     <row r="137">
@@ -4742,10 +4742,10 @@
         <v>42461</v>
       </c>
       <c r="B137" t="n">
-        <v>170.7102355957031</v>
+        <v>170.7102203369141</v>
       </c>
       <c r="C137" t="n">
-        <v>0.04687438592078474</v>
+        <v>0.04687409642646667</v>
       </c>
     </row>
     <row r="138">
@@ -4753,10 +4753,10 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>165.7833404541016</v>
+        <v>165.7833557128906</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.02886115835063363</v>
+        <v>-0.0288609821620508</v>
       </c>
     </row>
     <row r="139">
@@ -4764,10 +4764,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>169.6444854736328</v>
+        <v>169.6444702148438</v>
       </c>
       <c r="C139" t="n">
-        <v>0.02329030775321028</v>
+        <v>0.02329012152848398</v>
       </c>
     </row>
     <row r="140">
@@ -4775,10 +4775,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>183.7349243164062</v>
+        <v>183.7349548339844</v>
       </c>
       <c r="C140" t="n">
-        <v>0.08305863172288896</v>
+        <v>0.08305890903072721</v>
       </c>
     </row>
     <row r="141">
@@ -4786,10 +4786,10 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>188.1026916503906</v>
+        <v>188.1027221679688</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02377211273379221</v>
+        <v>0.02377210878534752</v>
       </c>
     </row>
     <row r="142">
@@ -4800,7 +4800,7 @@
         <v>173.4531860351562</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.07788036144885202</v>
+        <v>-0.0778805110525248</v>
       </c>
     </row>
     <row r="143">
@@ -4819,10 +4819,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>175.6370697021484</v>
+        <v>175.6370391845703</v>
       </c>
       <c r="C144" t="n">
-        <v>0.09390626441860528</v>
+        <v>0.0939060743484228</v>
       </c>
     </row>
     <row r="145">
@@ -4833,7 +4833,7 @@
         <v>165.9755706787109</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.0550083136767302</v>
+        <v>-0.05500814948096744</v>
       </c>
     </row>
     <row r="146">
@@ -4841,10 +4841,10 @@
         <v>42736</v>
       </c>
       <c r="B146" t="n">
-        <v>155.964599609375</v>
+        <v>155.9645690917969</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.06031593100357391</v>
+        <v>-0.06031611487146482</v>
       </c>
     </row>
     <row r="147">
@@ -4855,7 +4855,7 @@
         <v>161.4317626953125</v>
       </c>
       <c r="C147" t="n">
-        <v>0.03505387183777864</v>
+        <v>0.03505407436670938</v>
       </c>
     </row>
     <row r="148">
@@ -4863,10 +4863,10 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>162.5387115478516</v>
+        <v>162.5387268066406</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0068570697244279</v>
+        <v>0.006857164246031333</v>
       </c>
     </row>
     <row r="149">
@@ -4874,10 +4874,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>152.0225982666016</v>
+        <v>152.0225830078125</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.06469913032474139</v>
+        <v>-0.06469931200666013</v>
       </c>
     </row>
     <row r="150">
@@ -4885,10 +4885,10 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>152.1455841064453</v>
+        <v>152.1455688476562</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0008089970915250433</v>
+        <v>0.000808997172725423</v>
       </c>
     </row>
     <row r="151">
@@ -4896,10 +4896,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>142.9384765625</v>
+        <v>142.9384918212891</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.06051511516432684</v>
+        <v>-0.06051492065198594</v>
       </c>
     </row>
     <row r="152">
@@ -4907,10 +4907,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>141.8410186767578</v>
+        <v>141.8410034179688</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.007677833933414813</v>
+        <v>-0.007678046615270495</v>
       </c>
     </row>
     <row r="153">
@@ -4918,10 +4918,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>140.8041076660156</v>
+        <v>140.8040924072266</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.007310374815519438</v>
+        <v>-0.007310375601945474</v>
       </c>
     </row>
     <row r="154">
@@ -4932,7 +4932,7 @@
         <v>132.8900909423828</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.05620586540276717</v>
+        <v>-0.05620576312480519</v>
       </c>
     </row>
     <row r="155">
@@ -4951,10 +4951,10 @@
         <v>43040</v>
       </c>
       <c r="B156" t="n">
-        <v>151.4920501708984</v>
+        <v>151.4920349121094</v>
       </c>
       <c r="C156" t="n">
-        <v>0.07978035445029219</v>
+        <v>0.07978024569118158</v>
       </c>
     </row>
     <row r="157">
@@ -4962,10 +4962,10 @@
         <v>43070</v>
       </c>
       <c r="B157" t="n">
-        <v>157.8463287353516</v>
+        <v>157.8462982177734</v>
       </c>
       <c r="C157" t="n">
-        <v>0.04194463377639202</v>
+        <v>0.04194453727782177</v>
       </c>
     </row>
     <row r="158">
@@ -4973,10 +4973,10 @@
         <v>43101</v>
       </c>
       <c r="B158" t="n">
-        <v>169.8990478515625</v>
+        <v>169.8990783691406</v>
       </c>
       <c r="C158" t="n">
-        <v>0.07635729771339039</v>
+        <v>0.07635769915071755</v>
       </c>
     </row>
     <row r="159">
@@ -4987,7 +4987,7 @@
         <v>159.1717834472656</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.06313904957059602</v>
+        <v>-0.06313921785124554</v>
       </c>
     </row>
     <row r="160">
@@ -4995,10 +4995,10 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>160.5973205566406</v>
+        <v>160.5973663330078</v>
       </c>
       <c r="C160" t="n">
-        <v>0.008955966180069108</v>
+        <v>0.008956253771036593</v>
       </c>
     </row>
     <row r="161">
@@ -5006,10 +5006,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>228.1239624023438</v>
+        <v>228.1239318847656</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4204717837860024</v>
+        <v>0.4204711888720367</v>
       </c>
     </row>
     <row r="162">
@@ -5017,10 +5017,10 @@
         <v>43221</v>
       </c>
       <c r="B162" t="n">
-        <v>232.364990234375</v>
+        <v>232.3650054931641</v>
       </c>
       <c r="C162" t="n">
-        <v>0.01859089149324578</v>
+        <v>0.01859109464473363</v>
       </c>
     </row>
     <row r="163">
@@ -5028,10 +5028,10 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>227.9100952148438</v>
+        <v>227.9101409912109</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.01917197171156382</v>
+        <v>-0.01917183911793541</v>
       </c>
     </row>
     <row r="164">
@@ -5039,10 +5039,10 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>221.4770202636719</v>
+        <v>221.4770050048828</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.02822637121496363</v>
+        <v>-0.02822663334922082</v>
       </c>
     </row>
     <row r="165">
@@ -5050,10 +5050,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>299.8219299316406</v>
+        <v>299.8218994140625</v>
       </c>
       <c r="C165" t="n">
-        <v>0.353738322714916</v>
+        <v>0.353738278190336</v>
       </c>
     </row>
     <row r="166">
@@ -5061,10 +5061,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>253.1895904541016</v>
+        <v>253.1895141601562</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.1555334510993617</v>
+        <v>-0.1555336196089719</v>
       </c>
     </row>
     <row r="167">
@@ -5072,10 +5072,10 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>229.8464660644531</v>
+        <v>229.8464202880859</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.09219622476493594</v>
+        <v>-0.09219613201400012</v>
       </c>
     </row>
     <row r="168">
@@ -5083,10 +5083,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>199.2898712158203</v>
+        <v>199.2898406982422</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.1329435051660276</v>
+        <v>-0.1329434652562551</v>
       </c>
     </row>
     <row r="169">
@@ -5094,10 +5094,10 @@
         <v>43435</v>
       </c>
       <c r="B169" t="n">
-        <v>208.0267333984375</v>
+        <v>208.0267028808594</v>
       </c>
       <c r="C169" t="n">
-        <v>0.04383997103975057</v>
+        <v>0.04383997775303672</v>
       </c>
     </row>
     <row r="170">
@@ -5105,10 +5105,10 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>202.2188262939453</v>
+        <v>202.2188110351562</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.02791904198855155</v>
+        <v>-0.02791897273413702</v>
       </c>
     </row>
     <row r="171">
@@ -5119,7 +5119,7 @@
         <v>181.5603485107422</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.1021590232809183</v>
+        <v>-0.1021589555326905</v>
       </c>
     </row>
     <row r="172">
@@ -5127,10 +5127,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>207.1246490478516</v>
+        <v>207.1246337890625</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1408033237807804</v>
+        <v>0.1408032397382613</v>
       </c>
     </row>
     <row r="173">
@@ -5138,10 +5138,10 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>211.2203216552734</v>
+        <v>211.2203369140625</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01977395074053057</v>
+        <v>0.0197740995364708</v>
       </c>
     </row>
     <row r="174">
@@ -5149,10 +5149,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>225.0376281738281</v>
+        <v>225.0376586914062</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0654165584555142</v>
+        <v>0.06541662597084819</v>
       </c>
     </row>
     <row r="175">
@@ -5160,10 +5160,10 @@
         <v>43617</v>
       </c>
       <c r="B175" t="n">
-        <v>232.6889038085938</v>
+        <v>232.6888732910156</v>
       </c>
       <c r="C175" t="n">
-        <v>0.03399998345545785</v>
+        <v>0.03399970762272053</v>
       </c>
     </row>
     <row r="176">
@@ -5174,7 +5174,7 @@
         <v>191.2090148925781</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.1782632873208958</v>
+        <v>-0.1782631795485989</v>
       </c>
     </row>
     <row r="177">
@@ -5182,10 +5182,10 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>199.6506958007812</v>
+        <v>199.6507110595703</v>
       </c>
       <c r="C177" t="n">
-        <v>0.04414896919450007</v>
+        <v>0.0441490489961196</v>
       </c>
     </row>
     <row r="178">
@@ -5193,10 +5193,10 @@
         <v>43709</v>
       </c>
       <c r="B178" t="n">
-        <v>199.0607147216797</v>
+        <v>199.0606994628906</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.002955066481162061</v>
+        <v>-0.002955219110157059</v>
       </c>
     </row>
     <row r="179">
@@ -5204,10 +5204,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>161.9353790283203</v>
+        <v>161.9353637695312</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.1865025740777975</v>
+        <v>-0.1865025883739566</v>
       </c>
     </row>
     <row r="180">
@@ -5215,10 +5215,10 @@
         <v>43770</v>
       </c>
       <c r="B180" t="n">
-        <v>169.3786010742188</v>
+        <v>169.3786163330078</v>
       </c>
       <c r="C180" t="n">
-        <v>0.04596414996253984</v>
+        <v>0.04596434274893713</v>
       </c>
     </row>
     <row r="181">
@@ -5229,7 +5229,7 @@
         <v>158.4860687255859</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.0643087868216593</v>
+        <v>-0.06430887111515016</v>
       </c>
     </row>
     <row r="182">
@@ -5237,10 +5237,10 @@
         <v>43831</v>
       </c>
       <c r="B182" t="n">
-        <v>155.3998565673828</v>
+        <v>155.3998718261719</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.01947308165960515</v>
+        <v>-0.01947298538118025</v>
       </c>
     </row>
     <row r="183">
@@ -5248,10 +5248,10 @@
         <v>43862</v>
       </c>
       <c r="B183" t="n">
-        <v>124.8043899536133</v>
+        <v>124.8044204711914</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.1968822062619026</v>
+        <v>-0.196882088739456</v>
       </c>
     </row>
     <row r="184">
@@ -5262,7 +5262,7 @@
         <v>81.83149719238281</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.3443219647738548</v>
+        <v>-0.3443221251023559</v>
       </c>
     </row>
     <row r="185">
@@ -5270,10 +5270,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>78.85580444335938</v>
+        <v>78.85581207275391</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.03636366009566827</v>
+        <v>-0.03636356686268594</v>
       </c>
     </row>
     <row r="186">
@@ -5284,7 +5284,7 @@
         <v>80.76210784912109</v>
       </c>
       <c r="C186" t="n">
-        <v>0.02417454769776617</v>
+        <v>0.02417444860764872</v>
       </c>
     </row>
     <row r="187">
@@ -5292,10 +5292,10 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>115.1685333251953</v>
+        <v>115.1685256958008</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4260218856639049</v>
+        <v>0.4260217911964035</v>
       </c>
     </row>
     <row r="188">
@@ -5306,7 +5306,7 @@
         <v>148.738037109375</v>
       </c>
       <c r="C188" t="n">
-        <v>0.2914815602399941</v>
+        <v>0.2914816457948131</v>
       </c>
     </row>
     <row r="189">
@@ -5325,10 +5325,10 @@
         <v>44075</v>
       </c>
       <c r="B190" t="n">
-        <v>178.9134063720703</v>
+        <v>178.9134216308594</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1166569780841216</v>
+        <v>0.1166570733192056</v>
       </c>
     </row>
     <row r="191">
@@ -5336,10 +5336,10 @@
         <v>44105</v>
       </c>
       <c r="B191" t="n">
-        <v>165.3833160400391</v>
+        <v>165.3833312988281</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.07562368078719561</v>
+        <v>-0.07562367433756323</v>
       </c>
     </row>
     <row r="192">
@@ -5347,10 +5347,10 @@
         <v>44136</v>
       </c>
       <c r="B192" t="n">
-        <v>211.7389984130859</v>
+        <v>211.7389831542969</v>
       </c>
       <c r="C192" t="n">
-        <v>0.2802923746058172</v>
+        <v>0.2802921642188327</v>
       </c>
     </row>
     <row r="193">
@@ -5358,10 +5358,10 @@
         <v>44166</v>
       </c>
       <c r="B193" t="n">
-        <v>220.759033203125</v>
+        <v>220.7590484619141</v>
       </c>
       <c r="C193" t="n">
-        <v>0.04259978018995669</v>
+        <v>0.04259992738816609</v>
       </c>
     </row>
     <row r="194">
@@ -5369,10 +5369,10 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>220.3368225097656</v>
+        <v>220.3368072509766</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.001912540960309794</v>
+        <v>-0.001912679067423761</v>
       </c>
     </row>
     <row r="195">
@@ -5380,10 +5380,10 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>275.94677734375</v>
+        <v>275.9467468261719</v>
       </c>
       <c r="C195" t="n">
-        <v>0.2523861159499097</v>
+        <v>0.2523860641760698</v>
       </c>
     </row>
     <row r="196">
@@ -5391,10 +5391,10 @@
         <v>44256</v>
       </c>
       <c r="B196" t="n">
-        <v>256.0393371582031</v>
+        <v>256.0392761230469</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.07214231808457738</v>
+        <v>-0.07214243665523401</v>
       </c>
     </row>
     <row r="197">
@@ -5402,10 +5402,10 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>247.0202178955078</v>
+        <v>247.0202026367188</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.03522552183894512</v>
+        <v>-0.03522535144957117</v>
       </c>
     </row>
     <row r="198">
@@ -5413,10 +5413,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>267.1145935058594</v>
+        <v>267.1145324707031</v>
       </c>
       <c r="C198" t="n">
-        <v>0.08134708883971475</v>
+        <v>0.08134690855037552</v>
       </c>
     </row>
     <row r="199">
@@ -5424,10 +5424,10 @@
         <v>44348</v>
       </c>
       <c r="B199" t="n">
-        <v>290.9941101074219</v>
+        <v>290.9941711425781</v>
       </c>
       <c r="C199" t="n">
-        <v>0.08939802310366352</v>
+        <v>0.08939850052708787</v>
       </c>
     </row>
     <row r="200">
@@ -5435,10 +5435,10 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>388.7087707519531</v>
+        <v>388.708740234375</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3357960084087592</v>
+        <v>0.3357956233560422</v>
       </c>
     </row>
     <row r="201">
@@ -5446,10 +5446,10 @@
         <v>44409</v>
       </c>
       <c r="B201" t="n">
-        <v>420.8596801757812</v>
+        <v>420.8596496582031</v>
       </c>
       <c r="C201" t="n">
-        <v>0.08271207609139486</v>
+        <v>0.08271208258513174</v>
       </c>
     </row>
     <row r="202">
@@ -5460,7 +5460,7 @@
         <v>448.772705078125</v>
       </c>
       <c r="C202" t="n">
-        <v>0.06632382767264677</v>
+        <v>0.06632390499443508</v>
       </c>
     </row>
     <row r="203">
@@ -5468,10 +5468,10 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>433.6038513183594</v>
+        <v>433.6037902832031</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.03380074943979705</v>
+        <v>-0.03380088544440596</v>
       </c>
     </row>
     <row r="204">
@@ -5479,10 +5479,10 @@
         <v>44501</v>
       </c>
       <c r="B204" t="n">
-        <v>419.4212036132812</v>
+        <v>419.4211730957031</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.03270876783487098</v>
+        <v>-0.03270870205778598</v>
       </c>
     </row>
     <row r="205">
@@ -5490,10 +5490,10 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>489.8648071289062</v>
+        <v>489.8647766113281</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1679543211186245</v>
+        <v>0.1679543333391784</v>
       </c>
     </row>
     <row r="206">
@@ -5501,10 +5501,10 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>390.2575378417969</v>
+        <v>390.257568359375</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.203336242648062</v>
+        <v>-0.2033361307195682</v>
       </c>
     </row>
     <row r="207">
@@ -5515,7 +5515,7 @@
         <v>326.4296264648438</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.1635533082331591</v>
+        <v>-0.1635533736420821</v>
       </c>
     </row>
     <row r="208">
@@ -5523,10 +5523,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>345.8448181152344</v>
+        <v>345.8449096679688</v>
       </c>
       <c r="C208" t="n">
-        <v>0.05947741894831227</v>
+        <v>0.05947769941530101</v>
       </c>
     </row>
     <row r="209">
@@ -5537,7 +5537,7 @@
         <v>304.5169067382812</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.1194984259188259</v>
+        <v>-0.119498659006908</v>
       </c>
     </row>
     <row r="210">
@@ -5556,10 +5556,10 @@
         <v>44713</v>
       </c>
       <c r="B211" t="n">
-        <v>256.4501342773438</v>
+        <v>256.4501037597656</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.1102027746979684</v>
+        <v>-0.1102028805838803</v>
       </c>
     </row>
     <row r="212">
@@ -5570,7 +5570,7 @@
         <v>236.5513153076172</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.07759332638214389</v>
+        <v>-0.07759321661569296</v>
       </c>
     </row>
     <row r="213">
@@ -5589,10 +5589,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>202.2463226318359</v>
+        <v>202.2463531494141</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.08336954258363438</v>
+        <v>-0.08336940427040707</v>
       </c>
     </row>
     <row r="215">
@@ -5600,10 +5600,10 @@
         <v>44835</v>
       </c>
       <c r="B215" t="n">
-        <v>213.4742889404297</v>
+        <v>213.4743041992188</v>
       </c>
       <c r="C215" t="n">
-        <v>0.05551629400467695</v>
+        <v>0.0555162101811042</v>
       </c>
     </row>
     <row r="216">
@@ -5611,10 +5611,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>212.9965209960938</v>
+        <v>212.9965057373047</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.002238058488014283</v>
+        <v>-0.002238201284723074</v>
       </c>
     </row>
     <row r="217">
@@ -5622,10 +5622,10 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>203.5363616943359</v>
+        <v>203.5363922119141</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.04441461887507214</v>
+        <v>-0.04441440714082923</v>
       </c>
     </row>
     <row r="218">
@@ -5636,7 +5636,7 @@
         <v>220.0677185058594</v>
       </c>
       <c r="C218" t="n">
-        <v>0.08122065597472794</v>
+        <v>0.08122049386005403</v>
       </c>
     </row>
     <row r="219">
@@ -5644,10 +5644,10 @@
         <v>44958</v>
       </c>
       <c r="B219" t="n">
-        <v>279.1785888671875</v>
+        <v>279.1786193847656</v>
       </c>
       <c r="C219" t="n">
-        <v>0.2686030952774852</v>
+        <v>0.268603233951064</v>
       </c>
     </row>
     <row r="220">
@@ -5655,10 +5655,10 @@
         <v>44986</v>
       </c>
       <c r="B220" t="n">
-        <v>263.8396606445312</v>
+        <v>263.8396911621094</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.05494306810882754</v>
+        <v>-0.05494306210288991</v>
       </c>
     </row>
     <row r="221">
@@ -5669,7 +5669,7 @@
         <v>267.5902404785156</v>
       </c>
       <c r="C221" t="n">
-        <v>0.01421537544742946</v>
+        <v>0.0142152581360544</v>
       </c>
     </row>
     <row r="222">
@@ -5677,10 +5677,10 @@
         <v>45047</v>
       </c>
       <c r="B222" t="n">
-        <v>355.4887390136719</v>
+        <v>355.48876953125</v>
       </c>
       <c r="C222" t="n">
-        <v>0.3284817053789877</v>
+        <v>0.3284818194249188</v>
       </c>
     </row>
     <row r="223">
@@ -5691,7 +5691,7 @@
         <v>372.1259765625</v>
       </c>
       <c r="C223" t="n">
-        <v>0.04680102552612286</v>
+        <v>0.04680093566159038</v>
       </c>
     </row>
     <row r="224">
@@ -5699,10 +5699,10 @@
         <v>45108</v>
       </c>
       <c r="B224" t="n">
-        <v>481.997314453125</v>
+        <v>481.9972839355469</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2952530723749991</v>
+        <v>0.2952529903662706</v>
       </c>
     </row>
     <row r="225">
@@ -5710,10 +5710,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>510.6322631835938</v>
+        <v>510.6322326660156</v>
       </c>
       <c r="C225" t="n">
-        <v>0.05940893833186189</v>
+        <v>0.05940894209332903</v>
       </c>
     </row>
     <row r="226">
@@ -5721,10 +5721,10 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>501.3779907226562</v>
+        <v>501.3779602050781</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.0181231644143296</v>
+        <v>-0.01812316549744786</v>
       </c>
     </row>
     <row r="227">
@@ -5732,10 +5732,10 @@
         <v>45200</v>
       </c>
       <c r="B227" t="n">
-        <v>474.8749389648438</v>
+        <v>474.8749084472656</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.05286042117567347</v>
+        <v>-0.05286042439315042</v>
       </c>
     </row>
     <row r="228">
@@ -5743,10 +5743,10 @@
         <v>45231</v>
       </c>
       <c r="B228" t="n">
-        <v>521.7761840820312</v>
+        <v>521.776123046875</v>
       </c>
       <c r="C228" t="n">
-        <v>0.09876546700785083</v>
+        <v>0.09876540909050302</v>
       </c>
     </row>
     <row r="229">
@@ -5754,10 +5754,10 @@
         <v>45261</v>
       </c>
       <c r="B229" t="n">
-        <v>591.7404174804688</v>
+        <v>591.7403564453125</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1340885911102414</v>
+        <v>0.1340886067953555</v>
       </c>
     </row>
     <row r="230">
@@ -5768,7 +5768,7 @@
         <v>556.467529296875</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.05960871885983343</v>
+        <v>-0.05960862186302029</v>
       </c>
     </row>
     <row r="231">
@@ -5776,10 +5776,10 @@
         <v>45323</v>
       </c>
       <c r="B231" t="n">
-        <v>534.4674072265625</v>
+        <v>534.4674682617188</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.03953532041323371</v>
+        <v>-0.03953521073000332</v>
       </c>
     </row>
     <row r="232">
@@ -5787,10 +5787,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>590.0438842773438</v>
+        <v>590.0438232421875</v>
       </c>
       <c r="C232" t="n">
-        <v>0.1039847824195241</v>
+        <v>0.1039845421485113</v>
       </c>
     </row>
     <row r="233">
@@ -5798,10 +5798,10 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>596.3648681640625</v>
+        <v>596.3649291992188</v>
       </c>
       <c r="C233" t="n">
-        <v>0.01071273519673954</v>
+        <v>0.01071294318835148</v>
       </c>
     </row>
     <row r="234">
@@ -5809,10 +5809,10 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>593.3015747070312</v>
+        <v>593.3016357421875</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.005136609516354862</v>
+        <v>-0.00513660899064694</v>
       </c>
     </row>
     <row r="235">
@@ -5820,10 +5820,10 @@
         <v>45444</v>
       </c>
       <c r="B235" t="n">
-        <v>726.7725830078125</v>
+        <v>726.7726440429688</v>
       </c>
       <c r="C235" t="n">
-        <v>0.2249631789140092</v>
+        <v>0.2249631557712064</v>
       </c>
     </row>
     <row r="236">
@@ -5831,10 +5831,10 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>778.400634765625</v>
+        <v>778.4006958007812</v>
       </c>
       <c r="C236" t="n">
-        <v>0.07103742348692532</v>
+        <v>0.07103741752112525</v>
       </c>
     </row>
     <row r="237">
@@ -5842,10 +5842,10 @@
         <v>45505</v>
       </c>
       <c r="B237" t="n">
-        <v>753.4302978515625</v>
+        <v>753.4302368164062</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.03207902948535113</v>
+        <v>-0.03207918379194996</v>
       </c>
     </row>
     <row r="238">
@@ -5853,10 +5853,10 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>662.6241455078125</v>
+        <v>662.6242065429688</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.1205236272057116</v>
+        <v>-0.1205234749498976</v>
       </c>
     </row>
     <row r="239">
@@ -5867,7 +5867,7 @@
         <v>690.5380859375</v>
       </c>
       <c r="C239" t="n">
-        <v>0.04212635567074785</v>
+        <v>0.04212625967916717</v>
       </c>
     </row>
     <row r="240">
@@ -5908,10 +5908,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>726.3123168945312</v>
+        <v>726.312255859375</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1512068405594407</v>
+        <v>-0.1512069118871903</v>
       </c>
     </row>
     <row r="244">
@@ -5919,10 +5919,10 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>689.3302612304688</v>
+        <v>689.330322265625</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.05091756645706547</v>
+        <v>-0.05091740266724931</v>
       </c>
     </row>
     <row r="245">
@@ -5933,7 +5933,7 @@
         <v>707.6245727539062</v>
       </c>
       <c r="C245" t="n">
-        <v>0.02653925491502696</v>
+        <v>0.02653916402248702</v>
       </c>
     </row>
     <row r="246">
@@ -5952,10 +5952,10 @@
         <v>45809</v>
       </c>
       <c r="B247" t="n">
-        <v>828.7012329101562</v>
+        <v>828.701171875</v>
       </c>
       <c r="C247" t="n">
-        <v>0.01140390325014584</v>
+        <v>0.01140382875864909</v>
       </c>
     </row>
     <row r="248">
@@ -5966,7 +5966,7 @@
         <v>803.3386840820312</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.03060517810388574</v>
+        <v>-0.03060510670641892</v>
       </c>
     </row>
     <row r="249">
@@ -6071,7 +6071,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>11.03503704071045</v>
+        <v>11.03503608703613</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -6080,10 +6080,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>10.61944007873535</v>
+        <v>10.61943912506104</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03766158286935306</v>
+        <v>-0.03766158612415749</v>
       </c>
     </row>
     <row r="4">
@@ -6091,10 +6091,10 @@
         <v>38412</v>
       </c>
       <c r="B4" t="n">
-        <v>10.01386260986328</v>
+        <v>10.01386070251465</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.05702536709865658</v>
+        <v>-0.0570254620243803</v>
       </c>
     </row>
     <row r="5">
@@ -6102,10 +6102,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>10.38591861724854</v>
+        <v>10.38592052459717</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03715409546549919</v>
+        <v>0.03715448348398631</v>
       </c>
     </row>
     <row r="6">
@@ -6113,10 +6113,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86483955383301</v>
+        <v>10.86483860015869</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04611252545240418</v>
+        <v>0.04611224151266069</v>
       </c>
     </row>
     <row r="7">
@@ -6124,10 +6124,10 @@
         <v>38504</v>
       </c>
       <c r="B7" t="n">
-        <v>12.28973960876465</v>
+        <v>12.2897367477417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1311478230186058</v>
+        <v>0.1311476589778513</v>
       </c>
     </row>
     <row r="8">
@@ -6135,10 +6135,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>12.52692413330078</v>
+        <v>12.52692604064941</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01929939381034407</v>
+        <v>0.01929978629943396</v>
       </c>
     </row>
     <row r="9">
@@ -6146,10 +6146,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97202491760254</v>
+        <v>13.97202110290527</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1153595861940437</v>
+        <v>0.1153591118496733</v>
       </c>
     </row>
     <row r="10">
@@ -6160,7 +6160,7 @@
         <v>14.22583484649658</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01816557946259323</v>
+        <v>0.01816585744624533</v>
       </c>
     </row>
     <row r="11">
@@ -6168,10 +6168,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>12.473708152771</v>
+        <v>12.47370433807373</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1231651226540905</v>
+        <v>-0.1231653908068777</v>
       </c>
     </row>
     <row r="12">
@@ -6179,10 +6179,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>13.82055473327637</v>
+        <v>13.82055568695068</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1079748350698884</v>
+        <v>0.1079752503645555</v>
       </c>
     </row>
     <row r="13">
@@ -6190,10 +6190,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>13.46849250793457</v>
+        <v>13.4684886932373</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.02547381289219319</v>
+        <v>-0.02547415615464721</v>
       </c>
     </row>
     <row r="14">
@@ -6201,10 +6201,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>14.48783874511719</v>
+        <v>14.48783493041992</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07568376613656635</v>
+        <v>0.07568378757257621</v>
       </c>
     </row>
     <row r="15">
@@ -6212,10 +6212,10 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>14.40187358856201</v>
+        <v>14.40186500549316</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.005933608046552075</v>
+        <v>-0.005933938738234001</v>
       </c>
     </row>
     <row r="16">
@@ -6226,7 +6226,7 @@
         <v>18.71260452270508</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2993173705931327</v>
+        <v>0.2993181449463462</v>
       </c>
     </row>
     <row r="17">
@@ -6234,10 +6234,10 @@
         <v>38808</v>
       </c>
       <c r="B17" t="n">
-        <v>89.346435546875</v>
+        <v>89.34644317626953</v>
       </c>
       <c r="C17" t="n">
-        <v>3.774665944468919</v>
+        <v>3.774666352183116</v>
       </c>
     </row>
     <row r="18">
@@ -6245,10 +6245,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>15.35161972045898</v>
+        <v>15.35162544250488</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.8281787110308966</v>
+        <v>-0.828178661659558</v>
       </c>
     </row>
     <row r="19">
@@ -6256,10 +6256,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>14.38140106201172</v>
+        <v>14.38139820098877</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.06319975846941173</v>
+        <v>-0.06320029401119909</v>
       </c>
     </row>
     <row r="20">
@@ -6267,10 +6267,10 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>15.42940235137939</v>
+        <v>15.42940139770508</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07287198826100183</v>
+        <v>0.07287213538418369</v>
       </c>
     </row>
     <row r="21">
@@ -6278,10 +6278,10 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>15.78334903717041</v>
+        <v>15.78334999084473</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02293975344802468</v>
+        <v>0.02293987848370405</v>
       </c>
     </row>
     <row r="22">
@@ -6289,10 +6289,10 @@
         <v>38961</v>
       </c>
       <c r="B22" t="n">
-        <v>15.84254169464111</v>
+        <v>15.84254360198975</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003750323035453418</v>
+        <v>0.003750383231655885</v>
       </c>
     </row>
     <row r="23">
@@ -6300,10 +6300,10 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>20.6117992401123</v>
+        <v>20.61179542541504</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3010411862816456</v>
+        <v>0.3010407888557933</v>
       </c>
     </row>
     <row r="24">
@@ -6311,10 +6311,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>21.981689453125</v>
+        <v>21.98169136047363</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06646145720004748</v>
+        <v>0.06646174711056307</v>
       </c>
     </row>
     <row r="25">
@@ -6322,10 +6322,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>25.84656524658203</v>
+        <v>25.84655570983887</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1758225090796006</v>
+        <v>0.1758219732042474</v>
       </c>
     </row>
     <row r="26">
@@ -6336,7 +6336,7 @@
         <v>33.69299697875977</v>
       </c>
       <c r="C26" t="n">
-        <v>0.303577347988834</v>
+        <v>0.3035778289768039</v>
       </c>
     </row>
     <row r="27">
@@ -6344,10 +6344,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>33.53275299072266</v>
+        <v>33.53275680541992</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.004756002801950987</v>
+        <v>-0.004755889582658934</v>
       </c>
     </row>
     <row r="28">
@@ -6358,7 +6358,7 @@
         <v>37.13928985595703</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1075526625037968</v>
+        <v>0.1075525365082475</v>
       </c>
     </row>
     <row r="29">
@@ -6366,10 +6366,10 @@
         <v>39173</v>
       </c>
       <c r="B29" t="n">
-        <v>38.06903457641602</v>
+        <v>38.06904602050781</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02503399295099484</v>
+        <v>0.02503430109075322</v>
       </c>
     </row>
     <row r="30">
@@ -6377,10 +6377,10 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>50.95743560791016</v>
+        <v>50.95745086669922</v>
       </c>
       <c r="C30" t="n">
-        <v>0.33855339844837</v>
+        <v>0.3385533968791448</v>
       </c>
     </row>
     <row r="31">
@@ -6391,7 +6391,7 @@
         <v>43.65135192871094</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1433762039246945</v>
+        <v>-0.1433764604336366</v>
       </c>
     </row>
     <row r="32">
@@ -6399,10 +6399,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>40.68006134033203</v>
+        <v>40.68005752563477</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06806869563241613</v>
+        <v>-0.06806878302254493</v>
       </c>
     </row>
     <row r="33">
@@ -6410,10 +6410,10 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>39.78676986694336</v>
+        <v>39.78676605224609</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.02195895099359213</v>
+        <v>-0.02195895305275219</v>
       </c>
     </row>
     <row r="34">
@@ -6421,10 +6421,10 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>45.53852081298828</v>
+        <v>45.53853607177734</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1445644108652242</v>
+        <v>0.1445649041185779</v>
       </c>
     </row>
     <row r="35">
@@ -6435,7 +6435,7 @@
         <v>42.90365600585938</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.05786013160044057</v>
+        <v>-0.05786044728721407</v>
       </c>
     </row>
     <row r="36">
@@ -6443,10 +6443,10 @@
         <v>39387</v>
       </c>
       <c r="B36" t="n">
-        <v>28.64313316345215</v>
+        <v>28.64313125610352</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3323847935117618</v>
+        <v>-0.3323848379683142</v>
       </c>
     </row>
     <row r="37">
@@ -6454,10 +6454,10 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>30.41042900085449</v>
+        <v>30.41043663024902</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06170050697028362</v>
+        <v>0.06170084402936626</v>
       </c>
     </row>
     <row r="38">
@@ -6465,10 +6465,10 @@
         <v>39448</v>
       </c>
       <c r="B38" t="n">
-        <v>16.94681358337402</v>
+        <v>16.94681167602539</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4427302034148272</v>
+        <v>-0.4427304059433159</v>
       </c>
     </row>
     <row r="39">
@@ -6476,10 +6476,10 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>16.85041236877441</v>
+        <v>16.85041427612305</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.005688456660323804</v>
+        <v>-0.005688232202327281</v>
       </c>
     </row>
     <row r="40">
@@ -6487,10 +6487,10 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>13.09730911254883</v>
+        <v>13.09730815887451</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2227306474220465</v>
+        <v>-0.2227307919999728</v>
       </c>
     </row>
     <row r="41">
@@ -6501,7 +6501,7 @@
         <v>18.21926879882812</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3910696191305305</v>
+        <v>0.3910697204206088</v>
       </c>
     </row>
     <row r="42">
@@ -6509,10 +6509,10 @@
         <v>39569</v>
       </c>
       <c r="B42" t="n">
-        <v>18.50846481323242</v>
+        <v>18.50846672058105</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01587308566537526</v>
+        <v>0.01587319035391421</v>
       </c>
     </row>
     <row r="43">
@@ -6520,10 +6520,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>15.61651992797852</v>
+        <v>15.61651611328125</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1562498518616381</v>
+        <v>-0.1562501449179479</v>
       </c>
     </row>
     <row r="44">
@@ -6531,10 +6531,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>14.88772869110107</v>
+        <v>14.88773441314697</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.04666796701432441</v>
+        <v>-0.0466673677309164</v>
       </c>
     </row>
     <row r="45">
@@ -6542,10 +6542,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>15.71179962158203</v>
+        <v>15.71179676055908</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05535236083214845</v>
+        <v>0.05535176303819611</v>
       </c>
     </row>
     <row r="46">
@@ -6553,10 +6553,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>11.80257701873779</v>
+        <v>11.80257606506348</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2488080739951937</v>
+        <v>-0.2488079979056769</v>
       </c>
     </row>
     <row r="47">
@@ -6564,10 +6564,10 @@
         <v>39722</v>
       </c>
       <c r="B47" t="n">
-        <v>8.68337345123291</v>
+        <v>8.683374404907227</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.264281568555141</v>
+        <v>-0.2642814283052429</v>
       </c>
     </row>
     <row r="48">
@@ -6575,10 +6575,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>7.403001308441162</v>
+        <v>7.403000831604004</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1474510050710711</v>
+        <v>-0.1474511536183037</v>
       </c>
     </row>
     <row r="49">
@@ -6586,10 +6586,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>9.602791786193848</v>
+        <v>9.602787971496582</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2971484653453198</v>
+        <v>0.2971480336057117</v>
       </c>
     </row>
     <row r="50">
@@ -6597,10 +6597,10 @@
         <v>39814</v>
       </c>
       <c r="B50" t="n">
-        <v>7.294034957885742</v>
+        <v>7.294034004211426</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2404255845292259</v>
+        <v>-0.2404253821013337</v>
       </c>
     </row>
     <row r="51">
@@ -6608,10 +6608,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>6.538069725036621</v>
+        <v>6.538070201873779</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1036415697503383</v>
+        <v>-0.1036413871804228</v>
       </c>
     </row>
     <row r="52">
@@ -6619,10 +6619,10 @@
         <v>39873</v>
       </c>
       <c r="B52" t="n">
-        <v>7.191876888275146</v>
+        <v>7.19187593460083</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1000000291729626</v>
+        <v>0.0999998030825171</v>
       </c>
     </row>
     <row r="53">
@@ -6630,10 +6630,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>9.330368995666504</v>
+        <v>9.330373764038086</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2973482639667708</v>
+        <v>0.2973490990227918</v>
       </c>
     </row>
     <row r="54">
@@ -6641,10 +6641,10 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>14.88092041015625</v>
+        <v>14.88092136383057</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5948908791354022</v>
+        <v>0.5948901662638499</v>
       </c>
     </row>
     <row r="55">
@@ -6655,7 +6655,7 @@
         <v>13.62097835540771</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.08466828798362658</v>
+        <v>-0.0846683466445336</v>
       </c>
     </row>
     <row r="56">
@@ -6663,10 +6663,10 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>14.54304981231689</v>
+        <v>14.54305553436279</v>
       </c>
       <c r="C56" t="n">
-        <v>0.06769495060118835</v>
+        <v>0.06769537069185638</v>
       </c>
     </row>
     <row r="57">
@@ -6674,10 +6674,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>18.36559104919434</v>
+        <v>18.3655948638916</v>
       </c>
       <c r="C57" t="n">
-        <v>0.262843164687508</v>
+        <v>0.2628429301185566</v>
       </c>
     </row>
     <row r="58">
@@ -6685,10 +6685,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>17.85785102844238</v>
+        <v>17.85785293579102</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0276462662917798</v>
+        <v>-0.02764636440384793</v>
       </c>
     </row>
     <row r="59">
@@ -6696,10 +6696,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>19.80901145935059</v>
+        <v>19.80901908874512</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1092606511164513</v>
+        <v>0.1092609598684475</v>
       </c>
     </row>
     <row r="60">
@@ -6707,10 +6707,10 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>23.5517635345459</v>
+        <v>23.55176162719727</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1889418905570168</v>
+        <v>0.1889413363521195</v>
       </c>
     </row>
     <row r="61">
@@ -6718,10 +6718,10 @@
         <v>40148</v>
       </c>
       <c r="B61" t="n">
-        <v>26.06869506835938</v>
+        <v>26.06869125366211</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1068680708398597</v>
+        <v>0.1068679985092209</v>
       </c>
     </row>
     <row r="62">
@@ -6732,7 +6732,7 @@
         <v>24.63252258300781</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.05509184412896462</v>
+        <v>-0.05509170585817369</v>
       </c>
     </row>
     <row r="63">
@@ -6740,10 +6740,10 @@
         <v>40210</v>
       </c>
       <c r="B63" t="n">
-        <v>24.92991065979004</v>
+        <v>24.92990112304688</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01207298504568799</v>
+        <v>0.01207259788504977</v>
       </c>
     </row>
     <row r="64">
@@ -6751,10 +6751,10 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>24.62525939941406</v>
+        <v>24.62526893615723</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.01222031095632259</v>
+        <v>-0.0122195505463929</v>
       </c>
     </row>
     <row r="65">
@@ -6765,7 +6765,7 @@
         <v>27.14219284057617</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1022094183999538</v>
+        <v>0.1022089915421533</v>
       </c>
     </row>
     <row r="66">
@@ -6784,10 +6784,10 @@
         <v>40330</v>
       </c>
       <c r="B67" t="n">
-        <v>25.78747177124023</v>
+        <v>25.7874698638916</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.008304313042271527</v>
+        <v>-0.008304386392207874</v>
       </c>
     </row>
     <row r="68">
@@ -6795,10 +6795,10 @@
         <v>40360</v>
       </c>
       <c r="B68" t="n">
-        <v>27.17568588256836</v>
+        <v>27.17567825317383</v>
       </c>
       <c r="C68" t="n">
-        <v>0.05383288922787477</v>
+        <v>0.05383267131708958</v>
       </c>
     </row>
     <row r="69">
@@ -6806,10 +6806,10 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>27.32658004760742</v>
+        <v>27.32657623291016</v>
       </c>
       <c r="C69" t="n">
-        <v>0.005552543022873779</v>
+        <v>0.005552684953454845</v>
       </c>
     </row>
     <row r="70">
@@ -6817,10 +6817,10 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>30.60093116760254</v>
+        <v>30.60093688964844</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1198229384829956</v>
+        <v>0.1198233042013832</v>
       </c>
     </row>
     <row r="71">
@@ -6831,7 +6831,7 @@
         <v>33.10573959350586</v>
       </c>
       <c r="C71" t="n">
-        <v>0.08185399366393087</v>
+        <v>0.08185379136887594</v>
       </c>
     </row>
     <row r="72">
@@ -6839,10 +6839,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>31.59682273864746</v>
+        <v>31.59683227539062</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.04557870850752399</v>
+        <v>-0.04557842043834681</v>
       </c>
     </row>
     <row r="73">
@@ -6850,10 +6850,10 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>29.89174652099609</v>
+        <v>29.89173316955566</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.05396353398425136</v>
+        <v>-0.0539642420788804</v>
       </c>
     </row>
     <row r="74">
@@ -6861,10 +6861,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>29.98981094360352</v>
+        <v>29.98981857299805</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003280652153882624</v>
+        <v>0.003281355513446105</v>
       </c>
     </row>
     <row r="75">
@@ -6872,10 +6872,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>30.00491142272949</v>
+        <v>30.00491333007812</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0005035203174295066</v>
+        <v>0.0005033293897171998</v>
       </c>
     </row>
     <row r="76">
@@ -6883,10 +6883,10 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>27.83960914611816</v>
+        <v>27.8396110534668</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.07216492813809994</v>
+        <v>-0.07216492355072868</v>
       </c>
     </row>
     <row r="77">
@@ -6894,10 +6894,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>28.39791679382324</v>
+        <v>28.39791297912598</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02005443556246633</v>
+        <v>0.02005422865236683</v>
       </c>
     </row>
     <row r="78">
@@ -6905,10 +6905,10 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>27.89996910095215</v>
+        <v>27.89996528625488</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.01753465567514445</v>
+        <v>-0.0175346580305783</v>
       </c>
     </row>
     <row r="79">
@@ -6916,10 +6916,10 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>28.27312278747559</v>
+        <v>28.27311515808105</v>
       </c>
       <c r="C79" t="n">
-        <v>0.01337469891716481</v>
+        <v>0.01337456401818571</v>
       </c>
     </row>
     <row r="80">
@@ -6927,10 +6927,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>35.04451370239258</v>
+        <v>35.04450607299805</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2394992221346197</v>
+        <v>0.2394992867625902</v>
       </c>
     </row>
     <row r="81">
@@ -6938,10 +6938,10 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>30.43586921691895</v>
+        <v>30.43587684631348</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1315083018303943</v>
+        <v>-0.1315078950487917</v>
       </c>
     </row>
     <row r="82">
@@ -6949,10 +6949,10 @@
         <v>40787</v>
       </c>
       <c r="B82" t="n">
-        <v>30.90775299072266</v>
+        <v>30.90775108337402</v>
       </c>
       <c r="C82" t="n">
-        <v>0.01550419902387401</v>
+        <v>0.01550388179855267</v>
       </c>
     </row>
     <row r="83">
@@ -6963,7 +6963,7 @@
         <v>36.31856918334961</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1750633957198724</v>
+        <v>0.1750634682342251</v>
       </c>
     </row>
     <row r="84">
@@ -6982,10 +6982,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>28.96520042419434</v>
+        <v>28.96521186828613</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.1101714897110275</v>
+        <v>-0.1101711381415923</v>
       </c>
     </row>
     <row r="86">
@@ -6996,7 +6996,7 @@
         <v>32.88174819946289</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1352156283371373</v>
+        <v>0.1352151798159278</v>
       </c>
     </row>
     <row r="87">
@@ -7004,10 +7004,10 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>38.78017807006836</v>
+        <v>38.78019332885742</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1793830983324001</v>
+        <v>0.1793835623828199</v>
       </c>
     </row>
     <row r="88">
@@ -7018,7 +7018,7 @@
         <v>42.87762069702148</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1056581694790011</v>
+        <v>0.1056577344372096</v>
       </c>
     </row>
     <row r="89">
@@ -7037,10 +7037,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>49.32657241821289</v>
+        <v>49.32656478881836</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2022238230387792</v>
+        <v>0.2022236370895147</v>
       </c>
     </row>
     <row r="91">
@@ -7051,7 +7051,7 @@
         <v>46.22443008422852</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.06288988230690373</v>
+        <v>-0.0628897373630416</v>
       </c>
     </row>
     <row r="92">
@@ -7070,10 +7070,10 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>44.96287155151367</v>
+        <v>44.9628791809082</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.04794534489641067</v>
+        <v>-0.04794518334977604</v>
       </c>
     </row>
     <row r="94">
@@ -7081,10 +7081,10 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>48.19761276245117</v>
+        <v>48.1976203918457</v>
       </c>
       <c r="C94" t="n">
-        <v>0.07194249609328174</v>
+        <v>0.07194248388592994</v>
       </c>
     </row>
     <row r="95">
@@ -7092,10 +7092,10 @@
         <v>41183</v>
       </c>
       <c r="B95" t="n">
-        <v>47.59918975830078</v>
+        <v>47.59919738769531</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.01241602996189461</v>
+        <v>-0.01241602799651154</v>
       </c>
     </row>
     <row r="96">
@@ -7103,10 +7103,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>45.19739151000977</v>
+        <v>45.1973876953125</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.05045880529662106</v>
+        <v>-0.05045903763502735</v>
       </c>
     </row>
     <row r="97">
@@ -7114,10 +7114,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>39.19694900512695</v>
+        <v>39.19696044921875</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.1327608143835891</v>
+        <v>-0.1327604879853723</v>
       </c>
     </row>
     <row r="98">
@@ -7125,10 +7125,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>42.69047927856445</v>
+        <v>42.69047546386719</v>
       </c>
       <c r="C98" t="n">
-        <v>0.08912760717627655</v>
+        <v>0.08912719186923757</v>
       </c>
     </row>
     <row r="99">
@@ -7136,10 +7136,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>42.72281265258789</v>
+        <v>42.72282028198242</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0007573907477695929</v>
+        <v>0.0007576588867606038</v>
       </c>
     </row>
     <row r="100">
@@ -7150,7 +7150,7 @@
         <v>45.67451858520508</v>
       </c>
       <c r="C100" t="n">
-        <v>0.06908969118254893</v>
+        <v>0.06908950026568084</v>
       </c>
     </row>
     <row r="101">
@@ -7158,10 +7158,10 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>42.06778335571289</v>
+        <v>42.06778717041016</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.07896602616103943</v>
+        <v>-0.07896594264188295</v>
       </c>
     </row>
     <row r="102">
@@ -7169,10 +7169,10 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>42.90882110595703</v>
+        <v>42.9088249206543</v>
       </c>
       <c r="C102" t="n">
-        <v>0.01999244274728174</v>
+        <v>0.01999244093437169</v>
       </c>
     </row>
     <row r="103">
@@ -7180,10 +7180,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>45.265380859375</v>
+        <v>45.26537704467773</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0549201700880757</v>
+        <v>0.05491998740075266</v>
       </c>
     </row>
     <row r="104">
@@ -7191,10 +7191,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>40.06169891357422</v>
+        <v>40.06168746948242</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.1149594203562972</v>
+        <v>-0.114959598592522</v>
       </c>
     </row>
     <row r="105">
@@ -7202,10 +7202,10 @@
         <v>41487</v>
       </c>
       <c r="B105" t="n">
-        <v>47.03329467773438</v>
+        <v>47.03329849243164</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1740214707119661</v>
+        <v>0.174021901305579</v>
       </c>
     </row>
     <row r="106">
@@ -7213,10 +7213,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>46.99160003662109</v>
+        <v>46.9915885925293</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0008864920350353245</v>
+        <v>-0.0008868163883732905</v>
       </c>
     </row>
     <row r="107">
@@ -7227,7 +7227,7 @@
         <v>46.7747802734375</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.004614011078886926</v>
+        <v>-0.00461376866766039</v>
       </c>
     </row>
     <row r="108">
@@ -7246,10 +7246,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>60.21763229370117</v>
+        <v>60.21764755249023</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1335948997140968</v>
+        <v>0.1335951869602869</v>
       </c>
     </row>
     <row r="110">
@@ -7257,10 +7257,10 @@
         <v>41640</v>
       </c>
       <c r="B110" t="n">
-        <v>67.10585021972656</v>
+        <v>67.10584259033203</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1143887207725021</v>
+        <v>0.1143883116961275</v>
       </c>
     </row>
     <row r="111">
@@ -7271,7 +7271,7 @@
         <v>74.32762145996094</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1076176103363258</v>
+        <v>0.1076177362635389</v>
       </c>
     </row>
     <row r="112">
@@ -7279,10 +7279,10 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>67.13919067382812</v>
+        <v>67.13921356201172</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.09671277843870063</v>
+        <v>-0.09671247050225462</v>
       </c>
     </row>
     <row r="113">
@@ -7290,10 +7290,10 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>67.6812744140625</v>
+        <v>67.68124389648438</v>
       </c>
       <c r="C113" t="n">
-        <v>0.008074028518870513</v>
+        <v>0.008073230318255353</v>
       </c>
     </row>
     <row r="114">
@@ -7301,10 +7301,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>65.279541015625</v>
+        <v>65.27956390380859</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.03548593638683728</v>
+        <v>-0.03548516330977969</v>
       </c>
     </row>
     <row r="115">
@@ -7312,10 +7312,10 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>75.50261688232422</v>
+        <v>75.50260162353516</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1566045916936254</v>
+        <v>0.1566039524220859</v>
       </c>
     </row>
     <row r="116">
@@ -7323,10 +7323,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>64.18956756591797</v>
+        <v>64.1895751953125</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.1498365193624795</v>
+        <v>-0.1498362464995675</v>
       </c>
     </row>
     <row r="117">
@@ -7334,10 +7334,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>61.26760482788086</v>
+        <v>61.26760101318359</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.04552083537619211</v>
+        <v>-0.0455210082515437</v>
       </c>
     </row>
     <row r="118">
@@ -7345,10 +7345,10 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>68.19343566894531</v>
+        <v>68.19345855712891</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1130422979733123</v>
+        <v>0.1130427408518084</v>
       </c>
     </row>
     <row r="119">
@@ -7356,10 +7356,10 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>65.84222412109375</v>
+        <v>65.84223937988281</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.03447856123961623</v>
+        <v>-0.03447866154605383</v>
       </c>
     </row>
     <row r="120">
@@ -7370,7 +7370,7 @@
         <v>64.83700561523438</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.01526708004290112</v>
+        <v>-0.01526730825251321</v>
       </c>
     </row>
     <row r="121">
@@ -7378,10 +7378,10 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>63.1502685546875</v>
+        <v>63.15027236938477</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0260150363907391</v>
+        <v>-0.02601497755555338</v>
       </c>
     </row>
     <row r="122">
@@ -7389,10 +7389,10 @@
         <v>42005</v>
       </c>
       <c r="B122" t="n">
-        <v>59.68307876586914</v>
+        <v>59.68308639526367</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.05490380117411231</v>
+        <v>-0.05490373745089316</v>
       </c>
     </row>
     <row r="123">
@@ -7400,10 +7400,10 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>69.43717193603516</v>
+        <v>69.43717956542969</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1634314678776938</v>
+        <v>0.1634314469859601</v>
       </c>
     </row>
     <row r="124">
@@ -7411,10 +7411,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>59.51272201538086</v>
+        <v>59.51271820068359</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.142927046766775</v>
+        <v>-0.1429271958748615</v>
       </c>
     </row>
     <row r="125">
@@ -7422,10 +7422,10 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>59.77678680419922</v>
+        <v>59.77679443359375</v>
       </c>
       <c r="C125" t="n">
-        <v>0.004437114954179311</v>
+        <v>0.004437307535166912</v>
       </c>
     </row>
     <row r="126">
@@ -7433,10 +7433,10 @@
         <v>42125</v>
       </c>
       <c r="B126" t="n">
-        <v>65.05847930908203</v>
+        <v>65.05849456787109</v>
       </c>
       <c r="C126" t="n">
-        <v>0.08835691557298264</v>
+        <v>0.08835703192724398</v>
       </c>
     </row>
     <row r="127">
@@ -7447,7 +7447,7 @@
         <v>66.45558929443359</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02147467939903924</v>
+        <v>0.02147443982284281</v>
       </c>
     </row>
     <row r="128">
@@ -7455,10 +7455,10 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>83.75833129882812</v>
+        <v>83.75830078125</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2603654890145384</v>
+        <v>0.2603650297969098</v>
       </c>
     </row>
     <row r="129">
@@ -7466,10 +7466,10 @@
         <v>42217</v>
       </c>
       <c r="B129" t="n">
-        <v>80.99675750732422</v>
+        <v>80.99676513671875</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.03297073555168284</v>
+        <v>-0.03297029212356517</v>
       </c>
     </row>
     <row r="130">
@@ -7477,10 +7477,10 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>82.09966278076172</v>
+        <v>82.09965515136719</v>
       </c>
       <c r="C130" t="n">
-        <v>0.01361665957230174</v>
+        <v>0.01361646990206111</v>
       </c>
     </row>
     <row r="131">
@@ -7488,10 +7488,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>98.26078796386719</v>
+        <v>98.26079559326172</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1968476438966871</v>
+        <v>0.1968478480463558</v>
       </c>
     </row>
     <row r="132">
@@ -7502,7 +7502,7 @@
         <v>98.912109375</v>
       </c>
       <c r="C132" t="n">
-        <v>0.006628497741869577</v>
+        <v>0.006628419582865197</v>
       </c>
     </row>
     <row r="133">
@@ -7510,10 +7510,10 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>100.6576156616211</v>
+        <v>100.6576232910156</v>
       </c>
       <c r="C133" t="n">
-        <v>0.01764704339691558</v>
+        <v>0.01764712052998441</v>
       </c>
     </row>
     <row r="134">
@@ -7521,10 +7521,10 @@
         <v>42370</v>
       </c>
       <c r="B134" t="n">
-        <v>95.820556640625</v>
+        <v>95.82052612304688</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.04805457579341788</v>
+        <v>-0.04805495112857983</v>
       </c>
     </row>
     <row r="135">
@@ -7532,10 +7532,10 @@
         <v>42401</v>
       </c>
       <c r="B135" t="n">
-        <v>72.86843872070312</v>
+        <v>72.86843109130859</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.239532295830881</v>
+        <v>-0.2395321332536267</v>
       </c>
     </row>
     <row r="136">
@@ -7543,10 +7543,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>86.26802062988281</v>
+        <v>86.26799774169922</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1838873200033673</v>
+        <v>0.1838871298546301</v>
       </c>
     </row>
     <row r="137">
@@ -7554,10 +7554,10 @@
         <v>42461</v>
       </c>
       <c r="B137" t="n">
-        <v>81.56992340087891</v>
+        <v>81.56990814208984</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.05445931406216253</v>
+        <v>-0.05445924007273517</v>
       </c>
     </row>
     <row r="138">
@@ -7565,10 +7565,10 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>84.34014892578125</v>
+        <v>84.34016418457031</v>
       </c>
       <c r="C138" t="n">
-        <v>0.03396135989104643</v>
+        <v>0.03396174037188882</v>
       </c>
     </row>
     <row r="139">
@@ -7576,10 +7576,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>89.05563354492188</v>
+        <v>89.05561828613281</v>
       </c>
       <c r="C139" t="n">
-        <v>0.05591031886000364</v>
+        <v>0.05590994690552398</v>
       </c>
     </row>
     <row r="140">
@@ -7587,10 +7587,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>79.880859375</v>
+        <v>79.88083648681641</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1030229509882032</v>
+        <v>-0.1030230543101518</v>
       </c>
     </row>
     <row r="141">
@@ -7598,10 +7598,10 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>70.99729919433594</v>
+        <v>70.99730682373047</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1112101228025135</v>
+        <v>-0.1112097726286589</v>
       </c>
     </row>
     <row r="142">
@@ -7609,10 +7609,10 @@
         <v>42614</v>
       </c>
       <c r="B142" t="n">
-        <v>74.36080932617188</v>
+        <v>74.36080169677734</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0473751842676331</v>
+        <v>0.04737496425600529</v>
       </c>
     </row>
     <row r="143">
@@ -7620,10 +7620,10 @@
         <v>42644</v>
       </c>
       <c r="B143" t="n">
-        <v>72.21314239501953</v>
+        <v>72.21311950683594</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.02888170463196471</v>
+        <v>-0.02888191279458041</v>
       </c>
     </row>
     <row r="144">
@@ -7631,10 +7631,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>75.47013092041016</v>
+        <v>75.47014617919922</v>
       </c>
       <c r="C144" t="n">
-        <v>0.04510243450664819</v>
+        <v>0.04510297705744404</v>
       </c>
     </row>
     <row r="145">
@@ -7642,10 +7642,10 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>75.38137817382812</v>
+        <v>75.38140106201172</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.001175998312175075</v>
+        <v>-0.001175896982851699</v>
       </c>
     </row>
     <row r="146">
@@ -7653,10 +7653,10 @@
         <v>42736</v>
       </c>
       <c r="B146" t="n">
-        <v>72.78999328613281</v>
+        <v>72.79000091552734</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.03437699005342709</v>
+        <v>-0.03437718203662188</v>
       </c>
     </row>
     <row r="147">
@@ -7664,10 +7664,10 @@
         <v>42767</v>
       </c>
       <c r="B147" t="n">
-        <v>73.87268829345703</v>
+        <v>73.8726806640625</v>
       </c>
       <c r="C147" t="n">
-        <v>0.01487422870157729</v>
+        <v>0.01487401751501016</v>
       </c>
     </row>
     <row r="148">
@@ -7675,10 +7675,10 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>77.31604766845703</v>
+        <v>77.31607818603516</v>
       </c>
       <c r="C148" t="n">
-        <v>0.04661207618871743</v>
+        <v>0.04661259739079426</v>
       </c>
     </row>
     <row r="149">
@@ -7686,10 +7686,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>81.44278717041016</v>
+        <v>81.44277954101562</v>
       </c>
       <c r="C149" t="n">
-        <v>0.05337494124957365</v>
+        <v>0.05337442679194027</v>
       </c>
     </row>
     <row r="150">
@@ -7700,7 +7700,7 @@
         <v>92.74910736083984</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1388253101747665</v>
+        <v>0.1388254168576135</v>
       </c>
     </row>
     <row r="151">
@@ -7708,10 +7708,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>102.4934768676758</v>
+        <v>102.4934844970703</v>
       </c>
       <c r="C151" t="n">
-        <v>0.105061598802515</v>
+        <v>0.1050616810609295</v>
       </c>
     </row>
     <row r="152">
@@ -7719,10 +7719,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>91.49776458740234</v>
+        <v>91.49778747558594</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.1072820692234829</v>
+        <v>-0.1072819123619383</v>
       </c>
     </row>
     <row r="153">
@@ -7730,10 +7730,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>88.48925018310547</v>
+        <v>88.48928070068359</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.03288074214559655</v>
+        <v>-0.03288065053709732</v>
       </c>
     </row>
     <row r="154">
@@ -7741,10 +7741,10 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>98.76461029052734</v>
+        <v>98.76463317871094</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1161198686412157</v>
+        <v>0.1161197423762985</v>
       </c>
     </row>
     <row r="155">
@@ -7752,10 +7752,10 @@
         <v>43009</v>
       </c>
       <c r="B155" t="n">
-        <v>123.2305145263672</v>
+        <v>123.2305297851562</v>
       </c>
       <c r="C155" t="n">
-        <v>0.2477193416130596</v>
+        <v>0.2477192069571623</v>
       </c>
     </row>
     <row r="156">
@@ -7766,7 +7766,7 @@
         <v>116.3221740722656</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.05606030682135477</v>
+        <v>-0.05606042370291564</v>
       </c>
     </row>
     <row r="157">
@@ -7785,10 +7785,10 @@
         <v>43101</v>
       </c>
       <c r="B158" t="n">
-        <v>155.8516540527344</v>
+        <v>155.8516845703125</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3272612730665043</v>
+        <v>0.3272615329597974</v>
       </c>
     </row>
     <row r="159">
@@ -7796,10 +7796,10 @@
         <v>43132</v>
       </c>
       <c r="B159" t="n">
-        <v>151.9105682373047</v>
+        <v>151.9105987548828</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.02528741731605988</v>
+        <v>-0.0252874123644885</v>
       </c>
     </row>
     <row r="160">
@@ -7810,7 +7810,7 @@
         <v>157.4627532958984</v>
       </c>
       <c r="C160" t="n">
-        <v>0.03654903752265937</v>
+        <v>0.03654882928856318</v>
       </c>
     </row>
     <row r="161">
@@ -7818,10 +7818,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>211.5461730957031</v>
+        <v>211.5461578369141</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3434680181044023</v>
+        <v>0.3434679212002854</v>
       </c>
     </row>
     <row r="162">
@@ -7832,7 +7832,7 @@
         <v>203.3544616699219</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.03872304237843782</v>
+        <v>-0.03872297304169126</v>
       </c>
     </row>
     <row r="163">
@@ -7840,10 +7840,10 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>199.8593139648438</v>
+        <v>199.8593597412109</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.01718746506162883</v>
+        <v>-0.01718723995534488</v>
       </c>
     </row>
     <row r="164">
@@ -7851,10 +7851,10 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>223.3422698974609</v>
+        <v>223.3421936035156</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1174974309015588</v>
+        <v>0.117496793208542</v>
       </c>
     </row>
     <row r="165">
@@ -7862,10 +7862,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>256.0725402832031</v>
+        <v>256.0725708007812</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1465475854649863</v>
+        <v>0.1465481137673863</v>
       </c>
     </row>
     <row r="166">
@@ -7873,10 +7873,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>202.0098266601562</v>
+        <v>202.0098114013672</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.2111226512739565</v>
+        <v>-0.2111228048765663</v>
       </c>
     </row>
     <row r="167">
@@ -7884,10 +7884,10 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>226.0296325683594</v>
+        <v>226.0296478271484</v>
       </c>
       <c r="C167" t="n">
-        <v>0.118904145928564</v>
+        <v>0.1189043059797574</v>
       </c>
     </row>
     <row r="168">
@@ -7895,10 +7895,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>200.6656341552734</v>
+        <v>200.6656494140625</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.1122153680686755</v>
+        <v>-0.1122153604932505</v>
       </c>
     </row>
     <row r="169">
@@ -7906,10 +7906,10 @@
         <v>43435</v>
       </c>
       <c r="B169" t="n">
-        <v>211.6213989257812</v>
+        <v>211.6214447021484</v>
       </c>
       <c r="C169" t="n">
-        <v>0.05459711532882761</v>
+        <v>0.0545972632589411</v>
       </c>
     </row>
     <row r="170">
@@ -7917,10 +7917,10 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>241.3493499755859</v>
+        <v>241.3493041992188</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1404770557264425</v>
+        <v>0.1404765927144647</v>
       </c>
     </row>
     <row r="171">
@@ -7928,10 +7928,10 @@
         <v>43497</v>
       </c>
       <c r="B171" t="n">
-        <v>243.1814727783203</v>
+        <v>243.1814270019531</v>
       </c>
       <c r="C171" t="n">
-        <v>0.007591165266944699</v>
+        <v>0.007591166706749863</v>
       </c>
     </row>
     <row r="172">
@@ -7939,10 +7939,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>244.129638671875</v>
+        <v>244.1297607421875</v>
       </c>
       <c r="C172" t="n">
-        <v>0.003899005474068407</v>
+        <v>0.003899696419771281</v>
       </c>
     </row>
     <row r="173">
@@ -7950,10 +7950,10 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>238.1731109619141</v>
+        <v>238.1731262207031</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.0243990354565955</v>
+        <v>-0.02439946077600452</v>
       </c>
     </row>
     <row r="174">
@@ -7961,10 +7961,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>240.6036224365234</v>
+        <v>240.6036071777344</v>
       </c>
       <c r="C174" t="n">
-        <v>0.01020481054638456</v>
+        <v>0.01020468176069134</v>
       </c>
     </row>
     <row r="175">
@@ -7972,10 +7972,10 @@
         <v>43617</v>
       </c>
       <c r="B175" t="n">
-        <v>247.6742095947266</v>
+        <v>247.6742553710938</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0293868691028063</v>
+        <v>0.02938712464163618</v>
       </c>
     </row>
     <row r="176">
@@ -7983,10 +7983,10 @@
         <v>43647</v>
       </c>
       <c r="B176" t="n">
-        <v>221.6105499267578</v>
+        <v>221.6105041503906</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.1052336442725189</v>
+        <v>-0.1052339944725036</v>
       </c>
     </row>
     <row r="177">
@@ -7994,10 +7994,10 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>275.3766174316406</v>
+        <v>275.376708984375</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2426151080020895</v>
+        <v>0.2426157778040035</v>
       </c>
     </row>
     <row r="178">
@@ -8005,10 +8005,10 @@
         <v>43709</v>
       </c>
       <c r="B178" t="n">
-        <v>256.8439636230469</v>
+        <v>256.843994140625</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.06729930079555246</v>
+        <v>-0.06729950006338969</v>
       </c>
     </row>
     <row r="179">
@@ -8016,10 +8016,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>285.1632080078125</v>
+        <v>285.1632995605469</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1102585553707149</v>
+        <v>0.1102587799051931</v>
       </c>
     </row>
     <row r="180">
@@ -8027,10 +8027,10 @@
         <v>43770</v>
       </c>
       <c r="B180" t="n">
-        <v>276.3022155761719</v>
+        <v>276.3023071289062</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.03107340702731143</v>
+        <v>-0.03107339705107892</v>
       </c>
     </row>
     <row r="181">
@@ -8041,7 +8041,7 @@
         <v>294.63037109375</v>
       </c>
       <c r="C181" t="n">
-        <v>0.06633372620396294</v>
+        <v>0.06633337287441821</v>
       </c>
     </row>
     <row r="182">
@@ -8060,10 +8060,10 @@
         <v>43862</v>
       </c>
       <c r="B183" t="n">
-        <v>314.8011169433594</v>
+        <v>314.8010559082031</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.1254895138717038</v>
+        <v>-0.1254896834260075</v>
       </c>
     </row>
     <row r="184">
@@ -8071,10 +8071,10 @@
         <v>43891</v>
       </c>
       <c r="B184" t="n">
-        <v>213.8262786865234</v>
+        <v>213.8262481689453</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.3207575603202318</v>
+        <v>-0.3207575255678379</v>
       </c>
     </row>
     <row r="185">
@@ -8082,10 +8082,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>224.2032012939453</v>
+        <v>224.2032165527344</v>
       </c>
       <c r="C185" t="n">
-        <v>0.04852968807746394</v>
+        <v>0.04852990908576471</v>
       </c>
     </row>
     <row r="186">
@@ -8093,10 +8093,10 @@
         <v>43952</v>
       </c>
       <c r="B186" t="n">
-        <v>272.5648193359375</v>
+        <v>272.5648803710938</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2157044045887055</v>
+        <v>0.2157045940818798</v>
       </c>
     </row>
     <row r="187">
@@ -8104,10 +8104,10 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>264.585205078125</v>
+        <v>264.5851745605469</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.02927602423986198</v>
+        <v>-0.02927635357747704</v>
       </c>
     </row>
     <row r="188">
@@ -8115,10 +8115,10 @@
         <v>44013</v>
       </c>
       <c r="B188" t="n">
-        <v>361.6548156738281</v>
+        <v>361.6548461914062</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3668746730076651</v>
+        <v>0.3668749460058891</v>
       </c>
     </row>
     <row r="189">
@@ -8129,7 +8129,7 @@
         <v>361.2418212890625</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.001141957377219338</v>
+        <v>-0.001142041664015658</v>
       </c>
     </row>
     <row r="190">
@@ -8137,10 +8137,10 @@
         <v>44075</v>
       </c>
       <c r="B190" t="n">
-        <v>436.0060729980469</v>
+        <v>436.0060119628906</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2069645520061718</v>
+        <v>0.2069643830468966</v>
       </c>
     </row>
     <row r="191">
@@ -8148,10 +8148,10 @@
         <v>44105</v>
       </c>
       <c r="B191" t="n">
-        <v>414.1231689453125</v>
+        <v>414.1231384277344</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.05018944782641233</v>
+        <v>-0.05018938485880042</v>
       </c>
     </row>
     <row r="192">
@@ -8162,7 +8162,7 @@
         <v>450.7355041503906</v>
       </c>
       <c r="C192" t="n">
-        <v>0.08840928967660111</v>
+        <v>0.08840936988370007</v>
       </c>
     </row>
     <row r="193">
@@ -8170,10 +8170,10 @@
         <v>44166</v>
       </c>
       <c r="B193" t="n">
-        <v>507.906982421875</v>
+        <v>507.9071044921875</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1268404147111712</v>
+        <v>0.1268406855358819</v>
       </c>
     </row>
     <row r="194">
@@ -8184,7 +8184,7 @@
         <v>449.2616271972656</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.1154647548749343</v>
+        <v>-0.115464967463994</v>
       </c>
     </row>
     <row r="195">
@@ -8192,10 +8192,10 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>477.2840881347656</v>
+        <v>477.2841491699219</v>
       </c>
       <c r="C195" t="n">
-        <v>0.06237448124007194</v>
+        <v>0.06237461709666969</v>
       </c>
     </row>
     <row r="196">
@@ -8206,7 +8206,7 @@
         <v>549.55126953125</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1514133472978447</v>
+        <v>0.1514132000549628</v>
       </c>
     </row>
     <row r="197">
@@ -8214,10 +8214,10 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>538.6802978515625</v>
+        <v>538.68017578125</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01978154229169571</v>
+        <v>-0.01978176441894619</v>
       </c>
     </row>
     <row r="198">
@@ -8225,10 +8225,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>665.2326049804688</v>
+        <v>665.2327270507812</v>
       </c>
       <c r="C198" t="n">
-        <v>0.2349302687208707</v>
+        <v>0.23493077517841</v>
       </c>
     </row>
     <row r="199">
@@ -8236,10 +8236,10 @@
         <v>44348</v>
       </c>
       <c r="B199" t="n">
-        <v>783.5812377929688</v>
+        <v>783.5814208984375</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1779056407134083</v>
+        <v>0.1779056998177753</v>
       </c>
     </row>
     <row r="200">
@@ -8247,10 +8247,10 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>958.22998046875</v>
+        <v>958.2300415039062</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2228853043593746</v>
+        <v>0.2228850964909561</v>
       </c>
     </row>
     <row r="201">
@@ -8261,7 +8261,7 @@
         <v>984.4340209960938</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0273462958386308</v>
+        <v>0.02734623040106454</v>
       </c>
     </row>
     <row r="202">
@@ -8269,10 +8269,10 @@
         <v>44440</v>
       </c>
       <c r="B202" t="n">
-        <v>990.5858764648438</v>
+        <v>990.5855712890625</v>
       </c>
       <c r="C202" t="n">
-        <v>0.006249129283977028</v>
+        <v>0.006248819282722806</v>
       </c>
     </row>
     <row r="203">
@@ -8280,10 +8280,10 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>920.49658203125</v>
+        <v>920.4965209960938</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.07075539445779822</v>
+        <v>-0.07075516979493346</v>
       </c>
     </row>
     <row r="204">
@@ -8294,7 +8294,7 @@
         <v>1029.20458984375</v>
       </c>
       <c r="C204" t="n">
-        <v>0.118097133584804</v>
+        <v>0.1180972077222198</v>
       </c>
     </row>
     <row r="205">
@@ -8302,10 +8302,10 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>1116.130737304688</v>
+        <v>1116.130615234375</v>
       </c>
       <c r="C205" t="n">
-        <v>0.08445954120174903</v>
+        <v>0.08445942259528971</v>
       </c>
     </row>
     <row r="206">
@@ -8313,10 +8313,10 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>912.0841674804688</v>
+        <v>912.084228515625</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.1828160116053833</v>
+        <v>-0.1828158675460242</v>
       </c>
     </row>
     <row r="207">
@@ -8324,10 +8324,10 @@
         <v>44593</v>
       </c>
       <c r="B207" t="n">
-        <v>861.7935791015625</v>
+        <v>861.7936401367188</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.05513810037710487</v>
+        <v>-0.05513809668735514</v>
       </c>
     </row>
     <row r="208">
@@ -8335,10 +8335,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>846.9728393554688</v>
+        <v>846.972900390625</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.01719755183317173</v>
+        <v>-0.01719755061518269</v>
       </c>
     </row>
     <row r="209">
@@ -8349,7 +8349,7 @@
         <v>798.0829467773438</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.05772309371257922</v>
+        <v>-0.05772316161559965</v>
       </c>
     </row>
     <row r="210">
@@ -8357,10 +8357,10 @@
         <v>44682</v>
       </c>
       <c r="B210" t="n">
-        <v>745.787109375</v>
+        <v>745.7869873046875</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.06552681975415486</v>
+        <v>-0.06552697270857266</v>
       </c>
     </row>
     <row r="211">
@@ -8368,10 +8368,10 @@
         <v>44713</v>
       </c>
       <c r="B211" t="n">
-        <v>674.8215942382812</v>
+        <v>674.8214721679688</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.0951551914006542</v>
+        <v>-0.09515520697564295</v>
       </c>
     </row>
     <row r="212">
@@ -8379,10 +8379,10 @@
         <v>44743</v>
       </c>
       <c r="B212" t="n">
-        <v>753.9476318359375</v>
+        <v>753.9474487304688</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1172547504010617</v>
+        <v>0.1172546811652206</v>
       </c>
     </row>
     <row r="213">
@@ -8390,10 +8390,10 @@
         <v>44774</v>
       </c>
       <c r="B213" t="n">
-        <v>681.153076171875</v>
+        <v>681.1530151367188</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.09655120938147987</v>
+        <v>-0.09655107092188531</v>
       </c>
     </row>
     <row r="214">
@@ -8401,10 +8401,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>643.196044921875</v>
+        <v>643.1959838867188</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.05572467126379432</v>
+        <v>-0.05572467625703958</v>
       </c>
     </row>
     <row r="215">
@@ -8412,10 +8412,10 @@
         <v>44835</v>
       </c>
       <c r="B215" t="n">
-        <v>728.8386840820312</v>
+        <v>728.8387451171875</v>
       </c>
       <c r="C215" t="n">
-        <v>0.133151688099324</v>
+        <v>0.1331518905216802</v>
       </c>
     </row>
     <row r="216">
@@ -8423,10 +8423,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>774.8348999023438</v>
+        <v>774.8348388671875</v>
       </c>
       <c r="C216" t="n">
-        <v>0.06310891123766926</v>
+        <v>0.06310873846670217</v>
       </c>
     </row>
     <row r="217">
@@ -8434,10 +8434,10 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>745.6174926757812</v>
+        <v>745.6176147460938</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.03770791329900725</v>
+        <v>-0.03770767995384605</v>
       </c>
     </row>
     <row r="218">
@@ -8445,10 +8445,10 @@
         <v>44927</v>
       </c>
       <c r="B218" t="n">
-        <v>840.6026000976562</v>
+        <v>840.6025390625</v>
       </c>
       <c r="C218" t="n">
-        <v>0.1273912003874855</v>
+        <v>0.1273909339558075</v>
       </c>
     </row>
     <row r="219">
@@ -8456,10 +8456,10 @@
         <v>44958</v>
       </c>
       <c r="B219" t="n">
-        <v>828.7484741210938</v>
+        <v>828.7486572265625</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.01410193827045669</v>
+        <v>-0.01410164885911214</v>
       </c>
     </row>
     <row r="220">
@@ -8467,10 +8467,10 @@
         <v>44986</v>
       </c>
       <c r="B220" t="n">
-        <v>735.3309936523438</v>
+        <v>735.3308715820312</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1127211492821405</v>
+        <v>-0.1127214926141266</v>
       </c>
     </row>
     <row r="221">
@@ -8481,7 +8481,7 @@
         <v>806.7413940429688</v>
       </c>
       <c r="C221" t="n">
-        <v>0.09711327416777848</v>
+        <v>0.09711345629662049</v>
       </c>
     </row>
     <row r="222">
@@ -8511,10 +8511,10 @@
         <v>45108</v>
       </c>
       <c r="B224" t="n">
-        <v>911.0354614257812</v>
+        <v>911.0355834960938</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.001613254491949601</v>
+        <v>-0.001613120717374183</v>
       </c>
     </row>
     <row r="225">
@@ -8522,10 +8522,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>1063.014404296875</v>
+        <v>1063.014526367188</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1668200078987538</v>
+        <v>0.1668199855464212</v>
       </c>
     </row>
     <row r="226">
@@ -8533,10 +8533,10 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>992.6192626953125</v>
+        <v>992.6193237304688</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.06622218976244731</v>
+        <v>-0.06622223957493012</v>
       </c>
     </row>
     <row r="227">
@@ -8544,10 +8544,10 @@
         <v>45200</v>
       </c>
       <c r="B227" t="n">
-        <v>969.2449951171875</v>
+        <v>969.2450561523438</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.02354806969457313</v>
+        <v>-0.02354806824662614</v>
       </c>
     </row>
     <row r="228">
@@ -8555,10 +8555,10 @@
         <v>45231</v>
       </c>
       <c r="B228" t="n">
-        <v>1124.5146484375</v>
+        <v>1124.514526367188</v>
       </c>
       <c r="C228" t="n">
-        <v>0.1601964973794263</v>
+        <v>0.1601962983759999</v>
       </c>
     </row>
     <row r="229">
@@ -8569,7 +8569,7 @@
         <v>1224.759155273438</v>
       </c>
       <c r="C229" t="n">
-        <v>0.08914468742157</v>
+        <v>0.08914480565235228</v>
       </c>
     </row>
     <row r="230">
@@ -8577,10 +8577,10 @@
         <v>45292</v>
       </c>
       <c r="B230" t="n">
-        <v>1220.015747070312</v>
+        <v>1220.015991210938</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.003872931410801361</v>
+        <v>-0.003872732073140539</v>
       </c>
     </row>
     <row r="231">
@@ -8591,7 +8591,7 @@
         <v>1283.140991210938</v>
       </c>
       <c r="C231" t="n">
-        <v>0.05174133554604587</v>
+        <v>0.05174112507930717</v>
       </c>
     </row>
     <row r="232">
@@ -8599,10 +8599,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>1077.260375976562</v>
+        <v>1077.260498046875</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.16045050126571</v>
+        <v>-0.1604504061317277</v>
       </c>
     </row>
     <row r="233">
@@ -8610,10 +8610,10 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>999.1057739257812</v>
+        <v>999.1058349609375</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.07254940754683581</v>
+        <v>-0.07254945598361362</v>
       </c>
     </row>
     <row r="234">
@@ -8621,10 +8621,10 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>977.28662109375</v>
+        <v>977.2866821289062</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.02183868155050028</v>
+        <v>-0.02183868021638002</v>
       </c>
     </row>
     <row r="235">
@@ -8632,10 +8632,10 @@
         <v>45444</v>
       </c>
       <c r="B235" t="n">
-        <v>1073.186889648438</v>
+        <v>1073.18701171875</v>
       </c>
       <c r="C235" t="n">
-        <v>0.09812911226325682</v>
+        <v>0.09812916858841869</v>
       </c>
     </row>
     <row r="236">
@@ -8643,10 +8643,10 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>1239.646240234375</v>
+        <v>1239.646118164062</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1551075140700493</v>
+        <v>0.155107268936028</v>
       </c>
     </row>
     <row r="237">
@@ -8654,10 +8654,10 @@
         <v>45505</v>
       </c>
       <c r="B237" t="n">
-        <v>1251.006225585938</v>
+        <v>1251.006103515625</v>
       </c>
       <c r="C237" t="n">
-        <v>0.009163892877547708</v>
+        <v>0.009163893779933652</v>
       </c>
     </row>
     <row r="238">
@@ -8665,10 +8665,10 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>1383.598999023438</v>
+        <v>1383.59912109375</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1059888997557923</v>
+        <v>0.1059891052533692</v>
       </c>
     </row>
     <row r="239">
@@ -8676,10 +8676,10 @@
         <v>45566</v>
       </c>
       <c r="B239" t="n">
-        <v>1507.35693359375</v>
+        <v>1507.357177734375</v>
       </c>
       <c r="C239" t="n">
-        <v>0.08944638920500991</v>
+        <v>0.08944646954010271</v>
       </c>
     </row>
     <row r="240">
@@ -8687,10 +8687,10 @@
         <v>45597</v>
       </c>
       <c r="B240" t="n">
-        <v>1717.275268554688</v>
+        <v>1717.275146484375</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1392625265340857</v>
+        <v>0.1392622610292777</v>
       </c>
     </row>
     <row r="241">
@@ -8698,10 +8698,10 @@
         <v>45627</v>
       </c>
       <c r="B241" t="n">
-        <v>1910.457153320312</v>
+        <v>1910.45703125</v>
       </c>
       <c r="C241" t="n">
-        <v>0.1124932550436208</v>
+        <v>0.1124932630400604</v>
       </c>
     </row>
     <row r="242">
@@ -8709,10 +8709,10 @@
         <v>45658</v>
       </c>
       <c r="B242" t="n">
-        <v>1637.398681640625</v>
+        <v>1637.398559570312</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.1429283411067978</v>
+        <v>-0.1429283502393284</v>
       </c>
     </row>
     <row r="243">
@@ -8720,10 +8720,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>1458.735961914062</v>
+        <v>1458.73583984375</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1091137556966565</v>
+        <v>-0.1091137638312368</v>
       </c>
     </row>
     <row r="244">
@@ -8731,10 +8731,10 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>1606.756225585938</v>
+        <v>1606.75634765625</v>
       </c>
       <c r="C244" t="n">
-        <v>0.1014715942682678</v>
+        <v>0.101471770124161</v>
       </c>
     </row>
     <row r="245">
@@ -8745,7 +8745,7 @@
         <v>1447.412231445312</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.09917123182921972</v>
+        <v>-0.0991713002680028</v>
       </c>
     </row>
     <row r="246">
@@ -8764,10 +8764,10 @@
         <v>45809</v>
       </c>
       <c r="B247" t="n">
-        <v>1911.284423828125</v>
+        <v>1911.284545898438</v>
       </c>
       <c r="C247" t="n">
-        <v>0.1253728004825436</v>
+        <v>0.1253728723580885</v>
       </c>
     </row>
     <row r="248">
@@ -8778,7 +8778,7 @@
         <v>1740.173706054688</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.08952655901978135</v>
+        <v>-0.08952661717008548</v>
       </c>
     </row>
     <row r="249">

--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -447,7 +447,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>80.88383483886719</v>
+        <v>80.88381958007812</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -456,10 +456,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>87.58748626708984</v>
+        <v>87.58747863769531</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08287999006942903</v>
+        <v>0.08288010003014645</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         <v>88.25608825683594</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007633533261900638</v>
+        <v>0.007633621032822724</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>73.77353668212891</v>
+        <v>73.77351379394531</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1640969123009514</v>
+        <v>-0.164097171639248</v>
       </c>
     </row>
     <row r="6">
@@ -489,10 +489,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>87.99215698242188</v>
+        <v>87.99214935302734</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1927333423305613</v>
+        <v>0.1927336089588425</v>
       </c>
     </row>
     <row r="7">
@@ -500,10 +500,10 @@
         <v>38504</v>
       </c>
       <c r="B7" t="n">
-        <v>92.47422790527344</v>
+        <v>92.47422027587891</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05093716390822123</v>
+        <v>0.05093716832474859</v>
       </c>
     </row>
     <row r="8">
@@ -511,10 +511,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>88.952880859375</v>
+        <v>88.95289611816406</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.03807922624134319</v>
+        <v>-0.03807898187418779</v>
       </c>
     </row>
     <row r="9">
@@ -522,10 +522,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>93.1741943359375</v>
+        <v>93.17417144775391</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04745561285683308</v>
+        <v>0.04745517587175963</v>
       </c>
     </row>
     <row r="10">
@@ -533,10 +533,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>98.63261413574219</v>
+        <v>98.63263702392578</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05858295678011949</v>
+        <v>0.05858346246988244</v>
       </c>
     </row>
     <row r="11">
@@ -544,10 +544,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>99.14113616943359</v>
+        <v>99.14110565185547</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005155718908469442</v>
+        <v>0.005155176250700277</v>
       </c>
     </row>
     <row r="12">
@@ -555,10 +555,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>105.5292053222656</v>
+        <v>105.5292205810547</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06443409264459832</v>
+        <v>0.06443457420811671</v>
       </c>
     </row>
     <row r="13">
@@ -569,7 +569,7 @@
         <v>117.8100433349609</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1163738320135361</v>
+        <v>0.1163736705936687</v>
       </c>
     </row>
     <row r="14">
@@ -577,10 +577,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>113.228271484375</v>
+        <v>113.2283172607422</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.03889118211729126</v>
+        <v>-0.03889079355646996</v>
       </c>
     </row>
     <row r="15">
@@ -588,10 +588,10 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>111.2096939086914</v>
+        <v>111.2096557617188</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.01782750499694896</v>
+        <v>-0.01782823897642904</v>
       </c>
     </row>
     <row r="16">
@@ -599,10 +599,10 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>117.2026901245117</v>
+        <v>117.2026596069336</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05388915305117958</v>
+        <v>0.05388924013986385</v>
       </c>
     </row>
     <row r="17">
@@ -613,7 +613,7 @@
         <v>249.8114318847656</v>
       </c>
       <c r="C17" t="n">
-        <v>1.131447935362024</v>
+        <v>1.131448490354796</v>
       </c>
     </row>
     <row r="18">
@@ -621,10 +621,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>115.9503173828125</v>
+        <v>115.950325012207</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5358486338755759</v>
+        <v>-0.5358486033349618</v>
       </c>
     </row>
     <row r="19">
@@ -632,10 +632,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>122.6885375976562</v>
+        <v>122.6885147094727</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05811299500455336</v>
+        <v>0.05811272798550804</v>
       </c>
     </row>
     <row r="20">
@@ -646,7 +646,7 @@
         <v>131.9391326904297</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07539901668002402</v>
+        <v>0.0753992173013307</v>
       </c>
     </row>
     <row r="21">
@@ -665,10 +665,10 @@
         <v>38961</v>
       </c>
       <c r="B22" t="n">
-        <v>147.4079132080078</v>
+        <v>147.4079437255859</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02394230706042988</v>
+        <v>0.0239425190452458</v>
       </c>
     </row>
     <row r="23">
@@ -676,10 +676,10 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>167.4046630859375</v>
+        <v>167.4046783447266</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1356558779155377</v>
+        <v>0.1356557463169452</v>
       </c>
     </row>
     <row r="24">
@@ -687,10 +687,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>174.1312255859375</v>
+        <v>174.1312561035156</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04018145239208115</v>
+        <v>0.04018153987869688</v>
       </c>
     </row>
     <row r="25">
@@ -698,10 +698,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>179.0922393798828</v>
+        <v>179.0922088623047</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02849008715841683</v>
+        <v>0.02848973165300039</v>
       </c>
     </row>
     <row r="26">
@@ -709,10 +709,10 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>179.5315704345703</v>
+        <v>179.5316314697266</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00245309934259974</v>
+        <v>0.002453610965062802</v>
       </c>
     </row>
     <row r="27">
@@ -720,10 +720,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>165.9706573486328</v>
+        <v>165.9706878662109</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07553497723610525</v>
+        <v>-0.07553512154097664</v>
       </c>
     </row>
     <row r="28">
@@ -731,10 +731,10 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>161.2652740478516</v>
+        <v>161.2652893066406</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.02835069388739764</v>
+        <v>-0.02835078061111207</v>
       </c>
     </row>
     <row r="29">
@@ -745,7 +745,7 @@
         <v>163.8377227783203</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01595165943602606</v>
+        <v>0.01595156330751557</v>
       </c>
     </row>
     <row r="30">
@@ -753,10 +753,10 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>153.6640319824219</v>
+        <v>153.6639862060547</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06209614381459572</v>
+        <v>-0.06209642321525144</v>
       </c>
     </row>
     <row r="31">
@@ -764,10 +764,10 @@
         <v>39234</v>
       </c>
       <c r="B31" t="n">
-        <v>154.6245574951172</v>
+        <v>154.6246032714844</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006250815498614504</v>
+        <v>0.006251413158979036</v>
       </c>
     </row>
     <row r="32">
@@ -775,10 +775,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>158.3718414306641</v>
+        <v>158.3718719482422</v>
       </c>
       <c r="C32" t="n">
-        <v>0.024234726981613</v>
+        <v>0.02423462112415886</v>
       </c>
     </row>
     <row r="33">
@@ -789,7 +789,7 @@
         <v>148.6529998779297</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.06136723210981498</v>
+        <v>-0.06136741298030968</v>
       </c>
     </row>
     <row r="34">
@@ -797,10 +797,10 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>151.7148895263672</v>
+        <v>151.7149200439453</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0205975637958995</v>
+        <v>0.02059776908996125</v>
       </c>
     </row>
     <row r="35">
@@ -808,10 +808,10 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>147.7512817382812</v>
+        <v>147.7512969970703</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02612537108559199</v>
+        <v>-0.02612546640585456</v>
       </c>
     </row>
     <row r="36">
@@ -819,10 +819,10 @@
         <v>39387</v>
       </c>
       <c r="B36" t="n">
-        <v>128.8586730957031</v>
+        <v>128.8587341308594</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1278676463602089</v>
+        <v>-0.1278673233344648</v>
       </c>
     </row>
     <row r="37">
@@ -830,10 +830,10 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>142.3195495605469</v>
+        <v>142.3195037841797</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1044623240443145</v>
+        <v>0.1044614456607229</v>
       </c>
     </row>
     <row r="38">
@@ -844,7 +844,7 @@
         <v>120.5401916503906</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1530313859017006</v>
+        <v>-0.1530311134784188</v>
       </c>
     </row>
     <row r="39">
@@ -852,10 +852,10 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>124.4923629760742</v>
+        <v>124.4924011230469</v>
       </c>
       <c r="C39" t="n">
-        <v>0.03278716643446433</v>
+        <v>0.03278748290129707</v>
       </c>
     </row>
     <row r="40">
@@ -863,10 +863,10 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>115.7838592529297</v>
+        <v>115.7839050292969</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.06995211204094653</v>
+        <v>-0.06995202932219635</v>
       </c>
     </row>
     <row r="41">
@@ -874,10 +874,10 @@
         <v>39539</v>
       </c>
       <c r="B41" t="n">
-        <v>140.9685821533203</v>
+        <v>140.9686126708984</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2175149719735514</v>
+        <v>0.2175147541899634</v>
       </c>
     </row>
     <row r="42">
@@ -885,10 +885,10 @@
         <v>39569</v>
       </c>
       <c r="B42" t="n">
-        <v>160.1132354736328</v>
+        <v>160.1132507324219</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1358079440672133</v>
+        <v>0.1358078064243846</v>
       </c>
     </row>
     <row r="43">
@@ -896,10 +896,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>141.6775817871094</v>
+        <v>141.6775360107422</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1151413475093969</v>
+        <v>-0.1151417177363359</v>
       </c>
     </row>
     <row r="44">
@@ -907,10 +907,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>129.1681671142578</v>
+        <v>129.1681976318359</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.08829494769079793</v>
+        <v>-0.08829443771493717</v>
       </c>
     </row>
     <row r="45">
@@ -918,10 +918,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>142.6809234619141</v>
+        <v>142.6809387207031</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1046136726218567</v>
+        <v>0.1046135297744273</v>
       </c>
     </row>
     <row r="46">
@@ -929,10 +929,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>114.0443801879883</v>
+        <v>114.04443359375</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2007033777123665</v>
+        <v>-0.2007030888898823</v>
       </c>
     </row>
     <row r="47">
@@ -943,7 +943,7 @@
         <v>114.1569137573242</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0009867524305049447</v>
+        <v>0.0009862836793499419</v>
       </c>
     </row>
     <row r="48">
@@ -951,10 +951,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>102.2312164306641</v>
+        <v>102.2312545776367</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.104467587061892</v>
+        <v>-0.1044672528992784</v>
       </c>
     </row>
     <row r="49">
@@ -962,10 +962,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>91.67812347412109</v>
+        <v>91.67813873291016</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1032276962457974</v>
+        <v>-0.1032278816133699</v>
       </c>
     </row>
     <row r="50">
@@ -976,7 +976,7 @@
         <v>107.3927154541016</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1714104890510373</v>
+        <v>0.1714102940830131</v>
       </c>
     </row>
     <row r="51">
@@ -984,10 +984,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>101.195686340332</v>
+        <v>101.1956558227539</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05770437117234517</v>
+        <v>-0.05770465534039138</v>
       </c>
     </row>
     <row r="52">
@@ -995,10 +995,10 @@
         <v>39873</v>
       </c>
       <c r="B52" t="n">
-        <v>108.8105163574219</v>
+        <v>108.8104782104492</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0752485633772999</v>
+        <v>0.07524851067750205</v>
       </c>
     </row>
     <row r="53">
@@ -1006,10 +1006,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>124.044303894043</v>
+        <v>124.0443344116211</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1400028972069298</v>
+        <v>0.1400035773366259</v>
       </c>
     </row>
     <row r="54">
@@ -1017,10 +1017,10 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>131.9221343994141</v>
+        <v>131.9221038818359</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06350820036122129</v>
+        <v>0.06350769269375678</v>
       </c>
     </row>
     <row r="55">
@@ -1031,7 +1031,7 @@
         <v>147.2201538085938</v>
       </c>
       <c r="C55" t="n">
-        <v>0.115962491653316</v>
+        <v>0.1159627498092393</v>
       </c>
     </row>
     <row r="56">
@@ -1039,10 +1039,10 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>171.0745544433594</v>
+        <v>171.0745697021484</v>
       </c>
       <c r="C56" t="n">
-        <v>0.162032167591535</v>
+        <v>0.1620322712375961</v>
       </c>
     </row>
     <row r="57">
@@ -1050,10 +1050,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>176.6103210449219</v>
+        <v>176.6103515625</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03235879596223246</v>
+        <v>0.03235888226981776</v>
       </c>
     </row>
     <row r="58">
@@ -1061,10 +1061,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>191.1334686279297</v>
+        <v>191.1334838867188</v>
       </c>
       <c r="C58" t="n">
-        <v>0.08223272285040339</v>
+        <v>0.08223262224286554</v>
       </c>
     </row>
     <row r="59">
@@ -1072,10 +1072,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>183.6438446044922</v>
+        <v>183.6438903808594</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.03918530897389405</v>
+        <v>-0.03918514617929691</v>
       </c>
     </row>
     <row r="60">
@@ -1083,10 +1083,10 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>198.056884765625</v>
+        <v>198.0569000244141</v>
       </c>
       <c r="C60" t="n">
-        <v>0.07848365509975963</v>
+        <v>0.07848346935835182</v>
       </c>
     </row>
     <row r="61">
@@ -1094,10 +1094,10 @@
         <v>40148</v>
       </c>
       <c r="B61" t="n">
-        <v>216.5152740478516</v>
+        <v>216.5152587890625</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0931974129759221</v>
+        <v>0.09319725171086235</v>
       </c>
     </row>
     <row r="62">
@@ -1105,10 +1105,10 @@
         <v>40179</v>
       </c>
       <c r="B62" t="n">
-        <v>206.0603942871094</v>
+        <v>206.0603637695312</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.04828703104997378</v>
+        <v>-0.04828710492740285</v>
       </c>
     </row>
     <row r="63">
@@ -1119,7 +1119,7 @@
         <v>216.5860443115234</v>
       </c>
       <c r="C63" t="n">
-        <v>0.05108041290918042</v>
+        <v>0.0510805685743847</v>
       </c>
     </row>
     <row r="64">
@@ -1138,10 +1138,10 @@
         <v>40269</v>
       </c>
       <c r="B65" t="n">
-        <v>227.9233245849609</v>
+        <v>227.9233093261719</v>
       </c>
       <c r="C65" t="n">
-        <v>0.04671345671465077</v>
+        <v>0.04671338664029623</v>
       </c>
     </row>
     <row r="66">
@@ -1149,10 +1149,10 @@
         <v>40299</v>
       </c>
       <c r="B66" t="n">
-        <v>222.5694427490234</v>
+        <v>222.5694732666016</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.02348983740776289</v>
+        <v>-0.0234896381392421</v>
       </c>
     </row>
     <row r="67">
@@ -1160,10 +1160,10 @@
         <v>40330</v>
       </c>
       <c r="B67" t="n">
-        <v>233.7063751220703</v>
+        <v>233.7063140869141</v>
       </c>
       <c r="C67" t="n">
-        <v>0.05003801166724053</v>
+        <v>0.05003759346176095</v>
       </c>
     </row>
     <row r="68">
@@ -1171,10 +1171,10 @@
         <v>40360</v>
       </c>
       <c r="B68" t="n">
-        <v>233.4886322021484</v>
+        <v>233.4886474609375</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0009316943956199086</v>
+        <v>-0.0009313681867217927</v>
       </c>
     </row>
     <row r="69">
@@ -1182,10 +1182,10 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>227.2460784912109</v>
+        <v>227.2461395263672</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.0267360070255277</v>
+        <v>-0.02673580922436358</v>
       </c>
     </row>
     <row r="70">
@@ -1196,7 +1196,7 @@
         <v>255.4357757568359</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1240492133144346</v>
+        <v>0.1240489114104308</v>
       </c>
     </row>
     <row r="71">
@@ -1215,10 +1215,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>258.9084777832031</v>
+        <v>258.9083862304688</v>
       </c>
       <c r="C72" t="n">
-        <v>0.02668531838855959</v>
+        <v>0.02668495534193749</v>
       </c>
     </row>
     <row r="73">
@@ -1226,10 +1226,10 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>292.1523742675781</v>
+        <v>292.1524047851562</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1284001851504135</v>
+        <v>0.1284007020347928</v>
       </c>
     </row>
     <row r="74">
@@ -1237,10 +1237,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>264.5686645507812</v>
+        <v>264.5685729980469</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.09441549049857578</v>
+        <v>-0.09441589846708276</v>
       </c>
     </row>
     <row r="75">
@@ -1248,10 +1248,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>254.33447265625</v>
+        <v>254.3345336914062</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0386825549121933</v>
+        <v>-0.03868199155580043</v>
       </c>
     </row>
     <row r="76">
@@ -1259,10 +1259,10 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>275.0573425292969</v>
+        <v>275.0573120117188</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08147880881666891</v>
+        <v>0.081478429293665</v>
       </c>
     </row>
     <row r="77">
@@ -1270,10 +1270,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>246.6249847412109</v>
+        <v>246.6248626708984</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1033688376635775</v>
+        <v>-0.1033691819820044</v>
       </c>
     </row>
     <row r="78">
@@ -1281,10 +1281,10 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>238.0983734130859</v>
+        <v>238.0984497070312</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.0345731854259298</v>
+        <v>-0.03457239822266023</v>
       </c>
     </row>
     <row r="79">
@@ -1292,10 +1292,10 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>248.7655029296875</v>
+        <v>248.7654418945312</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04480135401049035</v>
+        <v>0.04480076288033463</v>
       </c>
     </row>
     <row r="80">
@@ -1303,10 +1303,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>237.2650146484375</v>
+        <v>237.2650299072266</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.04623023749599464</v>
+        <v>-0.04622994214839737</v>
       </c>
     </row>
     <row r="81">
@@ -1317,7 +1317,7 @@
         <v>200.2594299316406</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1559673042046639</v>
+        <v>-0.1559673584853848</v>
       </c>
     </row>
     <row r="82">
@@ -1325,10 +1325,10 @@
         <v>40787</v>
       </c>
       <c r="B82" t="n">
-        <v>216.5078582763672</v>
+        <v>216.5078125</v>
       </c>
       <c r="C82" t="n">
-        <v>0.08113689502797961</v>
+        <v>0.08113666644265294</v>
       </c>
     </row>
     <row r="83">
@@ -1336,10 +1336,10 @@
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>247.3135223388672</v>
+        <v>247.3133850097656</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1422842769206893</v>
+        <v>0.1422838841428211</v>
       </c>
     </row>
     <row r="84">
@@ -1347,10 +1347,10 @@
         <v>40848</v>
       </c>
       <c r="B84" t="n">
-        <v>224.0478363037109</v>
+        <v>224.0478973388672</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.09407365119032096</v>
+        <v>-0.09407290135137558</v>
       </c>
     </row>
     <row r="85">
@@ -1358,10 +1358,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>237.867919921875</v>
+        <v>237.8679351806641</v>
       </c>
       <c r="C85" t="n">
-        <v>0.06168362902389313</v>
+        <v>0.06168340790493732</v>
       </c>
     </row>
     <row r="86">
@@ -1369,10 +1369,10 @@
         <v>40909</v>
       </c>
       <c r="B86" t="n">
-        <v>236.0071868896484</v>
+        <v>236.0072631835938</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.00782254720534703</v>
+        <v>-0.007822290110926944</v>
       </c>
     </row>
     <row r="87">
@@ -1380,10 +1380,10 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>247.8204956054688</v>
+        <v>247.8205261230469</v>
       </c>
       <c r="C87" t="n">
-        <v>0.05005486854662577</v>
+        <v>0.05005465840372625</v>
       </c>
     </row>
     <row r="88">
@@ -1391,10 +1391,10 @@
         <v>40969</v>
       </c>
       <c r="B88" t="n">
-        <v>246.3465118408203</v>
+        <v>246.3464508056641</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.005947787978743402</v>
+        <v>-0.005948156677913374</v>
       </c>
     </row>
     <row r="89">
@@ -1402,10 +1402,10 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>211.6072387695312</v>
+        <v>211.6072235107422</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1410179215110472</v>
+        <v>-0.1410177706287585</v>
       </c>
     </row>
     <row r="90">
@@ -1413,10 +1413,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>211.6771697998047</v>
+        <v>211.6771850585938</v>
       </c>
       <c r="C90" t="n">
-        <v>0.000330475605088365</v>
+        <v>0.000330619846954372</v>
       </c>
     </row>
     <row r="91">
@@ -1424,10 +1424,10 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>218.6347198486328</v>
+        <v>218.6346740722656</v>
       </c>
       <c r="C91" t="n">
-        <v>0.03286868421100064</v>
+        <v>0.03286839350091508</v>
       </c>
     </row>
     <row r="92">
@@ -1435,10 +1435,10 @@
         <v>41091</v>
       </c>
       <c r="B92" t="n">
-        <v>194.0413208007812</v>
+        <v>194.0413360595703</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.1124862467629949</v>
+        <v>-0.1124859911496309</v>
       </c>
     </row>
     <row r="93">
@@ -1449,7 +1449,7 @@
         <v>205.7782135009766</v>
       </c>
       <c r="C93" t="n">
-        <v>0.06048656364406724</v>
+        <v>0.06048648025080094</v>
       </c>
     </row>
     <row r="94">
@@ -1457,10 +1457,10 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>220.8783721923828</v>
+        <v>220.87841796875</v>
       </c>
       <c r="C94" t="n">
-        <v>0.07338074538845474</v>
+        <v>0.07338096784333192</v>
       </c>
     </row>
     <row r="95">
@@ -1471,7 +1471,7 @@
         <v>207.2071533203125</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.06189478280002358</v>
+        <v>-0.06189497721942083</v>
       </c>
     </row>
     <row r="96">
@@ -1479,10 +1479,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>213.6829528808594</v>
+        <v>213.6829376220703</v>
       </c>
       <c r="C96" t="n">
-        <v>0.03125277991989117</v>
+        <v>0.03125270627962906</v>
       </c>
     </row>
     <row r="97">
@@ -1490,10 +1490,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>203.3225555419922</v>
+        <v>203.3225708007812</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.04848490344779033</v>
+        <v>-0.0484847640929239</v>
       </c>
     </row>
     <row r="98">
@@ -1501,10 +1501,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>244.6061706542969</v>
+        <v>244.606201171875</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2030449351881098</v>
+        <v>0.2030449949973538</v>
       </c>
     </row>
     <row r="99">
@@ -1512,10 +1512,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>254.9094696044922</v>
+        <v>254.9095611572266</v>
       </c>
       <c r="C99" t="n">
-        <v>0.04212199112816739</v>
+        <v>0.04212223539709781</v>
       </c>
     </row>
     <row r="100">
@@ -1523,10 +1523,10 @@
         <v>41334</v>
       </c>
       <c r="B100" t="n">
-        <v>253.3618621826172</v>
+        <v>253.3618774414062</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.006071204119157292</v>
+        <v>-0.006071501236729615</v>
       </c>
     </row>
     <row r="101">
@@ -1534,10 +1534,10 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>196.0225372314453</v>
+        <v>196.0225830078125</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.2263139545044986</v>
+        <v>-0.2263138204241256</v>
       </c>
     </row>
     <row r="102">
@@ -1548,7 +1548,7 @@
         <v>213.9330139160156</v>
       </c>
       <c r="C102" t="n">
-        <v>0.09136947688531993</v>
+        <v>0.09136922202218556</v>
       </c>
     </row>
     <row r="103">
@@ -1556,10 +1556,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>221.6637878417969</v>
+        <v>221.663818359375</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0361364231928043</v>
+        <v>0.03613656584296177</v>
       </c>
     </row>
     <row r="104">
@@ -1567,10 +1567,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>263.4266357421875</v>
+        <v>263.4266967773438</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1884062719806858</v>
+        <v>0.1884063837168961</v>
       </c>
     </row>
     <row r="105">
@@ -1581,7 +1581,7 @@
         <v>275.508544921875</v>
       </c>
       <c r="C105" t="n">
-        <v>0.04586441741415981</v>
+        <v>0.04586417509058771</v>
       </c>
     </row>
     <row r="106">
@@ -1589,10 +1589,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>267.2720947265625</v>
+        <v>267.2721252441406</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.02989544370628539</v>
+        <v>-0.02989533293811253</v>
       </c>
     </row>
     <row r="107">
@@ -1600,10 +1600,10 @@
         <v>41548</v>
       </c>
       <c r="B107" t="n">
-        <v>295.3699035644531</v>
+        <v>295.3699340820312</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1051281049996506</v>
+        <v>0.1051280929959477</v>
       </c>
     </row>
     <row r="108">
@@ -1611,10 +1611,10 @@
         <v>41579</v>
       </c>
       <c r="B108" t="n">
-        <v>299.3544311523438</v>
+        <v>299.3543701171875</v>
       </c>
       <c r="C108" t="n">
-        <v>0.01348995798084474</v>
+        <v>0.01348964662750562</v>
       </c>
     </row>
     <row r="109">
@@ -1622,10 +1622,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>311.0535278320312</v>
+        <v>311.0534973144531</v>
       </c>
       <c r="C109" t="n">
-        <v>0.03908108737409588</v>
+        <v>0.03908119728696735</v>
       </c>
     </row>
     <row r="110">
@@ -1633,10 +1633,10 @@
         <v>41640</v>
       </c>
       <c r="B110" t="n">
-        <v>330.2799682617188</v>
+        <v>330.2799377441406</v>
       </c>
       <c r="C110" t="n">
-        <v>0.061810713299705</v>
+        <v>0.06181071936397786</v>
       </c>
     </row>
     <row r="111">
@@ -1647,7 +1647,7 @@
         <v>341.3231811523438</v>
       </c>
       <c r="C111" t="n">
-        <v>0.03343591483536223</v>
+        <v>0.03343601032393928</v>
       </c>
     </row>
     <row r="112">
@@ -1655,10 +1655,10 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>292.9515686035156</v>
+        <v>292.9515380859375</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.1417179237153491</v>
+        <v>-0.1417180131249756</v>
       </c>
     </row>
     <row r="113">
@@ -1666,10 +1666,10 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>283.8492126464844</v>
+        <v>283.8493347167969</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.03107119719625229</v>
+        <v>-0.03107067956909138</v>
       </c>
     </row>
     <row r="114">
@@ -1677,10 +1677,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>265.9103698730469</v>
+        <v>265.9102783203125</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.06319849403908384</v>
+        <v>-0.06319921945345619</v>
       </c>
     </row>
     <row r="115">
@@ -1688,10 +1688,10 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>294.5105590820312</v>
+        <v>294.5106506347656</v>
       </c>
       <c r="C115" t="n">
-        <v>0.107555749791326</v>
+        <v>0.107556475421388</v>
       </c>
     </row>
     <row r="116">
@@ -1699,10 +1699,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>304.651611328125</v>
+        <v>304.6516418457031</v>
       </c>
       <c r="C116" t="n">
-        <v>0.03443357778988543</v>
+        <v>0.03443335984311724</v>
       </c>
     </row>
     <row r="117">
@@ -1710,10 +1710,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>325.5624084472656</v>
+        <v>325.5625</v>
       </c>
       <c r="C117" t="n">
-        <v>0.06863839330433952</v>
+        <v>0.06863858677278234</v>
       </c>
     </row>
     <row r="118">
@@ -1721,10 +1721,10 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>339.0369873046875</v>
+        <v>339.0370788574219</v>
       </c>
       <c r="C118" t="n">
-        <v>0.04138862014717049</v>
+        <v>0.04138860850811099</v>
       </c>
     </row>
     <row r="119">
@@ -1732,10 +1732,10 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>369.3205871582031</v>
+        <v>369.3206176757812</v>
       </c>
       <c r="C119" t="n">
-        <v>0.08932240725198581</v>
+        <v>0.08932220310656569</v>
       </c>
     </row>
     <row r="120">
@@ -1743,10 +1743,10 @@
         <v>41944</v>
       </c>
       <c r="B120" t="n">
-        <v>397.4532165527344</v>
+        <v>397.4533081054688</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0761740080914588</v>
+        <v>0.07617416706040658</v>
       </c>
     </row>
     <row r="121">
@@ -1754,10 +1754,10 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>359.6437072753906</v>
+        <v>359.6436767578125</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.09512945851911891</v>
+        <v>-0.09512974373740279</v>
       </c>
     </row>
     <row r="122">
@@ -1768,7 +1768,7 @@
         <v>390.5203857421875</v>
       </c>
       <c r="C122" t="n">
-        <v>0.08585352069889995</v>
+        <v>0.08585361283904258</v>
       </c>
     </row>
     <row r="123">
@@ -1787,10 +1787,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>404.4589538574219</v>
+        <v>404.4590148925781</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.02092061738545026</v>
+        <v>-0.0209204696368035</v>
       </c>
     </row>
     <row r="125">
@@ -1801,7 +1801,7 @@
         <v>354.1192932128906</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.1244617288464747</v>
+        <v>-0.124461860970159</v>
       </c>
     </row>
     <row r="126">
@@ -1831,10 +1831,10 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>398.6998291015625</v>
+        <v>398.699951171875</v>
       </c>
       <c r="C128" t="n">
-        <v>0.09417379869778819</v>
+        <v>0.09417413370203898</v>
       </c>
     </row>
     <row r="129">
@@ -1842,10 +1842,10 @@
         <v>42217</v>
       </c>
       <c r="B129" t="n">
-        <v>405.1223449707031</v>
+        <v>405.1224060058594</v>
       </c>
       <c r="C129" t="n">
-        <v>0.01610864966662584</v>
+        <v>0.01610849164918937</v>
       </c>
     </row>
     <row r="130">
@@ -1853,10 +1853,10 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>430.1277770996094</v>
+        <v>430.1278686523438</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0617231620011347</v>
+        <v>0.0617232280312896</v>
       </c>
     </row>
     <row r="131">
@@ -1864,10 +1864,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>424.1837768554688</v>
+        <v>424.1835632324219</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.01381914993777322</v>
+        <v>-0.01381985649650253</v>
       </c>
     </row>
     <row r="132">
@@ -1875,10 +1875,10 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>406.4198608398438</v>
+        <v>406.419921875</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.0418778769601027</v>
+        <v>-0.04187725055175862</v>
       </c>
     </row>
     <row r="133">
@@ -1886,10 +1886,10 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>412.9575805664062</v>
+        <v>412.9576721191406</v>
       </c>
       <c r="C133" t="n">
-        <v>0.01608612264433296</v>
+        <v>0.01608619531734323</v>
       </c>
     </row>
     <row r="134">
@@ -1897,10 +1897,10 @@
         <v>42370</v>
       </c>
       <c r="B134" t="n">
-        <v>435.1858215332031</v>
+        <v>435.1856994628906</v>
       </c>
       <c r="C134" t="n">
-        <v>0.05382693529032445</v>
+        <v>0.05382640605678612</v>
       </c>
     </row>
     <row r="135">
@@ -1908,10 +1908,10 @@
         <v>42401</v>
       </c>
       <c r="B135" t="n">
-        <v>404.9815979003906</v>
+        <v>404.9816589355469</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.06940534856213831</v>
+        <v>-0.06940494727795932</v>
       </c>
     </row>
     <row r="136">
@@ -1919,10 +1919,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>455.1349487304688</v>
+        <v>455.1349792480469</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1238410611496819</v>
+        <v>0.1238409671300249</v>
       </c>
     </row>
     <row r="137">
@@ -1930,10 +1930,10 @@
         <v>42461</v>
       </c>
       <c r="B137" t="n">
-        <v>451.3244018554688</v>
+        <v>451.3243713378906</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.008372345137698023</v>
+        <v>-0.008372478679735784</v>
       </c>
     </row>
     <row r="138">
@@ -1941,10 +1941,10 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>466.4731750488281</v>
+        <v>466.4733581542969</v>
       </c>
       <c r="C138" t="n">
-        <v>0.03356515431268559</v>
+        <v>0.03356562990715317</v>
       </c>
     </row>
     <row r="139">
@@ -1952,10 +1952,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>442.482666015625</v>
+        <v>442.4827270507812</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.0514295576175241</v>
+        <v>-0.05142979911744539</v>
       </c>
     </row>
     <row r="140">
@@ -1963,10 +1963,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>405.8421630859375</v>
+        <v>405.8421020507812</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.08280664022304018</v>
+        <v>-0.08280690467674445</v>
       </c>
     </row>
     <row r="141">
@@ -1977,7 +1977,7 @@
         <v>391.4807434082031</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.0353867118402218</v>
+        <v>-0.03538656677069241</v>
       </c>
     </row>
     <row r="142">
@@ -1985,10 +1985,10 @@
         <v>42614</v>
       </c>
       <c r="B142" t="n">
-        <v>391.5563659667969</v>
+        <v>391.5563354492188</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0001931705706272879</v>
+        <v>0.0001930926164017688</v>
       </c>
     </row>
     <row r="143">
@@ -1996,10 +1996,10 @@
         <v>42644</v>
       </c>
       <c r="B143" t="n">
-        <v>381.0301818847656</v>
+        <v>381.0302124023438</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.02688293435362976</v>
+        <v>-0.02688278057051163</v>
       </c>
     </row>
     <row r="144">
@@ -2007,10 +2007,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>372.6455993652344</v>
+        <v>372.6456298828125</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.02200503508162244</v>
+        <v>-0.02200503331918902</v>
       </c>
     </row>
     <row r="145">
@@ -2018,10 +2018,10 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>386.0342102050781</v>
+        <v>386.0341491699219</v>
       </c>
       <c r="C145" t="n">
-        <v>0.03592853602095381</v>
+        <v>0.03592828739550691</v>
       </c>
     </row>
     <row r="146">
@@ -2029,10 +2029,10 @@
         <v>42736</v>
       </c>
       <c r="B146" t="n">
-        <v>354.7113952636719</v>
+        <v>354.7114562988281</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.08113999773431013</v>
+        <v>-0.08113969434684998</v>
       </c>
     </row>
     <row r="147">
@@ -2040,10 +2040,10 @@
         <v>42767</v>
       </c>
       <c r="B147" t="n">
-        <v>386.7217407226562</v>
+        <v>386.7218017578125</v>
       </c>
       <c r="C147" t="n">
-        <v>0.09024335244485093</v>
+        <v>0.0902433369166884</v>
       </c>
     </row>
     <row r="148">
@@ -2051,10 +2051,10 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>390.4843444824219</v>
+        <v>390.4842834472656</v>
       </c>
       <c r="C148" t="n">
-        <v>0.009729485993558384</v>
+        <v>0.009729168803907839</v>
       </c>
     </row>
     <row r="149">
@@ -2062,10 +2062,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>351.0252380371094</v>
+        <v>351.0252685546875</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.1010516990063063</v>
+        <v>-0.1010514803418637</v>
       </c>
     </row>
     <row r="150">
@@ -2073,10 +2073,10 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>373.2185974121094</v>
+        <v>373.2185668945312</v>
       </c>
       <c r="C150" t="n">
-        <v>0.06322439804927593</v>
+        <v>0.06322421867583072</v>
       </c>
     </row>
     <row r="151">
@@ -2084,10 +2084,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>362.8438415527344</v>
+        <v>362.8439331054688</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.02779806775791283</v>
+        <v>-0.02779774295632587</v>
       </c>
     </row>
     <row r="152">
@@ -2095,10 +2095,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>392.1840515136719</v>
+        <v>392.1840209960938</v>
       </c>
       <c r="C152" t="n">
-        <v>0.08086181051159791</v>
+        <v>0.08086145368206177</v>
       </c>
     </row>
     <row r="153">
@@ -2106,10 +2106,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>354.8543395996094</v>
+        <v>354.8544006347656</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.09518416613318392</v>
+        <v>-0.09518394009658016</v>
       </c>
     </row>
     <row r="154">
@@ -2117,10 +2117,10 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>349.0173950195312</v>
+        <v>349.017333984375</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.01644884655113443</v>
+        <v>-0.01644918772304715</v>
       </c>
     </row>
     <row r="155">
@@ -2128,10 +2128,10 @@
         <v>43009</v>
       </c>
       <c r="B155" t="n">
-        <v>362.5222778320312</v>
+        <v>362.5223083496094</v>
       </c>
       <c r="C155" t="n">
-        <v>0.03869401068604117</v>
+        <v>0.03869427976846262</v>
       </c>
     </row>
     <row r="156">
@@ -2139,10 +2139,10 @@
         <v>43040</v>
       </c>
       <c r="B156" t="n">
-        <v>383.8563842773438</v>
+        <v>383.8564147949219</v>
       </c>
       <c r="C156" t="n">
-        <v>0.05884909080042067</v>
+        <v>0.058849085846431</v>
       </c>
     </row>
     <row r="157">
@@ -2150,10 +2150,10 @@
         <v>43070</v>
       </c>
       <c r="B157" t="n">
-        <v>409.7915649414062</v>
+        <v>409.7916259765625</v>
       </c>
       <c r="C157" t="n">
-        <v>0.06756480216654115</v>
+        <v>0.06756487629755181</v>
       </c>
     </row>
     <row r="158">
@@ -2164,7 +2164,7 @@
         <v>452.341796875</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1038338403565671</v>
+        <v>0.1038336759494229</v>
       </c>
     </row>
     <row r="159">
@@ -2183,10 +2183,10 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>445.0862121582031</v>
+        <v>445.0862426757812</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.03479451358546348</v>
+        <v>-0.03479444740562454</v>
       </c>
     </row>
     <row r="161">
@@ -2194,10 +2194,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>471.7096557617188</v>
+        <v>471.7095947265625</v>
       </c>
       <c r="C161" t="n">
-        <v>0.05981637461744715</v>
+        <v>0.05981616481948815</v>
       </c>
     </row>
     <row r="162">
@@ -2208,7 +2208,7 @@
         <v>484.4118041992188</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02692789575610566</v>
+        <v>0.02692802863172505</v>
       </c>
     </row>
     <row r="163">
@@ -2216,10 +2216,10 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>526.6638793945312</v>
+        <v>526.6637573242188</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08722346323735741</v>
+        <v>0.08722321124037569</v>
       </c>
     </row>
     <row r="164">
@@ -2227,10 +2227,10 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>549.9915161132812</v>
+        <v>549.9913330078125</v>
       </c>
       <c r="C164" t="n">
-        <v>0.04429321552404186</v>
+        <v>0.04429310990016178</v>
       </c>
     </row>
     <row r="165">
@@ -2238,10 +2238,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>580.611328125</v>
+        <v>580.6115112304688</v>
       </c>
       <c r="C165" t="n">
-        <v>0.05567324424948406</v>
+        <v>0.05567392863301945</v>
       </c>
     </row>
     <row r="166">
@@ -2249,10 +2249,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>588.266357421875</v>
+        <v>588.2664184570312</v>
       </c>
       <c r="C166" t="n">
-        <v>0.01318442980021728</v>
+        <v>0.0131842153978996</v>
       </c>
     </row>
     <row r="167">
@@ -2260,10 +2260,10 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>559.1168212890625</v>
+        <v>559.1168823242188</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.04955159472413606</v>
+        <v>-0.04955158958294625</v>
       </c>
     </row>
     <row r="168">
@@ -2271,10 +2271,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>543.6807250976562</v>
+        <v>543.680908203125</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.02760799819225224</v>
+        <v>-0.02760777685146487</v>
       </c>
     </row>
     <row r="169">
@@ -2285,7 +2285,7 @@
         <v>536.7570190429688</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.01273487496442671</v>
+        <v>-0.01273520746395129</v>
       </c>
     </row>
     <row r="170">
@@ -2304,10 +2304,10 @@
         <v>43497</v>
       </c>
       <c r="B171" t="n">
-        <v>601.4224243164062</v>
+        <v>601.4223022460938</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.02034549016851372</v>
+        <v>-0.02034568900834299</v>
       </c>
     </row>
     <row r="172">
@@ -2315,10 +2315,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>609.244384765625</v>
+        <v>609.2442626953125</v>
       </c>
       <c r="C172" t="n">
-        <v>0.01300576788121832</v>
+        <v>0.01300577052099094</v>
       </c>
     </row>
     <row r="173">
@@ -2329,7 +2329,7 @@
         <v>615.3870849609375</v>
       </c>
       <c r="C173" t="n">
-        <v>0.01008248963620018</v>
+        <v>0.01008269201986245</v>
       </c>
     </row>
     <row r="174">
@@ -2337,10 +2337,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>604.2482299804688</v>
+        <v>604.248046875</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.01810056670457394</v>
+        <v>-0.01810086424976654</v>
       </c>
     </row>
     <row r="175">
@@ -2351,7 +2351,7 @@
         <v>608.0078735351562</v>
       </c>
       <c r="C175" t="n">
-        <v>0.006222018316559996</v>
+        <v>0.006222323232323301</v>
       </c>
     </row>
     <row r="176">
@@ -2359,10 +2359,10 @@
         <v>43647</v>
       </c>
       <c r="B176" t="n">
-        <v>659.2150268554688</v>
+        <v>659.215087890625</v>
       </c>
       <c r="C176" t="n">
-        <v>0.08422120098968033</v>
+        <v>0.08422130137515049</v>
       </c>
     </row>
     <row r="177">
@@ -2370,10 +2370,10 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>676.8655395507812</v>
+        <v>676.865478515625</v>
       </c>
       <c r="C177" t="n">
-        <v>0.02677504604151304</v>
+        <v>0.0267748583872347</v>
       </c>
     </row>
     <row r="178">
@@ -2381,10 +2381,10 @@
         <v>43709</v>
       </c>
       <c r="B178" t="n">
-        <v>669.182373046875</v>
+        <v>669.1824951171875</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.01135109716030958</v>
+        <v>-0.01135082766414142</v>
       </c>
     </row>
     <row r="179">
@@ -2392,10 +2392,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>576.6357421875</v>
+        <v>576.6355590820312</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.1382980702823926</v>
+        <v>-0.1382985010971475</v>
       </c>
     </row>
     <row r="180">
@@ -2403,10 +2403,10 @@
         <v>43770</v>
       </c>
       <c r="B180" t="n">
-        <v>585.6770629882812</v>
+        <v>585.677001953125</v>
       </c>
       <c r="C180" t="n">
-        <v>0.01567943181337061</v>
+        <v>0.01567964848627645</v>
       </c>
     </row>
     <row r="181">
@@ -2414,10 +2414,10 @@
         <v>43800</v>
       </c>
       <c r="B181" t="n">
-        <v>614.9462890625</v>
+        <v>614.9463500976562</v>
       </c>
       <c r="C181" t="n">
-        <v>0.04997502535762521</v>
+        <v>0.04997523899166834</v>
       </c>
     </row>
     <row r="182">
@@ -2425,10 +2425,10 @@
         <v>43831</v>
       </c>
       <c r="B182" t="n">
-        <v>652.6260375976562</v>
+        <v>652.6259765625</v>
       </c>
       <c r="C182" t="n">
-        <v>0.06127323508627058</v>
+        <v>0.06127303049909982</v>
       </c>
     </row>
     <row r="183">
@@ -2439,7 +2439,7 @@
         <v>615.4088134765625</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.057026876000982</v>
+        <v>-0.05702678781185988</v>
       </c>
     </row>
     <row r="184">
@@ -2447,10 +2447,10 @@
         <v>43891</v>
       </c>
       <c r="B184" t="n">
-        <v>539.544677734375</v>
+        <v>539.5444946289062</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.1232743731985514</v>
+        <v>-0.1232746707332385</v>
       </c>
     </row>
     <row r="185">
@@ -2458,10 +2458,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>601.7835693359375</v>
+        <v>601.7835083007812</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1153544723356599</v>
+        <v>0.1153547377305415</v>
       </c>
     </row>
     <row r="186">
@@ -2472,7 +2472,7 @@
         <v>589.0885620117188</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.02109563632358324</v>
+        <v>-0.02109553703940548</v>
       </c>
     </row>
     <row r="187">
@@ -2480,10 +2480,10 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>627.4091796875</v>
+        <v>627.4091186523438</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06505069041727363</v>
+        <v>0.06505058680779929</v>
       </c>
     </row>
     <row r="188">
@@ -2491,10 +2491,10 @@
         <v>44013</v>
       </c>
       <c r="B188" t="n">
-        <v>823.5302734375</v>
+        <v>823.5303955078125</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3125888177914196</v>
+        <v>0.3125891400442689</v>
       </c>
     </row>
     <row r="189">
@@ -2502,10 +2502,10 @@
         <v>44044</v>
       </c>
       <c r="B189" t="n">
-        <v>791.6463012695312</v>
+        <v>791.6464233398438</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.03871621140881898</v>
+        <v>-0.03871620566999012</v>
       </c>
     </row>
     <row r="190">
@@ -2516,7 +2516,7 @@
         <v>859.5492553710938</v>
       </c>
       <c r="C190" t="n">
-        <v>0.08577435907004083</v>
+        <v>0.08577419164578237</v>
       </c>
     </row>
     <row r="191">
@@ -2524,10 +2524,10 @@
         <v>44105</v>
       </c>
       <c r="B191" t="n">
-        <v>913.8916015625</v>
+        <v>913.8916625976562</v>
       </c>
       <c r="C191" t="n">
-        <v>0.06322191061400551</v>
+        <v>0.0632219816223345</v>
       </c>
     </row>
     <row r="192">
@@ -2538,7 +2538,7 @@
         <v>947.841552734375</v>
       </c>
       <c r="C192" t="n">
-        <v>0.03714877247348602</v>
+        <v>0.03714870320648211</v>
       </c>
     </row>
     <row r="193">
@@ -2546,10 +2546,10 @@
         <v>44166</v>
       </c>
       <c r="B193" t="n">
-        <v>1082.09033203125</v>
+        <v>1082.090454101562</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1416363092645476</v>
+        <v>0.1416364380522255</v>
       </c>
     </row>
     <row r="194">
@@ -2557,10 +2557,10 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>1067.657470703125</v>
+        <v>1067.657592773438</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.01333794499488072</v>
+        <v>-0.01333794349023099</v>
       </c>
     </row>
     <row r="195">
@@ -2568,10 +2568,10 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>1079.936401367188</v>
+        <v>1079.936279296875</v>
       </c>
       <c r="C195" t="n">
-        <v>0.01150081463484343</v>
+        <v>0.01150058465049764</v>
       </c>
     </row>
     <row r="196">
@@ -2582,7 +2582,7 @@
         <v>1178.813354492188</v>
       </c>
       <c r="C196" t="n">
-        <v>0.09155812601540503</v>
+        <v>0.09155824939938983</v>
       </c>
     </row>
     <row r="197">
@@ -2590,10 +2590,10 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>1167.008422851562</v>
+        <v>1167.008544921875</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01001425000458223</v>
+        <v>-0.01001414645102816</v>
       </c>
     </row>
     <row r="198">
@@ -2601,10 +2601,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>1213.917846679688</v>
+        <v>1213.918090820312</v>
       </c>
       <c r="C198" t="n">
-        <v>0.04019630270834096</v>
+        <v>0.0401964031048101</v>
       </c>
     </row>
     <row r="199">
@@ -2615,7 +2615,7 @@
         <v>1376.833374023438</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1342063861976799</v>
+        <v>0.1342061580885032</v>
       </c>
     </row>
     <row r="200">
@@ -2645,10 +2645,10 @@
         <v>44440</v>
       </c>
       <c r="B202" t="n">
-        <v>1459.053100585938</v>
+        <v>1459.05322265625</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.01831295599133109</v>
+        <v>-0.01831287385940317</v>
       </c>
     </row>
     <row r="203">
@@ -2656,10 +2656,10 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>1465.4375</v>
+        <v>1465.437622070312</v>
       </c>
       <c r="C203" t="n">
-        <v>0.004375714229659433</v>
+        <v>0.004375713863569386</v>
       </c>
     </row>
     <row r="204">
@@ -2667,10 +2667,10 @@
         <v>44501</v>
       </c>
       <c r="B204" t="n">
-        <v>1504.890869140625</v>
+        <v>1504.890747070312</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0269225873779162</v>
+        <v>0.02692241853615185</v>
       </c>
     </row>
     <row r="205">
@@ -2678,10 +2678,10 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>1658.749755859375</v>
+        <v>1658.749877929688</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1022392320093031</v>
+        <v>0.1022394025339743</v>
       </c>
     </row>
     <row r="206">
@@ -2689,10 +2689,10 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>1525.583740234375</v>
+        <v>1525.583984375</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.08028095567435878</v>
+        <v>-0.08028087617458879</v>
       </c>
     </row>
     <row r="207">
@@ -2703,7 +2703,7 @@
         <v>1507.48291015625</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.01186485513757785</v>
+        <v>-0.01186501326976475</v>
       </c>
     </row>
     <row r="208">
@@ -2711,10 +2711,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>1675.53271484375</v>
+        <v>1675.532592773438</v>
       </c>
       <c r="C208" t="n">
-        <v>0.111477087770157</v>
+        <v>0.1114770067939073</v>
       </c>
     </row>
     <row r="209">
@@ -2722,10 +2722,10 @@
         <v>44652</v>
       </c>
       <c r="B209" t="n">
-        <v>1377.392822265625</v>
+        <v>1377.392578125</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.177937374744681</v>
+        <v>-0.1779374605628764</v>
       </c>
     </row>
     <row r="210">
@@ -2736,7 +2736,7 @@
         <v>1335.1923828125</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.03063791154633067</v>
+        <v>-0.0306377397284554</v>
       </c>
     </row>
     <row r="211">
@@ -2755,10 +2755,10 @@
         <v>44743</v>
       </c>
       <c r="B212" t="n">
-        <v>1376.129150390625</v>
+        <v>1376.129028320312</v>
       </c>
       <c r="C212" t="n">
-        <v>0.06005875940989336</v>
+        <v>0.06005866537678317</v>
       </c>
     </row>
     <row r="213">
@@ -2766,10 +2766,10 @@
         <v>44774</v>
       </c>
       <c r="B213" t="n">
-        <v>1325.735229492188</v>
+        <v>1325.735473632812</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.03662005189275497</v>
+        <v>-0.03661978902444185</v>
       </c>
     </row>
     <row r="214">
@@ -2777,10 +2777,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>1255.1396484375</v>
+        <v>1255.139526367188</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.05325013583725058</v>
+        <v>-0.05325040226326316</v>
       </c>
     </row>
     <row r="215">
@@ -2788,10 +2788,10 @@
         <v>44835</v>
       </c>
       <c r="B215" t="n">
-        <v>1380.350952148438</v>
+        <v>1380.35107421875</v>
       </c>
       <c r="C215" t="n">
-        <v>0.09975886258298883</v>
+        <v>0.09975906679791091</v>
       </c>
     </row>
     <row r="216">
@@ -2799,10 +2799,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>1467.697387695312</v>
+        <v>1467.697265625</v>
       </c>
       <c r="C216" t="n">
-        <v>0.06327842597632527</v>
+        <v>0.06327824351184441</v>
       </c>
     </row>
     <row r="217">
@@ -2810,10 +2810,10 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>1353.913696289062</v>
+        <v>1353.913452148438</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.07752530757373743</v>
+        <v>-0.07752539719293483</v>
       </c>
     </row>
     <row r="218">
@@ -2824,7 +2824,7 @@
         <v>1376.849975585938</v>
       </c>
       <c r="C218" t="n">
-        <v>0.01694072477421638</v>
+        <v>0.01694090815118465</v>
       </c>
     </row>
     <row r="219">
@@ -2832,10 +2832,10 @@
         <v>44958</v>
       </c>
       <c r="B219" t="n">
-        <v>1335.376098632812</v>
+        <v>1335.376342773438</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.03012229196247418</v>
+        <v>-0.03012211464422643</v>
       </c>
     </row>
     <row r="220">
@@ -2843,10 +2843,10 @@
         <v>44986</v>
       </c>
       <c r="B220" t="n">
-        <v>1281.873046875</v>
+        <v>1281.873168945312</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.04006590488821093</v>
+        <v>-0.04006598897581526</v>
       </c>
     </row>
     <row r="221">
@@ -2857,7 +2857,7 @@
         <v>1124.595703125</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1226933853811942</v>
+        <v>-0.1226934689254131</v>
       </c>
     </row>
     <row r="222">
@@ -2865,10 +2865,10 @@
         <v>45047</v>
       </c>
       <c r="B222" t="n">
-        <v>1183.440307617188</v>
+        <v>1183.440063476562</v>
       </c>
       <c r="C222" t="n">
-        <v>0.05232511944396689</v>
+        <v>0.05232490235206044</v>
       </c>
     </row>
     <row r="223">
@@ -2879,7 +2879,7 @@
         <v>1214.99462890625</v>
       </c>
       <c r="C223" t="n">
-        <v>0.02666321324866483</v>
+        <v>0.02666342504663088</v>
       </c>
     </row>
     <row r="224">
@@ -2898,10 +2898,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>1305.926025390625</v>
+        <v>1305.925903320312</v>
       </c>
       <c r="C225" t="n">
-        <v>0.05882578832106744</v>
+        <v>0.05882568934823729</v>
       </c>
     </row>
     <row r="226">
@@ -2909,7 +2909,7 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>1305.926025390625</v>
+        <v>1305.925903320312</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>45200</v>
       </c>
       <c r="B227" t="n">
-        <v>1261.039794921875</v>
+        <v>1261.039672851562</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.03437118917614324</v>
+        <v>-0.03437119238896091</v>
       </c>
     </row>
     <row r="228">
@@ -2931,10 +2931,10 @@
         <v>45231</v>
       </c>
       <c r="B228" t="n">
-        <v>1340.983642578125</v>
+        <v>1340.983520507812</v>
       </c>
       <c r="C228" t="n">
-        <v>0.06339518227591134</v>
+        <v>0.06339518841264891</v>
       </c>
     </row>
     <row r="229">
@@ -2942,10 +2942,10 @@
         <v>45261</v>
       </c>
       <c r="B229" t="n">
-        <v>1421.848999023438</v>
+        <v>1421.84912109375</v>
       </c>
       <c r="C229" t="n">
-        <v>0.06030301480027278</v>
+        <v>0.06030320235055142</v>
       </c>
     </row>
     <row r="230">
@@ -2953,10 +2953,10 @@
         <v>45292</v>
       </c>
       <c r="B230" t="n">
-        <v>1530.591064453125</v>
+        <v>1530.591186523438</v>
       </c>
       <c r="C230" t="n">
-        <v>0.07647933465816292</v>
+        <v>0.07647932809216651</v>
       </c>
     </row>
     <row r="231">
@@ -2964,10 +2964,10 @@
         <v>45323</v>
       </c>
       <c r="B231" t="n">
-        <v>1542.5712890625</v>
+        <v>1542.571044921875</v>
       </c>
       <c r="C231" t="n">
-        <v>0.007827188389901929</v>
+        <v>0.007826948504550346</v>
       </c>
     </row>
     <row r="232">
@@ -2975,10 +2975,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>1380.517700195312</v>
+        <v>1380.517944335938</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.1050541975053068</v>
+        <v>-0.1050538975948073</v>
       </c>
     </row>
     <row r="233">
@@ -2986,10 +2986,10 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>1309.098266601562</v>
+        <v>1309.098388671875</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.05173380506721914</v>
+        <v>-0.05173388434180548</v>
       </c>
     </row>
     <row r="234">
@@ -3000,7 +3000,7 @@
         <v>1322.459838867188</v>
       </c>
       <c r="C234" t="n">
-        <v>0.01020669922687456</v>
+        <v>0.01020660502750159</v>
       </c>
     </row>
     <row r="235">
@@ -3019,10 +3019,10 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>1756.119995117188</v>
+        <v>1756.1201171875</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1924365287972873</v>
+        <v>0.1924366116851881</v>
       </c>
     </row>
     <row r="237">
@@ -3033,7 +3033,7 @@
         <v>1827.041748046875</v>
       </c>
       <c r="C237" t="n">
-        <v>0.04038548227164562</v>
+        <v>0.04038540995302697</v>
       </c>
     </row>
     <row r="238">
@@ -3052,10 +3052,10 @@
         <v>45566</v>
       </c>
       <c r="B239" t="n">
-        <v>1670.589721679688</v>
+        <v>1670.589599609375</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.0524320431596984</v>
+        <v>-0.0524321123986714</v>
       </c>
     </row>
     <row r="240">
@@ -3066,7 +3066,7 @@
         <v>1766.228393554688</v>
       </c>
       <c r="C240" t="n">
-        <v>0.05724844983413435</v>
+        <v>0.05724852708748762</v>
       </c>
     </row>
     <row r="241">
@@ -3074,10 +3074,10 @@
         <v>45627</v>
       </c>
       <c r="B241" t="n">
-        <v>1787.2861328125</v>
+        <v>1787.286010742188</v>
       </c>
       <c r="C241" t="n">
-        <v>0.0119224327582188</v>
+        <v>0.01192236364466992</v>
       </c>
     </row>
     <row r="242">
@@ -3088,7 +3088,7 @@
         <v>1787.095947265625</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.0001064102402986711</v>
+        <v>-0.0001063419483060546</v>
       </c>
     </row>
     <row r="243">
@@ -3096,10 +3096,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>1604.469482421875</v>
+        <v>1604.469604492188</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1021917514407553</v>
+        <v>-0.1021916831342312</v>
       </c>
     </row>
     <row r="244">
@@ -3110,7 +3110,7 @@
         <v>1493.19189453125</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.06935475502011823</v>
+        <v>-0.06935482582492225</v>
       </c>
     </row>
     <row r="245">
@@ -3268,10 +3268,10 @@
         <v>38384</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92464351654053</v>
+        <v>11.92464828491211</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01740096601046359</v>
+        <v>-0.01740057309328291</v>
       </c>
     </row>
     <row r="4">
@@ -3282,7 +3282,7 @@
         <v>13.33685970306396</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1184283777175033</v>
+        <v>0.1184279304856886</v>
       </c>
     </row>
     <row r="5">
@@ -3290,10 +3290,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>12.57795906066895</v>
+        <v>12.57796287536621</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.056902498735941</v>
+        <v>-0.05690221270929374</v>
       </c>
     </row>
     <row r="6">
@@ -3301,10 +3301,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>11.50230026245117</v>
+        <v>11.50230121612549</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.08551934324395594</v>
+        <v>-0.08551954477043278</v>
       </c>
     </row>
     <row r="7">
@@ -3312,10 +3312,10 @@
         <v>38504</v>
       </c>
       <c r="B7" t="n">
-        <v>11.08325576782227</v>
+        <v>11.08325672149658</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.03643136460251006</v>
+        <v>-0.03643136158192695</v>
       </c>
     </row>
     <row r="8">
@@ -3323,10 +3323,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>11.69411659240723</v>
+        <v>11.69411849975586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05511564808947722</v>
+        <v>0.05511572939337195</v>
       </c>
     </row>
     <row r="9">
@@ -3334,10 +3334,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64410018920898</v>
+        <v>12.6440954208374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08123602918569883</v>
+        <v>0.08123544507449409</v>
       </c>
     </row>
     <row r="10">
@@ -3345,10 +3345,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>11.8580207824707</v>
+        <v>11.85802459716797</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06216965976030109</v>
+        <v>-0.06216900438555639</v>
       </c>
     </row>
     <row r="11">
@@ -3356,10 +3356,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>10.64044284820557</v>
+        <v>10.64044094085693</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1026796930618505</v>
+        <v>-0.1026801425763468</v>
       </c>
     </row>
     <row r="12">
@@ -3367,10 +3367,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>11.64394187927246</v>
+        <v>11.64394474029541</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09430989343043428</v>
+        <v>0.09431035847257463</v>
       </c>
     </row>
     <row r="13">
@@ -3378,10 +3378,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>12.4333610534668</v>
+        <v>12.43336296081543</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06779655741837676</v>
+        <v>0.06779645885712027</v>
       </c>
     </row>
     <row r="14">
@@ -3389,10 +3389,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>13.6877384185791</v>
+        <v>13.68773651123047</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1008880349985932</v>
+        <v>0.1008877127104131</v>
       </c>
     </row>
     <row r="15">
@@ -3403,7 +3403,7 @@
         <v>13.29971504211426</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.02834824604320019</v>
+        <v>-0.0283481106461867</v>
       </c>
     </row>
     <row r="16">
@@ -3411,10 +3411,10 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>14.08244800567627</v>
+        <v>14.0824499130249</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05885336348060433</v>
+        <v>0.05885350689334867</v>
       </c>
     </row>
     <row r="17">
@@ -3422,10 +3422,10 @@
         <v>38808</v>
       </c>
       <c r="B17" t="n">
-        <v>17.95930099487305</v>
+        <v>17.95929908752441</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752968083130234</v>
+        <v>0.275296500143331</v>
       </c>
     </row>
     <row r="18">
@@ -3433,10 +3433,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>15.05584049224854</v>
+        <v>15.05584144592285</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1616689036757822</v>
+        <v>-0.1616687615397238</v>
       </c>
     </row>
     <row r="19">
@@ -3444,10 +3444,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>13.09232807159424</v>
+        <v>13.09233093261719</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1304153309584547</v>
+        <v>-0.1304151960126669</v>
       </c>
     </row>
     <row r="20">
@@ -3455,10 +3455,10 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>13.90186405181885</v>
+        <v>13.90186500549316</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06183285171267738</v>
+        <v>0.06183269251613299</v>
       </c>
     </row>
     <row r="21">
@@ -3466,10 +3466,10 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>14.79318714141846</v>
+        <v>14.79318237304688</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06411536512493754</v>
+        <v>0.06411494912384175</v>
       </c>
     </row>
     <row r="22">
@@ -3477,10 +3477,10 @@
         <v>38961</v>
       </c>
       <c r="B22" t="n">
-        <v>14.84402179718018</v>
+        <v>14.84401988983154</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003436355889758991</v>
+        <v>0.003436550398871141</v>
       </c>
     </row>
     <row r="23">
@@ -3491,7 +3491,7 @@
         <v>16.54193496704102</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1143836349110847</v>
+        <v>0.1143837781012795</v>
       </c>
     </row>
     <row r="24">
@@ -3499,10 +3499,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>15.37610244750977</v>
+        <v>15.37609958648682</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07047739710342915</v>
+        <v>-0.07047757005919009</v>
       </c>
     </row>
     <row r="25">
@@ -3510,10 +3510,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>15.40998840332031</v>
+        <v>15.40999794006348</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00220380658403041</v>
+        <v>0.002204613295198277</v>
       </c>
     </row>
     <row r="26">
@@ -3521,10 +3521,10 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>16.59954643249512</v>
+        <v>16.59954452514648</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0771939600498659</v>
+        <v>0.07719316963634237</v>
       </c>
     </row>
     <row r="27">
@@ -3532,10 +3532,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>16.04713439941406</v>
+        <v>16.04713249206543</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0332787426046568</v>
+        <v>-0.03327874642850659</v>
       </c>
     </row>
     <row r="28">
@@ -3543,10 +3543,10 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>16.52837562561035</v>
+        <v>16.52837944030762</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02998923136169784</v>
+        <v>0.02998959150366232</v>
       </c>
     </row>
     <row r="29">
@@ -3554,10 +3554,10 @@
         <v>39173</v>
       </c>
       <c r="B29" t="n">
-        <v>20.55117607116699</v>
+        <v>20.55117797851562</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2433875255910447</v>
+        <v>0.2433873540195746</v>
       </c>
     </row>
     <row r="30">
@@ -3565,10 +3565,10 @@
         <v>39203</v>
       </c>
       <c r="B30" t="n">
-        <v>24.74003791809082</v>
+        <v>24.74004173278809</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2038258945579636</v>
+        <v>0.2038259684506423</v>
       </c>
     </row>
     <row r="31">
@@ -3576,10 +3576,10 @@
         <v>39234</v>
       </c>
       <c r="B31" t="n">
-        <v>22.88962554931641</v>
+        <v>22.88961601257324</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07479424141954627</v>
+        <v>-0.07479476955620756</v>
       </c>
     </row>
     <row r="32">
@@ -3587,10 +3587,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>18.21876525878906</v>
+        <v>18.21877288818359</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2040601442109147</v>
+        <v>-0.2040594792775885</v>
       </c>
     </row>
     <row r="33">
@@ -3598,10 +3598,10 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>14.42918014526367</v>
+        <v>14.42918395996094</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.208004497543939</v>
+        <v>-0.2080046198215975</v>
       </c>
     </row>
     <row r="34">
@@ -3609,10 +3609,10 @@
         <v>39326</v>
       </c>
       <c r="B34" t="n">
-        <v>13.58362579345703</v>
+        <v>13.58362865447998</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.05860030461149868</v>
+        <v>-0.05860035521255125</v>
       </c>
     </row>
     <row r="35">
@@ -3620,10 +3620,10 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>12.34097194671631</v>
+        <v>12.34097003936768</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09148174910260598</v>
+        <v>-0.09148208087258536</v>
       </c>
     </row>
     <row r="36">
@@ -3634,7 +3634,7 @@
         <v>11.43380165100098</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.07350882083130517</v>
+        <v>-0.07350867763821101</v>
       </c>
     </row>
     <row r="37">
@@ -3642,10 +3642,10 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>13.05301952362061</v>
+        <v>13.05301761627197</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1416167537310631</v>
+        <v>0.1416165869144006</v>
       </c>
     </row>
     <row r="38">
@@ -3656,7 +3656,7 @@
         <v>9.937821388244629</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2386572800062657</v>
+        <v>-0.2386571687564354</v>
       </c>
     </row>
     <row r="39">
@@ -3664,10 +3664,10 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>8.74309253692627</v>
+        <v>8.743090629577637</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1202203988825553</v>
+        <v>-0.1202205908108018</v>
       </c>
     </row>
     <row r="40">
@@ -3678,7 +3678,7 @@
         <v>7.60655689239502</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1299924071180896</v>
+        <v>-0.1299922173216134</v>
       </c>
     </row>
     <row r="41">
@@ -3686,10 +3686,10 @@
         <v>39539</v>
       </c>
       <c r="B41" t="n">
-        <v>10.82103157043457</v>
+        <v>10.82103061676025</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4225926031334044</v>
+        <v>0.4225924777581092</v>
       </c>
     </row>
     <row r="42">
@@ -3697,10 +3697,10 @@
         <v>39569</v>
       </c>
       <c r="B42" t="n">
-        <v>9.670804977416992</v>
+        <v>9.670807838439941</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1062954659665026</v>
+        <v>-0.1062951228082452</v>
       </c>
     </row>
     <row r="43">
@@ -3708,10 +3708,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>8.078969955444336</v>
+        <v>8.078973770141602</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1646021221283923</v>
+        <v>-0.1646019748185926</v>
       </c>
     </row>
     <row r="44">
@@ -3719,10 +3719,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>9.91724681854248</v>
+        <v>9.917245864868164</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2275385195434907</v>
+        <v>0.227537821885309</v>
       </c>
     </row>
     <row r="45">
@@ -3730,10 +3730,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>9.730195045471191</v>
+        <v>9.730194091796875</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.01886126023621337</v>
+        <v>-0.01886126204997296</v>
       </c>
     </row>
     <row r="46">
@@ -3741,10 +3741,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>7.729098796844482</v>
+        <v>7.729100704193115</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.20565839012221</v>
+        <v>-0.2056581162436214</v>
       </c>
     </row>
     <row r="47">
@@ -3755,7 +3755,7 @@
         <v>7.076185703277588</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.08447467301536571</v>
+        <v>-0.08447489894410543</v>
       </c>
     </row>
     <row r="48">
@@ -3763,10 +3763,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>6.052697658538818</v>
+        <v>6.052696228027344</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1446383811358575</v>
+        <v>-0.1446385832944121</v>
       </c>
     </row>
     <row r="49">
@@ -3774,10 +3774,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>5.435073852539062</v>
+        <v>5.435075759887695</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1020410800014843</v>
+        <v>-0.1020405526515147</v>
       </c>
     </row>
     <row r="50">
@@ -3788,7 +3788,7 @@
         <v>5.082147598266602</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.06493495099566804</v>
+        <v>-0.0649352791410559</v>
       </c>
     </row>
     <row r="51">
@@ -3796,10 +3796,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>4.813923358917236</v>
+        <v>4.813922882080078</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.05277773503486005</v>
+        <v>-0.05277782886077698</v>
       </c>
     </row>
     <row r="52">
@@ -3810,7 +3810,7 @@
         <v>5.463307857513428</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1348971411007784</v>
+        <v>0.1348972535166066</v>
       </c>
     </row>
     <row r="53">
@@ -3818,10 +3818,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>6.860897541046143</v>
+        <v>6.860898971557617</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2558138256131175</v>
+        <v>0.2558140874529244</v>
       </c>
     </row>
     <row r="54">
@@ -3829,10 +3829,10 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>8.459656715393066</v>
+        <v>8.459659576416016</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2330247849909075</v>
+        <v>0.2330249449068094</v>
       </c>
     </row>
     <row r="55">
@@ -3843,7 +3843,7 @@
         <v>8.685532569885254</v>
       </c>
       <c r="C55" t="n">
-        <v>0.02670035701108153</v>
+        <v>0.02670000978513731</v>
       </c>
     </row>
     <row r="56">
@@ -3862,10 +3862,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>15.62240600585938</v>
+        <v>15.62240219116211</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2232759727943174</v>
+        <v>0.2232756740933679</v>
       </c>
     </row>
     <row r="58">
@@ -3873,10 +3873,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>17.03528022766113</v>
+        <v>17.0352840423584</v>
       </c>
       <c r="C58" t="n">
-        <v>0.09043896447652444</v>
+        <v>0.0904394749224664</v>
       </c>
     </row>
     <row r="59">
@@ -3884,10 +3884,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>17.28483009338379</v>
+        <v>17.28483200073242</v>
       </c>
       <c r="C59" t="n">
-        <v>0.01464900268076885</v>
+        <v>0.01464888743583725</v>
       </c>
     </row>
     <row r="60">
@@ -3895,10 +3895,10 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>21.82072448730469</v>
+        <v>21.82071685791016</v>
       </c>
       <c r="C60" t="n">
-        <v>0.262420536934125</v>
+        <v>0.2624199562359375</v>
       </c>
     </row>
     <row r="61">
@@ -3906,10 +3906,10 @@
         <v>40148</v>
       </c>
       <c r="B61" t="n">
-        <v>23.82444000244141</v>
+        <v>23.82443809509277</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09182625976981118</v>
+        <v>0.09182655410590934</v>
       </c>
     </row>
     <row r="62">
@@ -3917,10 +3917,10 @@
         <v>40179</v>
       </c>
       <c r="B62" t="n">
-        <v>22.54367446899414</v>
+        <v>22.54366874694824</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.05375847379061249</v>
+        <v>-0.05375863821142279</v>
       </c>
     </row>
     <row r="63">
@@ -3928,10 +3928,10 @@
         <v>40210</v>
       </c>
       <c r="B63" t="n">
-        <v>20.92528343200684</v>
+        <v>20.92528915405273</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.07178914152673688</v>
+        <v>-0.07178865210723917</v>
       </c>
     </row>
     <row r="64">
@@ -3939,10 +3939,10 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>19.99315643310547</v>
+        <v>19.9931526184082</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.04454548976266703</v>
+        <v>-0.04454593333368573</v>
       </c>
     </row>
     <row r="65">
@@ -3953,7 +3953,7 @@
         <v>23.5455379486084</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1776798739803163</v>
+        <v>0.177680098681857</v>
       </c>
     </row>
     <row r="66">
@@ -3961,10 +3961,10 @@
         <v>40299</v>
       </c>
       <c r="B66" t="n">
-        <v>21.75833892822266</v>
+        <v>21.75833511352539</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0759039366306502</v>
+        <v>-0.07590409864424597</v>
       </c>
     </row>
     <row r="67">
@@ -3975,7 +3975,7 @@
         <v>24.23545837402344</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1138469004445795</v>
+        <v>0.1138470957255466</v>
       </c>
     </row>
     <row r="68">
@@ -4005,10 +4005,10 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>24.8782958984375</v>
+        <v>24.87829208374023</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0261202919953496</v>
+        <v>-0.02612044132455904</v>
       </c>
     </row>
     <row r="71">
@@ -4016,10 +4016,10 @@
         <v>40452</v>
       </c>
       <c r="B71" t="n">
-        <v>23.16464042663574</v>
+        <v>23.16463279724121</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.06888154553662118</v>
+        <v>-0.06888170943290051</v>
       </c>
     </row>
     <row r="72">
@@ -4027,10 +4027,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>24.43850135803223</v>
+        <v>24.43850326538086</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05499161255841223</v>
+        <v>0.05499204236431332</v>
       </c>
     </row>
     <row r="73">
@@ -4038,10 +4038,10 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>25.43181228637695</v>
+        <v>25.43181610107422</v>
       </c>
       <c r="C73" t="n">
-        <v>0.04064532901557216</v>
+        <v>0.04064540389019933</v>
       </c>
     </row>
     <row r="74">
@@ -4049,10 +4049,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>24.33235168457031</v>
+        <v>24.33234786987305</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0432317048201708</v>
+        <v>-0.04323199832963287</v>
       </c>
     </row>
     <row r="75">
@@ -4060,10 +4060,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>23.96838569641113</v>
+        <v>23.96838760375977</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.01495810979873269</v>
+        <v>-0.01495787698169138</v>
       </c>
     </row>
     <row r="76">
@@ -4071,10 +4071,10 @@
         <v>40603</v>
       </c>
       <c r="B76" t="n">
-        <v>23.73332977294922</v>
+        <v>23.73332595825195</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.009806915093873436</v>
+        <v>-0.009807153046496153</v>
       </c>
     </row>
     <row r="77">
@@ -4082,10 +4082,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>26.64502716064453</v>
+        <v>26.64502334594727</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1226838970995974</v>
+        <v>0.1226839168187859</v>
       </c>
     </row>
     <row r="78">
@@ -4093,7 +4093,7 @@
         <v>40664</v>
       </c>
       <c r="B78" t="n">
-        <v>26.64502716064453</v>
+        <v>26.64502334594727</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -4104,10 +4104,10 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>24.53707885742188</v>
+        <v>24.53707504272461</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.07911225950394818</v>
+        <v>-0.07911227083024031</v>
       </c>
     </row>
     <row r="80">
@@ -4115,10 +4115,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>22.57290649414062</v>
+        <v>22.57291412353516</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.08004915233367871</v>
+        <v>-0.08004869837865369</v>
       </c>
     </row>
     <row r="81">
@@ -4126,10 +4126,10 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>19.41130828857422</v>
+        <v>19.41130447387695</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1400616356775801</v>
+        <v>-0.1400620953216589</v>
       </c>
     </row>
     <row r="82">
@@ -4140,7 +4140,7 @@
         <v>18.56666374206543</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.04351301488555304</v>
+        <v>-0.04351282691733627</v>
       </c>
     </row>
     <row r="83">
@@ -4148,10 +4148,10 @@
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>20.52716827392578</v>
+        <v>20.52716445922852</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1055927203237137</v>
+        <v>0.1055925148642236</v>
       </c>
     </row>
     <row r="84">
@@ -4159,10 +4159,10 @@
         <v>40848</v>
       </c>
       <c r="B84" t="n">
-        <v>19.51205062866211</v>
+        <v>19.51205253601074</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.04945239556267023</v>
+        <v>-0.04945212599791904</v>
       </c>
     </row>
     <row r="85">
@@ -4170,10 +4170,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>22.08472061157227</v>
+        <v>22.084716796875</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1318503130127722</v>
+        <v>0.1318500068671014</v>
       </c>
     </row>
     <row r="86">
@@ -4184,7 +4184,7 @@
         <v>26.91236114501953</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2185964051054199</v>
+        <v>0.2185966155938048</v>
       </c>
     </row>
     <row r="87">
@@ -4214,10 +4214,10 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>34.39056396484375</v>
+        <v>34.39056015014648</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2117257267726012</v>
+        <v>0.2117255923646042</v>
       </c>
     </row>
     <row r="90">
@@ -4225,10 +4225,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>34.75331497192383</v>
+        <v>34.75331115722656</v>
       </c>
       <c r="C90" t="n">
-        <v>0.01054798076155139</v>
+        <v>0.01054798193156303</v>
       </c>
     </row>
     <row r="91">
@@ -4236,10 +4236,10 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>41.03051376342773</v>
+        <v>41.03050994873047</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1806215837704999</v>
+        <v>0.1806216035964283</v>
       </c>
     </row>
     <row r="92">
@@ -4250,7 +4250,7 @@
         <v>43.07244873046875</v>
       </c>
       <c r="C92" t="n">
-        <v>0.04976625393516465</v>
+        <v>0.04976635153425524</v>
       </c>
     </row>
     <row r="93">
@@ -4258,10 +4258,10 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>39.47639846801758</v>
+        <v>39.47639465332031</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.08348841007284979</v>
+        <v>-0.08348849863752106</v>
       </c>
     </row>
     <row r="94">
@@ -4272,7 +4272,7 @@
         <v>44.53007888793945</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1280177679839813</v>
+        <v>0.1280178769870028</v>
       </c>
     </row>
     <row r="95">
@@ -4280,10 +4280,10 @@
         <v>41183</v>
       </c>
       <c r="B95" t="n">
-        <v>36.88147354125977</v>
+        <v>36.88148498535156</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1717626722810779</v>
+        <v>-0.1717624152841876</v>
       </c>
     </row>
     <row r="96">
@@ -4291,10 +4291,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>41.75096130371094</v>
+        <v>41.75095748901367</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1320307269448877</v>
+        <v>0.1320302722516771</v>
       </c>
     </row>
     <row r="97">
@@ -4302,10 +4302,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>45.01061630249023</v>
+        <v>45.01062393188477</v>
       </c>
       <c r="C97" t="n">
-        <v>0.07807377116582881</v>
+        <v>0.07807405240296195</v>
       </c>
     </row>
     <row r="98">
@@ -4313,10 +4313,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>41.19828033447266</v>
+        <v>41.19827651977539</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.08469859515801959</v>
+        <v>-0.08469883505455633</v>
       </c>
     </row>
     <row r="99">
@@ -4324,10 +4324,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>36.5611457824707</v>
+        <v>36.56113815307617</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.1125565075618419</v>
+        <v>-0.1125566105774684</v>
       </c>
     </row>
     <row r="100">
@@ -4335,10 +4335,10 @@
         <v>41334</v>
       </c>
       <c r="B100" t="n">
-        <v>39.39540100097656</v>
+        <v>39.39540481567383</v>
       </c>
       <c r="C100" t="n">
-        <v>0.07752096270092146</v>
+        <v>0.07752129189006629</v>
       </c>
     </row>
     <row r="101">
@@ -4349,7 +4349,7 @@
         <v>39.82582092285156</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01092563880398956</v>
+        <v>0.01092554091502795</v>
       </c>
     </row>
     <row r="102">
@@ -4357,10 +4357,10 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>40.36992263793945</v>
+        <v>40.36993408203125</v>
       </c>
       <c r="C102" t="n">
-        <v>0.01366203388856424</v>
+        <v>0.01366232124213362</v>
       </c>
     </row>
     <row r="103">
@@ -4368,10 +4368,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>40.66228485107422</v>
+        <v>40.66230010986328</v>
       </c>
       <c r="C103" t="n">
-        <v>0.007242080094055137</v>
+        <v>0.007242172534588365</v>
       </c>
     </row>
     <row r="104">
@@ -4379,10 +4379,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>36.62065124511719</v>
+        <v>36.62064361572266</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.09939514271663608</v>
+        <v>-0.09939566830259705</v>
       </c>
     </row>
     <row r="105">
@@ -4390,10 +4390,10 @@
         <v>41487</v>
       </c>
       <c r="B105" t="n">
-        <v>37.59609603881836</v>
+        <v>37.59608840942383</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0266364676906512</v>
+        <v>0.02663647323998353</v>
       </c>
     </row>
     <row r="106">
@@ -4401,10 +4401,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>38.14994812011719</v>
+        <v>38.14995193481445</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01473163811282352</v>
+        <v>0.01473194549813317</v>
       </c>
     </row>
     <row r="107">
@@ -4415,7 +4415,7 @@
         <v>44.48210525512695</v>
       </c>
       <c r="C107" t="n">
-        <v>0.165980753501227</v>
+        <v>0.1659806369122572</v>
       </c>
     </row>
     <row r="108">
@@ -4423,10 +4423,10 @@
         <v>41579</v>
       </c>
       <c r="B108" t="n">
-        <v>53.40994262695312</v>
+        <v>53.40993499755859</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2007062687483112</v>
+        <v>0.2007060972322714</v>
       </c>
     </row>
     <row r="109">
@@ -4434,10 +4434,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>58.94850158691406</v>
+        <v>58.9484977722168</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1036990247049232</v>
+        <v>0.1036991109409022</v>
       </c>
     </row>
     <row r="110">
@@ -4445,10 +4445,10 @@
         <v>41640</v>
       </c>
       <c r="B110" t="n">
-        <v>64.00011444091797</v>
+        <v>64.0001220703125</v>
       </c>
       <c r="C110" t="n">
-        <v>0.08569535642149906</v>
+        <v>0.08569555610417279</v>
       </c>
     </row>
     <row r="111">
@@ -4456,10 +4456,10 @@
         <v>41671</v>
       </c>
       <c r="B111" t="n">
-        <v>66.16522979736328</v>
+        <v>66.16524505615234</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0338298669519419</v>
+        <v>0.03382998212817734</v>
       </c>
     </row>
     <row r="112">
@@ -4467,10 +4467,10 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>62.7127685546875</v>
+        <v>62.71277618408203</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.0521793886796621</v>
+        <v>-0.05217949195442884</v>
       </c>
     </row>
     <row r="113">
@@ -4481,7 +4481,7 @@
         <v>60.44734954833984</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.03612372820651566</v>
+        <v>-0.03612384546798619</v>
       </c>
     </row>
     <row r="114">
@@ -4489,10 +4489,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>61.08266448974609</v>
+        <v>61.08267974853516</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0105102199873659</v>
+        <v>0.01051047241843484</v>
       </c>
     </row>
     <row r="115">
@@ -4500,10 +4500,10 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>73.29585266113281</v>
+        <v>73.29586791992188</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1999452426217743</v>
+        <v>0.1999451926743538</v>
       </c>
     </row>
     <row r="116">
@@ -4511,10 +4511,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>71.43006896972656</v>
+        <v>71.43007659912109</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.02545551519855138</v>
+        <v>-0.02545561398958018</v>
       </c>
     </row>
     <row r="117">
@@ -4522,10 +4522,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>75.32069396972656</v>
+        <v>75.32070922851562</v>
       </c>
       <c r="C117" t="n">
-        <v>0.05446760805521444</v>
+        <v>0.05446770904684151</v>
       </c>
     </row>
     <row r="118">
@@ -4533,10 +4533,10 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>104.4030075073242</v>
+        <v>104.4030151367188</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3861131915391889</v>
+        <v>0.3861130120266163</v>
       </c>
     </row>
     <row r="119">
@@ -4544,10 +4544,10 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>102.9450912475586</v>
+        <v>102.9450607299805</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.01396431285433375</v>
+        <v>-0.01396467721577821</v>
       </c>
     </row>
     <row r="120">
@@ -4555,10 +4555,10 @@
         <v>41944</v>
       </c>
       <c r="B120" t="n">
-        <v>100.1139678955078</v>
+        <v>100.1139984130859</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.02750129528024414</v>
+        <v>-0.02750071054229852</v>
       </c>
     </row>
     <row r="121">
@@ -4566,10 +4566,10 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>102.4619369506836</v>
+        <v>102.4619216918945</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02345296170486844</v>
+        <v>0.02345249731331966</v>
       </c>
     </row>
     <row r="122">
@@ -4577,10 +4577,10 @@
         <v>42005</v>
       </c>
       <c r="B122" t="n">
-        <v>111.3580627441406</v>
+        <v>111.3580551147461</v>
       </c>
       <c r="C122" t="n">
-        <v>0.08682371286557733</v>
+        <v>0.08682380025627912</v>
       </c>
     </row>
     <row r="123">
@@ -4588,10 +4588,10 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>123.2124481201172</v>
+        <v>123.2124938964844</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1064528699930201</v>
+        <v>0.1064533568723267</v>
       </c>
     </row>
     <row r="124">
@@ -4599,10 +4599,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>109.7706527709961</v>
+        <v>109.7706451416016</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.1090944588327388</v>
+        <v>-0.1090948517459263</v>
       </c>
     </row>
     <row r="125">
@@ -4610,10 +4610,10 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>119.2354125976562</v>
+        <v>119.2354049682617</v>
       </c>
       <c r="C125" t="n">
-        <v>0.08622304402621683</v>
+        <v>0.08622305001898134</v>
       </c>
     </row>
     <row r="126">
@@ -4624,7 +4624,7 @@
         <v>132.1310424804688</v>
       </c>
       <c r="C126" t="n">
-        <v>0.108152683853471</v>
+        <v>0.1081527547597092</v>
       </c>
     </row>
     <row r="127">
@@ -4632,10 +4632,10 @@
         <v>42156</v>
       </c>
       <c r="B127" t="n">
-        <v>112.3053665161133</v>
+        <v>112.3054046630859</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1500455577445856</v>
+        <v>-0.1500452690389799</v>
       </c>
     </row>
     <row r="128">
@@ -4643,10 +4643,10 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>164.6190032958984</v>
+        <v>164.6190490722656</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4658160015200996</v>
+        <v>0.4658159112299147</v>
       </c>
     </row>
     <row r="129">
@@ -4657,7 +4657,7 @@
         <v>144.1385650634766</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.1244111422276614</v>
+        <v>-0.1244113857066347</v>
       </c>
     </row>
     <row r="130">
@@ -4665,10 +4665,10 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>139.2274017333984</v>
+        <v>139.2273864746094</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.03407251437472902</v>
+        <v>-0.03407262023667557</v>
       </c>
     </row>
     <row r="131">
@@ -4676,10 +4676,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>165.9804077148438</v>
+        <v>165.9803619384766</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1921533092506724</v>
+        <v>0.1921531111175894</v>
       </c>
     </row>
     <row r="132">
@@ -4687,10 +4687,10 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>188.0030517578125</v>
+        <v>188.0030975341797</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1326821903028694</v>
+        <v>0.1326827784835547</v>
       </c>
     </row>
     <row r="133">
@@ -4698,10 +4698,10 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>187.7359771728516</v>
+        <v>187.7360076904297</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.001420586434442539</v>
+        <v>-0.001420667250982111</v>
       </c>
     </row>
     <row r="134">
@@ -4709,10 +4709,10 @@
         <v>42370</v>
       </c>
       <c r="B134" t="n">
-        <v>156.7057037353516</v>
+        <v>156.7057495117188</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1652867708405722</v>
+        <v>-0.1652866626943446</v>
       </c>
     </row>
     <row r="135">
@@ -4723,7 +4723,7 @@
         <v>146.0663604736328</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.06789378438762339</v>
+        <v>-0.06789405667141968</v>
       </c>
     </row>
     <row r="136">
@@ -4731,10 +4731,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>163.0666198730469</v>
+        <v>163.0666046142578</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1163872321066208</v>
+        <v>0.1163871276418489</v>
       </c>
     </row>
     <row r="137">
@@ -4742,10 +4742,10 @@
         <v>42461</v>
       </c>
       <c r="B137" t="n">
-        <v>170.7102203369141</v>
+        <v>170.710205078125</v>
       </c>
       <c r="C137" t="n">
-        <v>0.04687409642646667</v>
+        <v>0.04687410081266186</v>
       </c>
     </row>
     <row r="138">
@@ -4756,7 +4756,7 @@
         <v>165.7833557128906</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.0288609821620508</v>
+        <v>-0.02886089535760106</v>
       </c>
     </row>
     <row r="139">
@@ -4764,10 +4764,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>169.6444702148438</v>
+        <v>169.6444549560547</v>
       </c>
       <c r="C139" t="n">
-        <v>0.02329012152848398</v>
+        <v>0.02329002948794723</v>
       </c>
     </row>
     <row r="140">
@@ -4775,10 +4775,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>183.7349548339844</v>
+        <v>183.7349395751953</v>
       </c>
       <c r="C140" t="n">
-        <v>0.08305890903072721</v>
+        <v>0.08305891650151898</v>
       </c>
     </row>
     <row r="141">
@@ -4786,10 +4786,10 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>188.1027221679688</v>
+        <v>188.1027069091797</v>
       </c>
       <c r="C141" t="n">
-        <v>0.02377210878534752</v>
+        <v>0.02377211075956964</v>
       </c>
     </row>
     <row r="142">
@@ -4800,7 +4800,7 @@
         <v>173.4531860351562</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.0778805110525248</v>
+        <v>-0.07788043625069452</v>
       </c>
     </row>
     <row r="143">
@@ -4808,10 +4808,10 @@
         <v>42644</v>
       </c>
       <c r="B143" t="n">
-        <v>160.5595245361328</v>
+        <v>160.5595092773438</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.07433510905017393</v>
+        <v>-0.07433519702082125</v>
       </c>
     </row>
     <row r="144">
@@ -4819,10 +4819,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>175.6370391845703</v>
+        <v>175.6370697021484</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0939060743484228</v>
+        <v>0.09390636837809674</v>
       </c>
     </row>
     <row r="145">
@@ -4830,10 +4830,10 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>165.9755706787109</v>
+        <v>165.9755401611328</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.05500814948096744</v>
+        <v>-0.05500848743035847</v>
       </c>
     </row>
     <row r="146">
@@ -4841,10 +4841,10 @@
         <v>42736</v>
       </c>
       <c r="B146" t="n">
-        <v>155.9645690917969</v>
+        <v>155.964599609375</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.06031611487146482</v>
+        <v>-0.06031575822581425</v>
       </c>
     </row>
     <row r="147">
@@ -4855,7 +4855,7 @@
         <v>161.4317626953125</v>
       </c>
       <c r="C147" t="n">
-        <v>0.03505407436670938</v>
+        <v>0.03505387183777864</v>
       </c>
     </row>
     <row r="148">
@@ -4863,10 +4863,10 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>162.5387268066406</v>
+        <v>162.5387115478516</v>
       </c>
       <c r="C148" t="n">
-        <v>0.006857164246031333</v>
+        <v>0.0068570697244279</v>
       </c>
     </row>
     <row r="149">
@@ -4874,10 +4874,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>152.0225830078125</v>
+        <v>152.0225677490234</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.06469931200666013</v>
+        <v>-0.06469931808049412</v>
       </c>
     </row>
     <row r="150">
@@ -4885,10 +4885,10 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>152.1455688476562</v>
+        <v>152.1455841064453</v>
       </c>
       <c r="C150" t="n">
-        <v>0.000808997172725423</v>
+        <v>0.0008091979976614372</v>
       </c>
     </row>
     <row r="151">
@@ -4896,10 +4896,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>142.9384918212891</v>
+        <v>142.9384765625</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.06051492065198594</v>
+        <v>-0.06051511516432684</v>
       </c>
     </row>
     <row r="152">
@@ -4907,10 +4907,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>141.8410034179688</v>
+        <v>141.8409729003906</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.007678046615270495</v>
+        <v>-0.007678154185654096</v>
       </c>
     </row>
     <row r="153">
@@ -4918,10 +4918,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>140.8040924072266</v>
+        <v>140.8041381835938</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.007310375601945474</v>
+        <v>-0.007309839291112286</v>
       </c>
     </row>
     <row r="154">
@@ -4929,10 +4929,10 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>132.8900909423828</v>
+        <v>132.8900756835938</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.05620576312480519</v>
+        <v>-0.05620617832752117</v>
       </c>
     </row>
     <row r="155">
@@ -4943,7 +4943,7 @@
         <v>140.2989501953125</v>
       </c>
       <c r="C155" t="n">
-        <v>0.05575178104244016</v>
+        <v>0.05575190226664484</v>
       </c>
     </row>
     <row r="156">
@@ -4973,10 +4973,10 @@
         <v>43101</v>
       </c>
       <c r="B158" t="n">
-        <v>169.8990783691406</v>
+        <v>169.8990478515625</v>
       </c>
       <c r="C158" t="n">
-        <v>0.07635769915071755</v>
+        <v>0.07635750581341116</v>
       </c>
     </row>
     <row r="159">
@@ -4984,10 +4984,10 @@
         <v>43132</v>
       </c>
       <c r="B159" t="n">
-        <v>159.1717834472656</v>
+        <v>159.1717987060547</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.06313921785124554</v>
+        <v>-0.06313895975968031</v>
       </c>
     </row>
     <row r="160">
@@ -4995,10 +4995,10 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>160.5973663330078</v>
+        <v>160.5973052978516</v>
       </c>
       <c r="C160" t="n">
-        <v>0.008956253771036593</v>
+        <v>0.008955773594224281</v>
       </c>
     </row>
     <row r="161">
@@ -5006,10 +5006,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>228.1239318847656</v>
+        <v>228.1239471435547</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4204711888720367</v>
+        <v>0.4204718237361762</v>
       </c>
     </row>
     <row r="162">
@@ -5017,10 +5017,10 @@
         <v>43221</v>
       </c>
       <c r="B162" t="n">
-        <v>232.3650054931641</v>
+        <v>232.3649749755859</v>
       </c>
       <c r="C162" t="n">
-        <v>0.01859109464473363</v>
+        <v>0.01859089273675618</v>
       </c>
     </row>
     <row r="163">
@@ -5028,10 +5028,10 @@
         <v>43252</v>
       </c>
       <c r="B163" t="n">
-        <v>227.9101409912109</v>
+        <v>227.9100952148438</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.01917183911793541</v>
+        <v>-0.0191719073031994</v>
       </c>
     </row>
     <row r="164">
@@ -5039,10 +5039,10 @@
         <v>43282</v>
       </c>
       <c r="B164" t="n">
-        <v>221.4770050048828</v>
+        <v>221.4769897460938</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.02822663334922082</v>
+        <v>-0.02822650511679048</v>
       </c>
     </row>
     <row r="165">
@@ -5050,10 +5050,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>299.8218994140625</v>
+        <v>299.8219604492188</v>
       </c>
       <c r="C165" t="n">
-        <v>0.353738278190336</v>
+        <v>0.353738647039322</v>
       </c>
     </row>
     <row r="166">
@@ -5061,10 +5061,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>253.1895141601562</v>
+        <v>253.1895599365234</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.1555336196089719</v>
+        <v>-0.155533638839619</v>
       </c>
     </row>
     <row r="167">
@@ -5072,10 +5072,10 @@
         <v>43374</v>
       </c>
       <c r="B167" t="n">
-        <v>229.8464202880859</v>
+        <v>229.8464508056641</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.09219613201400012</v>
+        <v>-0.09219617561131532</v>
       </c>
     </row>
     <row r="168">
@@ -5083,10 +5083,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>199.2898406982422</v>
+        <v>199.2898712158203</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.1329434652562551</v>
+        <v>-0.132943447604851</v>
       </c>
     </row>
     <row r="169">
@@ -5094,10 +5094,10 @@
         <v>43435</v>
       </c>
       <c r="B169" t="n">
-        <v>208.0267028808594</v>
+        <v>208.0267181396484</v>
       </c>
       <c r="C169" t="n">
-        <v>0.04383997775303672</v>
+        <v>0.04383989447394732</v>
       </c>
     </row>
     <row r="170">
@@ -5105,10 +5105,10 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>202.2188110351562</v>
+        <v>202.2187957763672</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.02791897273413702</v>
+        <v>-0.02791911738655795</v>
       </c>
     </row>
     <row r="171">
@@ -5119,7 +5119,7 @@
         <v>181.5603485107422</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.1021589555326905</v>
+        <v>-0.1021588877844525</v>
       </c>
     </row>
     <row r="172">
@@ -5127,10 +5127,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>207.1246337890625</v>
+        <v>207.1246032714844</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1408032397382613</v>
+        <v>0.1408030716532231</v>
       </c>
     </row>
     <row r="173">
@@ -5138,10 +5138,10 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>211.2203369140625</v>
+        <v>211.2202911376953</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0197740995364708</v>
+        <v>0.01977402878035983</v>
       </c>
     </row>
     <row r="174">
@@ -5149,10 +5149,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>225.0376586914062</v>
+        <v>225.0376281738281</v>
       </c>
       <c r="C174" t="n">
-        <v>0.06541662597084819</v>
+        <v>0.06541671238927149</v>
       </c>
     </row>
     <row r="175">
@@ -5160,10 +5160,10 @@
         <v>43617</v>
       </c>
       <c r="B175" t="n">
-        <v>232.6888732910156</v>
+        <v>232.6889190673828</v>
       </c>
       <c r="C175" t="n">
-        <v>0.03399970762272053</v>
+        <v>0.03400005126095862</v>
       </c>
     </row>
     <row r="176">
@@ -5174,7 +5174,7 @@
         <v>191.2090148925781</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.1782631795485989</v>
+        <v>-0.1782633412070336</v>
       </c>
     </row>
     <row r="177">
@@ -5193,10 +5193,10 @@
         <v>43709</v>
       </c>
       <c r="B178" t="n">
-        <v>199.0606994628906</v>
+        <v>199.0607147216797</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.002955219110157059</v>
+        <v>-0.002955142682735445</v>
       </c>
     </row>
     <row r="179">
@@ -5204,10 +5204,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>161.9353637695312</v>
+        <v>161.9353942871094</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.1865025883739566</v>
+        <v>-0.1865024974238525</v>
       </c>
     </row>
     <row r="180">
@@ -5215,10 +5215,10 @@
         <v>43770</v>
       </c>
       <c r="B180" t="n">
-        <v>169.3786163330078</v>
+        <v>169.3786315917969</v>
       </c>
       <c r="C180" t="n">
-        <v>0.04596434274893713</v>
+        <v>0.04596423985908071</v>
       </c>
     </row>
     <row r="181">
@@ -5229,7 +5229,7 @@
         <v>158.4860687255859</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.06430887111515016</v>
+        <v>-0.06430895540862591</v>
       </c>
     </row>
     <row r="182">
@@ -5248,10 +5248,10 @@
         <v>43862</v>
       </c>
       <c r="B183" t="n">
-        <v>124.8044204711914</v>
+        <v>124.8044128417969</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.196882088739456</v>
+        <v>-0.1968821378346994</v>
       </c>
     </row>
     <row r="184">
@@ -5262,7 +5262,7 @@
         <v>81.83149719238281</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.3443221251023559</v>
+        <v>-0.344322085020238</v>
       </c>
     </row>
     <row r="185">
@@ -5270,10 +5270,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>78.85581207275391</v>
+        <v>78.85579681396484</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.03636356686268594</v>
+        <v>-0.03636375332865061</v>
       </c>
     </row>
     <row r="186">
@@ -5281,10 +5281,10 @@
         <v>43952</v>
       </c>
       <c r="B186" t="n">
-        <v>80.76210784912109</v>
+        <v>80.76210021972656</v>
       </c>
       <c r="C186" t="n">
-        <v>0.02417444860764872</v>
+        <v>0.02417455003668323</v>
       </c>
     </row>
     <row r="187">
@@ -5295,7 +5295,7 @@
         <v>115.1685256958008</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4260217911964035</v>
+        <v>0.4260219259091318</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
         <v>44044</v>
       </c>
       <c r="B189" t="n">
-        <v>160.2223510742188</v>
+        <v>160.2223358154297</v>
       </c>
       <c r="C189" t="n">
-        <v>0.07721168161173675</v>
+        <v>0.07721157902339182</v>
       </c>
     </row>
     <row r="190">
@@ -5325,10 +5325,10 @@
         <v>44075</v>
       </c>
       <c r="B190" t="n">
-        <v>178.9134216308594</v>
+        <v>178.9134063720703</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1166570733192056</v>
+        <v>0.1166570844290529</v>
       </c>
     </row>
     <row r="191">
@@ -5336,10 +5336,10 @@
         <v>44105</v>
       </c>
       <c r="B191" t="n">
-        <v>165.3833312988281</v>
+        <v>165.38330078125</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.07562367433756323</v>
+        <v>-0.07562376607308541</v>
       </c>
     </row>
     <row r="192">
@@ -5347,10 +5347,10 @@
         <v>44136</v>
       </c>
       <c r="B192" t="n">
-        <v>211.7389831542969</v>
+        <v>211.7389984130859</v>
       </c>
       <c r="C192" t="n">
-        <v>0.2802921642188327</v>
+        <v>0.2802924927296615</v>
       </c>
     </row>
     <row r="193">
@@ -5361,7 +5361,7 @@
         <v>220.7590484619141</v>
       </c>
       <c r="C193" t="n">
-        <v>0.04259992738816609</v>
+        <v>0.04259985225409779</v>
       </c>
     </row>
     <row r="194">
@@ -5369,10 +5369,10 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>220.3368072509766</v>
+        <v>220.3368377685547</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.001912679067423761</v>
+        <v>-0.00191254082811565</v>
       </c>
     </row>
     <row r="195">
@@ -5380,10 +5380,10 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>275.9467468261719</v>
+        <v>275.94677734375</v>
       </c>
       <c r="C195" t="n">
-        <v>0.2523860641760698</v>
+        <v>0.2523860292195392</v>
       </c>
     </row>
     <row r="196">
@@ -5391,10 +5391,10 @@
         <v>44256</v>
       </c>
       <c r="B196" t="n">
-        <v>256.0392761230469</v>
+        <v>256.0393371582031</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.07214243665523401</v>
+        <v>-0.07214231808457738</v>
       </c>
     </row>
     <row r="197">
@@ -5402,10 +5402,10 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>247.0202026367188</v>
+        <v>247.0202178955078</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.03522535144957117</v>
+        <v>-0.03522552183894512</v>
       </c>
     </row>
     <row r="198">
@@ -5413,10 +5413,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>267.1145324707031</v>
+        <v>267.1145935058594</v>
       </c>
       <c r="C198" t="n">
-        <v>0.08134690855037552</v>
+        <v>0.08134708883971475</v>
       </c>
     </row>
     <row r="199">
@@ -5427,7 +5427,7 @@
         <v>290.9941711425781</v>
       </c>
       <c r="C199" t="n">
-        <v>0.08939850052708787</v>
+        <v>0.08939825160168535</v>
       </c>
     </row>
     <row r="200">
@@ -5435,10 +5435,10 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>388.708740234375</v>
+        <v>388.7087097167969</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3357956233560422</v>
+        <v>0.3357955184825392</v>
       </c>
     </row>
     <row r="201">
@@ -5446,10 +5446,10 @@
         <v>44409</v>
       </c>
       <c r="B201" t="n">
-        <v>420.8596496582031</v>
+        <v>420.8596801757812</v>
       </c>
       <c r="C201" t="n">
-        <v>0.08271208258513174</v>
+        <v>0.0827122460991645</v>
       </c>
     </row>
     <row r="202">
@@ -5460,7 +5460,7 @@
         <v>448.772705078125</v>
       </c>
       <c r="C202" t="n">
-        <v>0.06632390499443508</v>
+        <v>0.06632382767264677</v>
       </c>
     </row>
     <row r="203">
@@ -5468,10 +5468,10 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>433.6037902832031</v>
+        <v>433.6038513183594</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.03380088544440596</v>
+        <v>-0.03380074943979705</v>
       </c>
     </row>
     <row r="204">
@@ -5479,10 +5479,10 @@
         <v>44501</v>
       </c>
       <c r="B204" t="n">
-        <v>419.4211730957031</v>
+        <v>419.4212036132812</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.03270870205778598</v>
+        <v>-0.03270876783487098</v>
       </c>
     </row>
     <row r="205">
@@ -5490,10 +5490,10 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>489.8647766113281</v>
+        <v>489.8648071289062</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1679543333391784</v>
+        <v>0.1679543211186245</v>
       </c>
     </row>
     <row r="206">
@@ -5501,10 +5501,10 @@
         <v>44562</v>
       </c>
       <c r="B206" t="n">
-        <v>390.257568359375</v>
+        <v>390.2575378417969</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.2033361307195682</v>
+        <v>-0.203336242648062</v>
       </c>
     </row>
     <row r="207">
@@ -5515,7 +5515,7 @@
         <v>326.4296264648438</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.1635533736420821</v>
+        <v>-0.1635533082331591</v>
       </c>
     </row>
     <row r="208">
@@ -5523,10 +5523,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>345.8449096679688</v>
+        <v>345.8448486328125</v>
       </c>
       <c r="C208" t="n">
-        <v>0.05947769941530101</v>
+        <v>0.05947751243730859</v>
       </c>
     </row>
     <row r="209">
@@ -5534,10 +5534,10 @@
         <v>44652</v>
       </c>
       <c r="B209" t="n">
-        <v>304.5169067382812</v>
+        <v>304.5169372558594</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.119498659006908</v>
+        <v>-0.1194984153742057</v>
       </c>
     </row>
     <row r="210">
@@ -5548,7 +5548,7 @@
         <v>288.2118835449219</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.05354390128286968</v>
+        <v>-0.05354399613325211</v>
       </c>
     </row>
     <row r="211">
@@ -5556,10 +5556,10 @@
         <v>44713</v>
       </c>
       <c r="B211" t="n">
-        <v>256.4501037597656</v>
+        <v>256.4501342773438</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.1102028805838803</v>
+        <v>-0.1102027746979684</v>
       </c>
     </row>
     <row r="212">
@@ -5570,7 +5570,7 @@
         <v>236.5513153076172</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.07759321661569296</v>
+        <v>-0.07759332638214389</v>
       </c>
     </row>
     <row r="213">
@@ -5589,10 +5589,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>202.2463531494141</v>
+        <v>202.246337890625</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.08336940427040707</v>
+        <v>-0.08336947342702072</v>
       </c>
     </row>
     <row r="215">
@@ -5603,7 +5603,7 @@
         <v>213.4743041992188</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0555162101811042</v>
+        <v>0.05551628981616386</v>
       </c>
     </row>
     <row r="216">
@@ -5611,10 +5611,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>212.9965057373047</v>
+        <v>212.9965209960938</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.002238201284723074</v>
+        <v>-0.002238129806382383</v>
       </c>
     </row>
     <row r="217">
@@ -5622,10 +5622,10 @@
         <v>44896</v>
       </c>
       <c r="B217" t="n">
-        <v>203.5363922119141</v>
+        <v>203.5363616943359</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.04441440714082923</v>
+        <v>-0.04441461887507214</v>
       </c>
     </row>
     <row r="218">
@@ -5633,10 +5633,10 @@
         <v>44927</v>
       </c>
       <c r="B218" t="n">
-        <v>220.0677185058594</v>
+        <v>220.0677490234375</v>
       </c>
       <c r="C218" t="n">
-        <v>0.08122049386005403</v>
+        <v>0.08122080591146585</v>
       </c>
     </row>
     <row r="219">
@@ -5644,10 +5644,10 @@
         <v>44958</v>
       </c>
       <c r="B219" t="n">
-        <v>279.1786193847656</v>
+        <v>279.1785888671875</v>
       </c>
       <c r="C219" t="n">
-        <v>0.268603233951064</v>
+        <v>0.2686029193557782</v>
       </c>
     </row>
     <row r="220">
@@ -5658,7 +5658,7 @@
         <v>263.8396911621094</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.05494306210288991</v>
+        <v>-0.05494295879679811</v>
       </c>
     </row>
     <row r="221">
@@ -5677,10 +5677,10 @@
         <v>45047</v>
       </c>
       <c r="B222" t="n">
-        <v>355.48876953125</v>
+        <v>355.4887084960938</v>
       </c>
       <c r="C222" t="n">
-        <v>0.3284818194249188</v>
+        <v>0.3284815913330568</v>
       </c>
     </row>
     <row r="223">
@@ -5691,7 +5691,7 @@
         <v>372.1259765625</v>
       </c>
       <c r="C223" t="n">
-        <v>0.04680093566159038</v>
+        <v>0.04680111539067089</v>
       </c>
     </row>
     <row r="224">
@@ -5699,10 +5699,10 @@
         <v>45108</v>
       </c>
       <c r="B224" t="n">
-        <v>481.9972839355469</v>
+        <v>481.997314453125</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2952529903662706</v>
+        <v>0.2952530723749991</v>
       </c>
     </row>
     <row r="225">
@@ -5710,10 +5710,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>510.6322326660156</v>
+        <v>510.6322631835938</v>
       </c>
       <c r="C225" t="n">
-        <v>0.05940894209332903</v>
+        <v>0.05940893833186189</v>
       </c>
     </row>
     <row r="226">
@@ -5721,10 +5721,10 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>501.3779602050781</v>
+        <v>501.3779907226562</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.01812316549744786</v>
+        <v>-0.0181231644143296</v>
       </c>
     </row>
     <row r="227">
@@ -5735,7 +5735,7 @@
         <v>474.8749084472656</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.05286042439315042</v>
+        <v>-0.05286048204308025</v>
       </c>
     </row>
     <row r="228">
@@ -5765,10 +5765,10 @@
         <v>45292</v>
       </c>
       <c r="B230" t="n">
-        <v>556.467529296875</v>
+        <v>556.4675903320312</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.05960862186302029</v>
+        <v>-0.05960851871785611</v>
       </c>
     </row>
     <row r="231">
@@ -5776,10 +5776,10 @@
         <v>45323</v>
       </c>
       <c r="B231" t="n">
-        <v>534.4674682617188</v>
+        <v>534.4674072265625</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.03953521073000332</v>
+        <v>-0.03953542576009095</v>
       </c>
     </row>
     <row r="232">
@@ -5787,10 +5787,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>590.0438232421875</v>
+        <v>590.0439453125</v>
       </c>
       <c r="C232" t="n">
-        <v>0.1039845421485113</v>
+        <v>0.1039848966176125</v>
       </c>
     </row>
     <row r="233">
@@ -5798,10 +5798,10 @@
         <v>45383</v>
       </c>
       <c r="B233" t="n">
-        <v>596.3649291992188</v>
+        <v>596.364990234375</v>
       </c>
       <c r="C233" t="n">
-        <v>0.01071294318835148</v>
+        <v>0.01071283753030849</v>
       </c>
     </row>
     <row r="234">
@@ -5809,10 +5809,10 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>593.3016357421875</v>
+        <v>593.3015747070312</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.00513660899064694</v>
+        <v>-0.00513681315554726</v>
       </c>
     </row>
     <row r="235">
@@ -5823,7 +5823,7 @@
         <v>726.7726440429688</v>
       </c>
       <c r="C235" t="n">
-        <v>0.2249631557712064</v>
+        <v>0.2249632817877565</v>
       </c>
     </row>
     <row r="236">
@@ -5842,10 +5842,10 @@
         <v>45505</v>
       </c>
       <c r="B237" t="n">
-        <v>753.4302368164062</v>
+        <v>753.4302978515625</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.03207918379194996</v>
+        <v>-0.03207910538097658</v>
       </c>
     </row>
     <row r="238">
@@ -5853,10 +5853,10 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>662.6242065429688</v>
+        <v>662.6240844726562</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.1205234749498976</v>
+        <v>-0.1205237082154035</v>
       </c>
     </row>
     <row r="239">
@@ -5867,7 +5867,7 @@
         <v>690.5380859375</v>
       </c>
       <c r="C239" t="n">
-        <v>0.04212625967916717</v>
+        <v>0.04212645166234608</v>
       </c>
     </row>
     <row r="240">
@@ -5875,10 +5875,10 @@
         <v>45597</v>
       </c>
       <c r="B240" t="n">
-        <v>744.7960205078125</v>
+        <v>744.7960815429688</v>
       </c>
       <c r="C240" t="n">
-        <v>0.07857341350933589</v>
+        <v>0.07857350189715628</v>
       </c>
     </row>
     <row r="241">
@@ -5889,7 +5889,7 @@
         <v>737.4864501953125</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.009814190880767959</v>
+        <v>-0.00981427202532148</v>
       </c>
     </row>
     <row r="242">
@@ -5908,10 +5908,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>726.312255859375</v>
+        <v>726.3123168945312</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1512069118871903</v>
+        <v>-0.1512068405594407</v>
       </c>
     </row>
     <row r="244">
@@ -5919,10 +5919,10 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>689.330322265625</v>
+        <v>689.3302612304688</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.05091740266724931</v>
+        <v>-0.05091756645706547</v>
       </c>
     </row>
     <row r="245">
@@ -5933,7 +5933,7 @@
         <v>707.6245727539062</v>
       </c>
       <c r="C245" t="n">
-        <v>0.02653916402248702</v>
+        <v>0.02653925491502696</v>
       </c>
     </row>
     <row r="246">
@@ -5952,10 +5952,10 @@
         <v>45809</v>
       </c>
       <c r="B247" t="n">
-        <v>828.701171875</v>
+        <v>828.7012329101562</v>
       </c>
       <c r="C247" t="n">
-        <v>0.01140382875864909</v>
+        <v>0.01140390325014584</v>
       </c>
     </row>
     <row r="248">
@@ -5966,7 +5966,7 @@
         <v>803.3386840820312</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.03060510670641892</v>
+        <v>-0.03060517810388574</v>
       </c>
     </row>
     <row r="249">
@@ -6071,7 +6071,7 @@
         <v>38353</v>
       </c>
       <c r="B2" t="n">
-        <v>11.03503608703613</v>
+        <v>11.03503513336182</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -6083,7 +6083,7 @@
         <v>10.61943912506104</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03766158612415749</v>
+        <v>-0.03766150295655379</v>
       </c>
     </row>
     <row r="4">
@@ -6102,10 +6102,10 @@
         <v>38443</v>
       </c>
       <c r="B5" t="n">
-        <v>10.38592052459717</v>
+        <v>10.38591861724854</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03715448348398631</v>
+        <v>0.037154293013129</v>
       </c>
     </row>
     <row r="6">
@@ -6113,10 +6113,10 @@
         <v>38473</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86483860015869</v>
+        <v>10.86484050750732</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04611224151266069</v>
+        <v>0.04611261727618521</v>
       </c>
     </row>
     <row r="7">
@@ -6127,7 +6127,7 @@
         <v>12.2897367477417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1311476589778513</v>
+        <v>0.1311474604021852</v>
       </c>
     </row>
     <row r="8">
@@ -6135,10 +6135,10 @@
         <v>38534</v>
       </c>
       <c r="B8" t="n">
-        <v>12.52692604064941</v>
+        <v>12.52692317962646</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01929978629943396</v>
+        <v>0.0192995535016931</v>
       </c>
     </row>
     <row r="9">
@@ -6146,10 +6146,10 @@
         <v>38565</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97202110290527</v>
+        <v>13.97202587127686</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1153591118496733</v>
+        <v>0.1153597472363108</v>
       </c>
     </row>
     <row r="10">
@@ -6157,10 +6157,10 @@
         <v>38596</v>
       </c>
       <c r="B10" t="n">
-        <v>14.22583484649658</v>
+        <v>14.22583293914795</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01816585744624533</v>
+        <v>0.01816537345474445</v>
       </c>
     </row>
     <row r="11">
@@ -6168,10 +6168,10 @@
         <v>38626</v>
       </c>
       <c r="B11" t="n">
-        <v>12.47370433807373</v>
+        <v>12.47370529174805</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1231653908068777</v>
+        <v>-0.1231652062058339</v>
       </c>
     </row>
     <row r="12">
@@ -6179,10 +6179,10 @@
         <v>38657</v>
       </c>
       <c r="B12" t="n">
-        <v>13.82055568695068</v>
+        <v>13.82055187225342</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1079752503645555</v>
+        <v>0.1079748598354633</v>
       </c>
     </row>
     <row r="13">
@@ -6190,10 +6190,10 @@
         <v>38687</v>
       </c>
       <c r="B13" t="n">
-        <v>13.4684886932373</v>
+        <v>13.46849060058594</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.02547415615464721</v>
+        <v>-0.02547374916151435</v>
       </c>
     </row>
     <row r="14">
@@ -6201,10 +6201,10 @@
         <v>38718</v>
       </c>
       <c r="B14" t="n">
-        <v>14.48783493041992</v>
+        <v>14.48783874511719</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07568378757257621</v>
+        <v>0.07568391847018874</v>
       </c>
     </row>
     <row r="15">
@@ -6212,10 +6212,10 @@
         <v>38749</v>
       </c>
       <c r="B15" t="n">
-        <v>14.40186500549316</v>
+        <v>14.40186405181885</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.005933938738234001</v>
+        <v>-0.005934266305063329</v>
       </c>
     </row>
     <row r="16">
@@ -6223,10 +6223,10 @@
         <v>38777</v>
       </c>
       <c r="B16" t="n">
-        <v>18.71260452270508</v>
+        <v>18.71260261535645</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2993181449463462</v>
+        <v>0.2993180985480268</v>
       </c>
     </row>
     <row r="17">
@@ -6234,10 +6234,10 @@
         <v>38808</v>
       </c>
       <c r="B17" t="n">
-        <v>89.34644317626953</v>
+        <v>89.34645843505859</v>
       </c>
       <c r="C17" t="n">
-        <v>3.774666352183116</v>
+        <v>3.774667654286458</v>
       </c>
     </row>
     <row r="18">
@@ -6245,10 +6245,10 @@
         <v>38838</v>
       </c>
       <c r="B18" t="n">
-        <v>15.35162544250488</v>
+        <v>15.35162258148193</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.828178661659558</v>
+        <v>-0.8281787230252641</v>
       </c>
     </row>
     <row r="19">
@@ -6256,10 +6256,10 @@
         <v>38869</v>
       </c>
       <c r="B19" t="n">
-        <v>14.38139820098877</v>
+        <v>14.38139915466309</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.06320029401119909</v>
+        <v>-0.06320005730138201</v>
       </c>
     </row>
     <row r="20">
@@ -6267,10 +6267,10 @@
         <v>38899</v>
       </c>
       <c r="B20" t="n">
-        <v>15.42940139770508</v>
+        <v>15.42940616607666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07287213538418369</v>
+        <v>0.07287239580397609</v>
       </c>
     </row>
     <row r="21">
@@ -6278,10 +6278,10 @@
         <v>38930</v>
       </c>
       <c r="B21" t="n">
-        <v>15.78334999084473</v>
+        <v>15.78334808349609</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02293987848370405</v>
+        <v>0.02293943873210202</v>
       </c>
     </row>
     <row r="22">
@@ -6289,10 +6289,10 @@
         <v>38961</v>
       </c>
       <c r="B22" t="n">
-        <v>15.84254360198975</v>
+        <v>15.84254550933838</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003750383231655885</v>
+        <v>0.003750625376131911</v>
       </c>
     </row>
     <row r="23">
@@ -6300,10 +6300,10 @@
         <v>38991</v>
       </c>
       <c r="B23" t="n">
-        <v>20.61179542541504</v>
+        <v>20.6117992401123</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3010407888557933</v>
+        <v>0.3010408730063419</v>
       </c>
     </row>
     <row r="24">
@@ -6311,10 +6311,10 @@
         <v>39022</v>
       </c>
       <c r="B24" t="n">
-        <v>21.98169136047363</v>
+        <v>21.98169326782227</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06646174711056307</v>
+        <v>0.06646164227352025</v>
       </c>
     </row>
     <row r="25">
@@ -6322,10 +6322,10 @@
         <v>39052</v>
       </c>
       <c r="B25" t="n">
-        <v>25.84655570983887</v>
+        <v>25.8465633392334</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1758219732042474</v>
+        <v>0.1758222182578033</v>
       </c>
     </row>
     <row r="26">
@@ -6333,10 +6333,10 @@
         <v>39083</v>
       </c>
       <c r="B26" t="n">
-        <v>33.69299697875977</v>
+        <v>33.69300079345703</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3035778289768039</v>
+        <v>0.3035775917765149</v>
       </c>
     </row>
     <row r="27">
@@ -6344,10 +6344,10 @@
         <v>39114</v>
       </c>
       <c r="B27" t="n">
-        <v>33.53275680541992</v>
+        <v>33.53275299072266</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.004755889582658934</v>
+        <v>-0.004756115482759116</v>
       </c>
     </row>
     <row r="28">
@@ -6355,10 +6355,10 @@
         <v>39142</v>
       </c>
       <c r="B28" t="n">
-        <v>37.13928985595703</v>
+        <v>37.1392936706543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1075525365082475</v>
+        <v>0.1075527762641333</v>
       </c>
     </row>
     <row r="29">
@@ -6366,10 +6366,10 @@
         <v>39173</v>
       </c>
       <c r="B29" t="n">
-        <v>38.06904602050781</v>
+        <v>38.06903839111328</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02503430109075322</v>
+        <v>0.02503399037967236</v>
       </c>
     </row>
     <row r="30">
@@ -6380,7 +6380,7 @@
         <v>50.95745086669922</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3385533968791448</v>
+        <v>0.3385536651378767</v>
       </c>
     </row>
     <row r="31">
@@ -6399,10 +6399,10 @@
         <v>39264</v>
       </c>
       <c r="B32" t="n">
-        <v>40.68005752563477</v>
+        <v>40.6800651550293</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06806878302254493</v>
+        <v>-0.06806860824228733</v>
       </c>
     </row>
     <row r="33">
@@ -6410,10 +6410,10 @@
         <v>39295</v>
       </c>
       <c r="B33" t="n">
-        <v>39.78676605224609</v>
+        <v>39.78676986694336</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.02195895305275219</v>
+        <v>-0.02195904270756799</v>
       </c>
     </row>
     <row r="34">
@@ -6424,7 +6424,7 @@
         <v>45.53853607177734</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1445649041185779</v>
+        <v>0.14456479437937</v>
       </c>
     </row>
     <row r="35">
@@ -6432,10 +6432,10 @@
         <v>39356</v>
       </c>
       <c r="B35" t="n">
-        <v>42.90365600585938</v>
+        <v>42.90365219116211</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.05786044728721407</v>
+        <v>-0.05786053105576694</v>
       </c>
     </row>
     <row r="36">
@@ -6446,7 +6446,7 @@
         <v>28.64313125610352</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3323848379683142</v>
+        <v>-0.3323847786085721</v>
       </c>
     </row>
     <row r="37">
@@ -6454,10 +6454,10 @@
         <v>39417</v>
       </c>
       <c r="B37" t="n">
-        <v>30.41043663024902</v>
+        <v>30.41044425964355</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06170084402936626</v>
+        <v>0.06170111038971848</v>
       </c>
     </row>
     <row r="38">
@@ -6465,10 +6465,10 @@
         <v>39448</v>
       </c>
       <c r="B38" t="n">
-        <v>16.94681167602539</v>
+        <v>16.94681549072266</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4427304059433159</v>
+        <v>-0.4427304203111536</v>
       </c>
     </row>
     <row r="39">
@@ -6476,10 +6476,10 @@
         <v>39479</v>
       </c>
       <c r="B39" t="n">
-        <v>16.85041427612305</v>
+        <v>16.85041618347168</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.005688232202327281</v>
+        <v>-0.005688343471004886</v>
       </c>
     </row>
     <row r="40">
@@ -6487,10 +6487,10 @@
         <v>39508</v>
       </c>
       <c r="B40" t="n">
-        <v>13.09730815887451</v>
+        <v>13.09731197357178</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2227307919999728</v>
+        <v>-0.2227306535954445</v>
       </c>
     </row>
     <row r="41">
@@ -6501,7 +6501,7 @@
         <v>18.21926879882812</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3910697204206088</v>
+        <v>0.3910693152603844</v>
       </c>
     </row>
     <row r="42">
@@ -6520,10 +6520,10 @@
         <v>39600</v>
       </c>
       <c r="B43" t="n">
-        <v>15.61651611328125</v>
+        <v>15.61651706695557</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1562501449179479</v>
+        <v>-0.1562500933915664</v>
       </c>
     </row>
     <row r="44">
@@ -6531,10 +6531,10 @@
         <v>39630</v>
       </c>
       <c r="B44" t="n">
-        <v>14.88773441314697</v>
+        <v>14.88772964477539</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0466673677309164</v>
+        <v>-0.04666773129088331</v>
       </c>
     </row>
     <row r="45">
@@ -6542,10 +6542,10 @@
         <v>39661</v>
       </c>
       <c r="B45" t="n">
-        <v>15.71179676055908</v>
+        <v>15.7117977142334</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05535176303819611</v>
+        <v>0.05535216511318097</v>
       </c>
     </row>
     <row r="46">
@@ -6553,10 +6553,10 @@
         <v>39692</v>
       </c>
       <c r="B46" t="n">
-        <v>11.80257606506348</v>
+        <v>11.80257892608643</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.2488079979056769</v>
+        <v>-0.2488078614075836</v>
       </c>
     </row>
     <row r="47">
@@ -6564,10 +6564,10 @@
         <v>39722</v>
       </c>
       <c r="B47" t="n">
-        <v>8.683374404907227</v>
+        <v>8.683372497558594</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2642814283052429</v>
+        <v>-0.264281768252671</v>
       </c>
     </row>
     <row r="48">
@@ -6575,10 +6575,10 @@
         <v>39753</v>
       </c>
       <c r="B48" t="n">
-        <v>7.403000831604004</v>
+        <v>7.402999401092529</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1474511536183037</v>
+        <v>-0.1474511310929081</v>
       </c>
     </row>
     <row r="49">
@@ -6586,10 +6586,10 @@
         <v>39783</v>
       </c>
       <c r="B49" t="n">
-        <v>9.602787971496582</v>
+        <v>9.602792739868164</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2971480336057117</v>
+        <v>0.2971489283723285</v>
       </c>
     </row>
     <row r="50">
@@ -6597,10 +6597,10 @@
         <v>39814</v>
       </c>
       <c r="B50" t="n">
-        <v>7.294034004211426</v>
+        <v>7.294034957885742</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2404253821013337</v>
+        <v>-0.2404256599642198</v>
       </c>
     </row>
     <row r="51">
@@ -6608,10 +6608,10 @@
         <v>39845</v>
       </c>
       <c r="B51" t="n">
-        <v>6.538070201873779</v>
+        <v>6.538069725036621</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1036413871804228</v>
+        <v>-0.1036415697503383</v>
       </c>
     </row>
     <row r="52">
@@ -6622,7 +6622,7 @@
         <v>7.19187593460083</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0999998030825171</v>
+        <v>0.09999988330814968</v>
       </c>
     </row>
     <row r="53">
@@ -6630,10 +6630,10 @@
         <v>39904</v>
       </c>
       <c r="B53" t="n">
-        <v>9.330373764038086</v>
+        <v>9.330370903015137</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2973490990227918</v>
+        <v>0.2973487012096239</v>
       </c>
     </row>
     <row r="54">
@@ -6641,10 +6641,10 @@
         <v>39934</v>
       </c>
       <c r="B54" t="n">
-        <v>14.88092136383057</v>
+        <v>14.8809175491333</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5948901662638499</v>
+        <v>0.5948902464664603</v>
       </c>
     </row>
     <row r="55">
@@ -6655,7 +6655,7 @@
         <v>13.62097835540771</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0846683466445336</v>
+        <v>-0.08466811200086033</v>
       </c>
     </row>
     <row r="56">
@@ -6663,10 +6663,10 @@
         <v>39995</v>
       </c>
       <c r="B56" t="n">
-        <v>14.54305553436279</v>
+        <v>14.54305171966553</v>
       </c>
       <c r="C56" t="n">
-        <v>0.06769537069185638</v>
+        <v>0.06769509063141088</v>
       </c>
     </row>
     <row r="57">
@@ -6674,10 +6674,10 @@
         <v>40026</v>
       </c>
       <c r="B57" t="n">
-        <v>18.3655948638916</v>
+        <v>18.36558723449707</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2628429301185566</v>
+        <v>0.2628427367594797</v>
       </c>
     </row>
     <row r="58">
@@ -6685,10 +6685,10 @@
         <v>40057</v>
       </c>
       <c r="B58" t="n">
-        <v>17.85785293579102</v>
+        <v>17.85785484313965</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.02764636440384793</v>
+        <v>-0.027645856616211</v>
       </c>
     </row>
     <row r="59">
@@ -6696,10 +6696,10 @@
         <v>40087</v>
       </c>
       <c r="B59" t="n">
-        <v>19.80901908874512</v>
+        <v>19.80901145935059</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1092609598684475</v>
+        <v>0.1092604141622588</v>
       </c>
     </row>
     <row r="60">
@@ -6707,10 +6707,10 @@
         <v>40118</v>
       </c>
       <c r="B60" t="n">
-        <v>23.55176162719727</v>
+        <v>23.55176734924316</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1889413363521195</v>
+        <v>0.1889420831308499</v>
       </c>
     </row>
     <row r="61">
@@ -6721,7 +6721,7 @@
         <v>26.06869125366211</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1068679985092209</v>
+        <v>0.106867729588872</v>
       </c>
     </row>
     <row r="62">
@@ -6729,10 +6729,10 @@
         <v>40179</v>
       </c>
       <c r="B62" t="n">
-        <v>24.63252258300781</v>
+        <v>24.63251876831055</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.05509170585817369</v>
+        <v>-0.0550918521906929</v>
       </c>
     </row>
     <row r="63">
@@ -6740,10 +6740,10 @@
         <v>40210</v>
       </c>
       <c r="B63" t="n">
-        <v>24.92990112304688</v>
+        <v>24.92990684509277</v>
       </c>
       <c r="C63" t="n">
-        <v>0.01207259788504977</v>
+        <v>0.01207298691536218</v>
       </c>
     </row>
     <row r="64">
@@ -6751,10 +6751,10 @@
         <v>40238</v>
       </c>
       <c r="B64" t="n">
-        <v>24.62526893615723</v>
+        <v>24.62526321411133</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0122195505463929</v>
+        <v>-0.01222000679242052</v>
       </c>
     </row>
     <row r="65">
@@ -6762,10 +6762,10 @@
         <v>40269</v>
       </c>
       <c r="B65" t="n">
-        <v>27.14219284057617</v>
+        <v>27.14219856262207</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1022089915421533</v>
+        <v>0.1022094800216564</v>
       </c>
     </row>
     <row r="66">
@@ -6773,10 +6773,10 @@
         <v>40299</v>
       </c>
       <c r="B66" t="n">
-        <v>26.0034122467041</v>
+        <v>26.00341987609863</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.04195610135705952</v>
+        <v>-0.04195602223954209</v>
       </c>
     </row>
     <row r="67">
@@ -6784,10 +6784,10 @@
         <v>40330</v>
       </c>
       <c r="B67" t="n">
-        <v>25.7874698638916</v>
+        <v>25.78747749328613</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.008304386392207874</v>
+        <v>-0.008304383955703654</v>
       </c>
     </row>
     <row r="68">
@@ -6795,10 +6795,10 @@
         <v>40360</v>
       </c>
       <c r="B68" t="n">
-        <v>27.17567825317383</v>
+        <v>27.17568588256836</v>
       </c>
       <c r="C68" t="n">
-        <v>0.05383267131708958</v>
+        <v>0.0538326553903401</v>
       </c>
     </row>
     <row r="69">
@@ -6806,10 +6806,10 @@
         <v>40391</v>
       </c>
       <c r="B69" t="n">
-        <v>27.32657623291016</v>
+        <v>27.32657432556152</v>
       </c>
       <c r="C69" t="n">
-        <v>0.005552684953454845</v>
+        <v>0.005552332465321497</v>
       </c>
     </row>
     <row r="70">
@@ -6817,10 +6817,10 @@
         <v>40422</v>
       </c>
       <c r="B70" t="n">
-        <v>30.60093688964844</v>
+        <v>30.60093879699707</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1198233042013832</v>
+        <v>0.1198234521614616</v>
       </c>
     </row>
     <row r="71">
@@ -6828,10 +6828,10 @@
         <v>40452</v>
       </c>
       <c r="B71" t="n">
-        <v>33.10573959350586</v>
+        <v>33.10572814941406</v>
       </c>
       <c r="C71" t="n">
-        <v>0.08185379136887594</v>
+        <v>0.08185334995875326</v>
       </c>
     </row>
     <row r="72">
@@ -6839,10 +6839,10 @@
         <v>40483</v>
       </c>
       <c r="B72" t="n">
-        <v>31.59683227539062</v>
+        <v>31.59682655334473</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.04557842043834681</v>
+        <v>-0.04557826335247184</v>
       </c>
     </row>
     <row r="73">
@@ -6850,10 +6850,10 @@
         <v>40513</v>
       </c>
       <c r="B73" t="n">
-        <v>29.89173316955566</v>
+        <v>29.8917350769043</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0539642420788804</v>
+        <v>-0.05396401039078191</v>
       </c>
     </row>
     <row r="74">
@@ -6861,10 +6861,10 @@
         <v>40544</v>
       </c>
       <c r="B74" t="n">
-        <v>29.98981857299805</v>
+        <v>29.98983192443848</v>
       </c>
       <c r="C74" t="n">
-        <v>0.003281355513446105</v>
+        <v>0.003281738155439973</v>
       </c>
     </row>
     <row r="75">
@@ -6872,10 +6872,10 @@
         <v>40575</v>
       </c>
       <c r="B75" t="n">
-        <v>30.00491333007812</v>
+        <v>30.00491523742676</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0005033293897171998</v>
+        <v>0.0005029475665714322</v>
       </c>
     </row>
     <row r="76">
@@ -6886,7 +6886,7 @@
         <v>27.8396110534668</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.07216492355072868</v>
+        <v>-0.07216498253123071</v>
       </c>
     </row>
     <row r="77">
@@ -6894,10 +6894,10 @@
         <v>40634</v>
       </c>
       <c r="B77" t="n">
-        <v>28.39791297912598</v>
+        <v>28.39790725708008</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02005422865236683</v>
+        <v>0.02005402311623738</v>
       </c>
     </row>
     <row r="78">
@@ -6908,7 +6908,7 @@
         <v>27.89996528625488</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.0175346580305783</v>
+        <v>-0.01753446006839288</v>
       </c>
     </row>
     <row r="79">
@@ -6916,10 +6916,10 @@
         <v>40695</v>
       </c>
       <c r="B79" t="n">
-        <v>28.27311515808105</v>
+        <v>28.27311897277832</v>
       </c>
       <c r="C79" t="n">
-        <v>0.01337456401818571</v>
+        <v>0.01337470074585623</v>
       </c>
     </row>
     <row r="80">
@@ -6927,10 +6927,10 @@
         <v>40725</v>
       </c>
       <c r="B80" t="n">
-        <v>35.04450607299805</v>
+        <v>35.04451751708984</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2394992867625902</v>
+        <v>0.2394995242948295</v>
       </c>
     </row>
     <row r="81">
@@ -6938,10 +6938,10 @@
         <v>40756</v>
       </c>
       <c r="B81" t="n">
-        <v>30.43587684631348</v>
+        <v>30.43586921691895</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1315078950487917</v>
+        <v>-0.131508396368232</v>
       </c>
     </row>
     <row r="82">
@@ -6949,10 +6949,10 @@
         <v>40787</v>
       </c>
       <c r="B82" t="n">
-        <v>30.90775108337402</v>
+        <v>30.90774726867676</v>
       </c>
       <c r="C82" t="n">
-        <v>0.01550388179855267</v>
+        <v>0.01550401102050669</v>
       </c>
     </row>
     <row r="83">
@@ -6963,7 +6963,7 @@
         <v>36.31856918334961</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1750634682342251</v>
+        <v>0.1750636132629573</v>
       </c>
     </row>
     <row r="84">
@@ -6982,10 +6982,10 @@
         <v>40878</v>
       </c>
       <c r="B85" t="n">
-        <v>28.96521186828613</v>
+        <v>28.96519660949707</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.1101711381415923</v>
+        <v>-0.1101716069008393</v>
       </c>
     </row>
     <row r="86">
@@ -6993,10 +6993,10 @@
         <v>40909</v>
       </c>
       <c r="B86" t="n">
-        <v>32.88174819946289</v>
+        <v>32.88175964355469</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1352151798159278</v>
+        <v>0.1352161729423049</v>
       </c>
     </row>
     <row r="87">
@@ -7004,10 +7004,10 @@
         <v>40940</v>
       </c>
       <c r="B87" t="n">
-        <v>38.78019332885742</v>
+        <v>38.78018569946289</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1793835623828199</v>
+        <v>0.1793829198877555</v>
       </c>
     </row>
     <row r="88">
@@ -7015,10 +7015,10 @@
         <v>40969</v>
       </c>
       <c r="B88" t="n">
-        <v>42.87762069702148</v>
+        <v>42.87761688232422</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1056577344372096</v>
+        <v>0.1056578535908888</v>
       </c>
     </row>
     <row r="89">
@@ -7026,10 +7026,10 @@
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>41.02944183349609</v>
+        <v>41.02944564819336</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.04310357789171304</v>
+        <v>-0.04310340379231159</v>
       </c>
     </row>
     <row r="90">
@@ -7037,10 +7037,10 @@
         <v>41030</v>
       </c>
       <c r="B90" t="n">
-        <v>49.32656478881836</v>
+        <v>49.32656097412109</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2022236370895147</v>
+        <v>0.202223432338601</v>
       </c>
     </row>
     <row r="91">
@@ -7048,10 +7048,10 @@
         <v>41061</v>
       </c>
       <c r="B91" t="n">
-        <v>46.22443008422852</v>
+        <v>46.22441864013672</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.0628897373630416</v>
+        <v>-0.0628898968977768</v>
       </c>
     </row>
     <row r="92">
@@ -7059,10 +7059,10 @@
         <v>41091</v>
       </c>
       <c r="B92" t="n">
-        <v>47.22719573974609</v>
+        <v>47.22719192504883</v>
       </c>
       <c r="C92" t="n">
-        <v>0.02169341306513406</v>
+        <v>0.02169358348709216</v>
       </c>
     </row>
     <row r="93">
@@ -7070,10 +7070,10 @@
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>44.9628791809082</v>
+        <v>44.96286773681641</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.04794518334977604</v>
+        <v>-0.04794534876911549</v>
       </c>
     </row>
     <row r="94">
@@ -7081,10 +7081,10 @@
         <v>41153</v>
       </c>
       <c r="B94" t="n">
-        <v>48.1976203918457</v>
+        <v>48.19761276245117</v>
       </c>
       <c r="C94" t="n">
-        <v>0.07194248388592994</v>
+        <v>0.07194258703801704</v>
       </c>
     </row>
     <row r="95">
@@ -7092,10 +7092,10 @@
         <v>41183</v>
       </c>
       <c r="B95" t="n">
-        <v>47.59919738769531</v>
+        <v>47.59919357299805</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.01241602799651154</v>
+        <v>-0.0124159508148779</v>
       </c>
     </row>
     <row r="96">
@@ -7103,10 +7103,10 @@
         <v>41214</v>
       </c>
       <c r="B96" t="n">
-        <v>45.1973876953125</v>
+        <v>45.19739532470703</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.05045903763502735</v>
+        <v>-0.0504588012527486</v>
       </c>
     </row>
     <row r="97">
@@ -7114,10 +7114,10 @@
         <v>41244</v>
       </c>
       <c r="B97" t="n">
-        <v>39.19696044921875</v>
+        <v>39.19695281982422</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.1327604879853723</v>
+        <v>-0.1327608031784674</v>
       </c>
     </row>
     <row r="98">
@@ -7125,10 +7125,10 @@
         <v>41275</v>
       </c>
       <c r="B98" t="n">
-        <v>42.69047546386719</v>
+        <v>42.69047164916992</v>
       </c>
       <c r="C98" t="n">
-        <v>0.08912719186923757</v>
+        <v>0.08912730653845169</v>
       </c>
     </row>
     <row r="99">
@@ -7136,10 +7136,10 @@
         <v>41306</v>
       </c>
       <c r="B99" t="n">
-        <v>42.72282028198242</v>
+        <v>42.72280502319336</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0007576588867606038</v>
+        <v>0.0007573908831262077</v>
       </c>
     </row>
     <row r="100">
@@ -7150,7 +7150,7 @@
         <v>45.67451858520508</v>
       </c>
       <c r="C100" t="n">
-        <v>0.06908950026568084</v>
+        <v>0.06908988209948519</v>
       </c>
     </row>
     <row r="101">
@@ -7158,10 +7158,10 @@
         <v>41365</v>
       </c>
       <c r="B101" t="n">
-        <v>42.06778717041016</v>
+        <v>42.06777954101562</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.07896594264188295</v>
+        <v>-0.07896610968019602</v>
       </c>
     </row>
     <row r="102">
@@ -7169,10 +7169,10 @@
         <v>41395</v>
       </c>
       <c r="B102" t="n">
-        <v>42.9088249206543</v>
+        <v>42.90882110595703</v>
       </c>
       <c r="C102" t="n">
-        <v>0.01999244093437169</v>
+        <v>0.01999253523997857</v>
       </c>
     </row>
     <row r="103">
@@ -7180,10 +7180,10 @@
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>45.26537704467773</v>
+        <v>45.2653694152832</v>
       </c>
       <c r="C103" t="n">
-        <v>0.05491998740075266</v>
+        <v>0.05491990338086938</v>
       </c>
     </row>
     <row r="104">
@@ -7191,10 +7191,10 @@
         <v>41456</v>
       </c>
       <c r="B104" t="n">
-        <v>40.06168746948242</v>
+        <v>40.06169891357422</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.114959598592522</v>
+        <v>-0.1149591965983611</v>
       </c>
     </row>
     <row r="105">
@@ -7205,7 +7205,7 @@
         <v>47.03329849243164</v>
       </c>
       <c r="C105" t="n">
-        <v>0.174021901305579</v>
+        <v>0.1740215659325226</v>
       </c>
     </row>
     <row r="106">
@@ -7213,10 +7213,10 @@
         <v>41518</v>
       </c>
       <c r="B106" t="n">
-        <v>46.9915885925293</v>
+        <v>46.99160385131836</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0008868163883732905</v>
+        <v>-0.000886491963135283</v>
       </c>
     </row>
     <row r="107">
@@ -7224,10 +7224,10 @@
         <v>41548</v>
       </c>
       <c r="B107" t="n">
-        <v>46.7747802734375</v>
+        <v>46.77478408813477</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.00461376866766039</v>
+        <v>-0.004614010704329541</v>
       </c>
     </row>
     <row r="108">
@@ -7235,10 +7235,10 @@
         <v>41579</v>
       </c>
       <c r="B108" t="n">
-        <v>53.12094497680664</v>
+        <v>53.12093734741211</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1356749228167515</v>
+        <v>0.1356746670881406</v>
       </c>
     </row>
     <row r="109">
@@ -7246,10 +7246,10 @@
         <v>41609</v>
       </c>
       <c r="B109" t="n">
-        <v>60.21764755249023</v>
+        <v>60.21761322021484</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1335951869602869</v>
+        <v>0.1335947034667389</v>
       </c>
     </row>
     <row r="110">
@@ -7260,7 +7260,7 @@
         <v>67.10584259033203</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1143883116961275</v>
+        <v>0.114388947049878</v>
       </c>
     </row>
     <row r="111">
@@ -7279,10 +7279,10 @@
         <v>41699</v>
       </c>
       <c r="B112" t="n">
-        <v>67.13921356201172</v>
+        <v>67.13922119140625</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.09671247050225462</v>
+        <v>-0.09671236785677262</v>
       </c>
     </row>
     <row r="113">
@@ -7290,10 +7290,10 @@
         <v>41730</v>
       </c>
       <c r="B113" t="n">
-        <v>67.68124389648438</v>
+        <v>67.68128204345703</v>
       </c>
       <c r="C113" t="n">
-        <v>0.008073230318255353</v>
+        <v>0.008073683942585896</v>
       </c>
     </row>
     <row r="114">
@@ -7301,10 +7301,10 @@
         <v>41760</v>
       </c>
       <c r="B114" t="n">
-        <v>65.27956390380859</v>
+        <v>65.27954864501953</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.03548516330977969</v>
+        <v>-0.03548593238667352</v>
       </c>
     </row>
     <row r="115">
@@ -7312,10 +7312,10 @@
         <v>41791</v>
       </c>
       <c r="B115" t="n">
-        <v>75.50260162353516</v>
+        <v>75.50257873535156</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1566039524220859</v>
+        <v>0.1566038721548666</v>
       </c>
     </row>
     <row r="116">
@@ -7323,10 +7323,10 @@
         <v>41821</v>
       </c>
       <c r="B116" t="n">
-        <v>64.1895751953125</v>
+        <v>64.18956756591797</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.1498362464995675</v>
+        <v>-0.1498360898253221</v>
       </c>
     </row>
     <row r="117">
@@ -7334,10 +7334,10 @@
         <v>41852</v>
       </c>
       <c r="B117" t="n">
-        <v>61.26760101318359</v>
+        <v>61.26760482788086</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0455210082515437</v>
+        <v>-0.04552083537619211</v>
       </c>
     </row>
     <row r="118">
@@ -7345,10 +7345,10 @@
         <v>41883</v>
       </c>
       <c r="B118" t="n">
-        <v>68.19345855712891</v>
+        <v>68.19343566894531</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1130427408518084</v>
+        <v>0.1130422979733123</v>
       </c>
     </row>
     <row r="119">
@@ -7356,10 +7356,10 @@
         <v>41913</v>
       </c>
       <c r="B119" t="n">
-        <v>65.84223937988281</v>
+        <v>65.84222412109375</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.03447866154605383</v>
+        <v>-0.03447856123961623</v>
       </c>
     </row>
     <row r="120">
@@ -7367,10 +7367,10 @@
         <v>41944</v>
       </c>
       <c r="B120" t="n">
-        <v>64.83700561523438</v>
+        <v>64.83701324462891</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.01526730825251321</v>
+        <v>-0.01526696416901274</v>
       </c>
     </row>
     <row r="121">
@@ -7378,10 +7378,10 @@
         <v>41974</v>
       </c>
       <c r="B121" t="n">
-        <v>63.15027236938477</v>
+        <v>63.1502685546875</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.02601497755555338</v>
+        <v>-0.02601515099989793</v>
       </c>
     </row>
     <row r="122">
@@ -7389,10 +7389,10 @@
         <v>42005</v>
       </c>
       <c r="B122" t="n">
-        <v>59.68308639526367</v>
+        <v>59.68310928344727</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.05490373745089316</v>
+        <v>-0.05490331792077352</v>
       </c>
     </row>
     <row r="123">
@@ -7400,10 +7400,10 @@
         <v>42036</v>
       </c>
       <c r="B123" t="n">
-        <v>69.43717956542969</v>
+        <v>69.43717193603516</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1634314469859601</v>
+        <v>0.16343087298391</v>
       </c>
     </row>
     <row r="124">
@@ -7411,10 +7411,10 @@
         <v>42064</v>
       </c>
       <c r="B124" t="n">
-        <v>59.51271820068359</v>
+        <v>59.51271057128906</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.1429271958748615</v>
+        <v>-0.1429272115789567</v>
       </c>
     </row>
     <row r="125">
@@ -7422,10 +7422,10 @@
         <v>42095</v>
       </c>
       <c r="B125" t="n">
-        <v>59.77679443359375</v>
+        <v>59.77680587768555</v>
       </c>
       <c r="C125" t="n">
-        <v>0.004437307535166912</v>
+        <v>0.004437628598350063</v>
       </c>
     </row>
     <row r="126">
@@ -7436,7 +7436,7 @@
         <v>65.05849456787109</v>
       </c>
       <c r="C126" t="n">
-        <v>0.08835703192724398</v>
+        <v>0.08835682356452534</v>
       </c>
     </row>
     <row r="127">
@@ -7444,10 +7444,10 @@
         <v>42156</v>
       </c>
       <c r="B127" t="n">
-        <v>66.45558929443359</v>
+        <v>66.45557403564453</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02147443982284281</v>
+        <v>0.0214742052833079</v>
       </c>
     </row>
     <row r="128">
@@ -7455,10 +7455,10 @@
         <v>42186</v>
       </c>
       <c r="B128" t="n">
-        <v>83.75830078125</v>
+        <v>83.75831604003906</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2603650297969098</v>
+        <v>0.2603655487967633</v>
       </c>
     </row>
     <row r="129">
@@ -7466,10 +7466,10 @@
         <v>42217</v>
       </c>
       <c r="B129" t="n">
-        <v>80.99676513671875</v>
+        <v>80.99675750732422</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.03297029212356517</v>
+        <v>-0.03297055938176618</v>
       </c>
     </row>
     <row r="130">
@@ -7477,10 +7477,10 @@
         <v>42248</v>
       </c>
       <c r="B130" t="n">
-        <v>82.09965515136719</v>
+        <v>82.09963989257812</v>
       </c>
       <c r="C130" t="n">
-        <v>0.01361646990206111</v>
+        <v>0.01361637699082174</v>
       </c>
     </row>
     <row r="131">
@@ -7488,10 +7488,10 @@
         <v>42278</v>
       </c>
       <c r="B131" t="n">
-        <v>98.26079559326172</v>
+        <v>98.26078796386719</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1968478480463558</v>
+        <v>0.1968479775603746</v>
       </c>
     </row>
     <row r="132">
@@ -7499,10 +7499,10 @@
         <v>42309</v>
       </c>
       <c r="B132" t="n">
-        <v>98.912109375</v>
+        <v>98.91209411621094</v>
       </c>
       <c r="C132" t="n">
-        <v>0.006628419582865197</v>
+        <v>0.006628342453179226</v>
       </c>
     </row>
     <row r="133">
@@ -7510,10 +7510,10 @@
         <v>42339</v>
       </c>
       <c r="B133" t="n">
-        <v>100.6576232910156</v>
+        <v>100.657600402832</v>
       </c>
       <c r="C133" t="n">
-        <v>0.01764712052998441</v>
+        <v>0.01764704611925727</v>
       </c>
     </row>
     <row r="134">
@@ -7524,7 +7524,7 @@
         <v>95.82052612304688</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.04805495112857983</v>
+        <v>-0.04805473466908783</v>
       </c>
     </row>
     <row r="135">
@@ -7543,10 +7543,10 @@
         <v>42430</v>
       </c>
       <c r="B136" t="n">
-        <v>86.26799774169922</v>
+        <v>86.26801300048828</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1838871298546301</v>
+        <v>0.1838873392565457</v>
       </c>
     </row>
     <row r="137">
@@ -7557,7 +7557,7 @@
         <v>81.56990814208984</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.05445924007273517</v>
+        <v>-0.05445940731672871</v>
       </c>
     </row>
     <row r="138">
@@ -7565,10 +7565,10 @@
         <v>42491</v>
       </c>
       <c r="B138" t="n">
-        <v>84.34016418457031</v>
+        <v>84.34015655517578</v>
       </c>
       <c r="C138" t="n">
-        <v>0.03396174037188882</v>
+        <v>0.03396164683991465</v>
       </c>
     </row>
     <row r="139">
@@ -7576,10 +7576,10 @@
         <v>42522</v>
       </c>
       <c r="B139" t="n">
-        <v>89.05561828613281</v>
+        <v>89.05565643310547</v>
       </c>
       <c r="C139" t="n">
-        <v>0.05590994690552398</v>
+        <v>0.05591049472198661</v>
       </c>
     </row>
     <row r="140">
@@ -7587,10 +7587,10 @@
         <v>42552</v>
       </c>
       <c r="B140" t="n">
-        <v>79.88083648681641</v>
+        <v>79.880859375</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1030230543101518</v>
+        <v>-0.1030231815201672</v>
       </c>
     </row>
     <row r="141">
@@ -7598,10 +7598,10 @@
         <v>42583</v>
       </c>
       <c r="B141" t="n">
-        <v>70.99730682373047</v>
+        <v>70.99729156494141</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1112097726286589</v>
+        <v>-0.1112102183121837</v>
       </c>
     </row>
     <row r="142">
@@ -7609,10 +7609,10 @@
         <v>42614</v>
       </c>
       <c r="B142" t="n">
-        <v>74.36080169677734</v>
+        <v>74.36078643798828</v>
       </c>
       <c r="C142" t="n">
-        <v>0.04737496425600529</v>
+        <v>0.04737497443786687</v>
       </c>
     </row>
     <row r="143">
@@ -7623,7 +7623,7 @@
         <v>72.21311950683594</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.02888191279458041</v>
+        <v>-0.02888171352172764</v>
       </c>
     </row>
     <row r="144">
@@ -7631,10 +7631,10 @@
         <v>42675</v>
       </c>
       <c r="B144" t="n">
-        <v>75.47014617919922</v>
+        <v>75.47013092041016</v>
       </c>
       <c r="C144" t="n">
-        <v>0.04510297705744404</v>
+        <v>0.04510276575527117</v>
       </c>
     </row>
     <row r="145">
@@ -7642,10 +7642,10 @@
         <v>42705</v>
       </c>
       <c r="B145" t="n">
-        <v>75.38140106201172</v>
+        <v>75.38137817382812</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.001175896982851699</v>
+        <v>-0.001175998312175075</v>
       </c>
     </row>
     <row r="146">
@@ -7656,7 +7656,7 @@
         <v>72.79000091552734</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.03437718203662188</v>
+        <v>-0.03437688884282686</v>
       </c>
     </row>
     <row r="147">
@@ -7675,10 +7675,10 @@
         <v>42795</v>
       </c>
       <c r="B148" t="n">
-        <v>77.31607818603516</v>
+        <v>77.31606292724609</v>
       </c>
       <c r="C148" t="n">
-        <v>0.04661259739079426</v>
+        <v>0.04661239083555735</v>
       </c>
     </row>
     <row r="149">
@@ -7686,10 +7686,10 @@
         <v>42826</v>
       </c>
       <c r="B149" t="n">
-        <v>81.44277954101562</v>
+        <v>81.44277191162109</v>
       </c>
       <c r="C149" t="n">
-        <v>0.05337442679194027</v>
+        <v>0.05337453600370479</v>
       </c>
     </row>
     <row r="150">
@@ -7697,10 +7697,10 @@
         <v>42856</v>
       </c>
       <c r="B150" t="n">
-        <v>92.74910736083984</v>
+        <v>92.74911499023438</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1388254168576135</v>
+        <v>0.1388256172184628</v>
       </c>
     </row>
     <row r="151">
@@ -7708,10 +7708,10 @@
         <v>42887</v>
       </c>
       <c r="B151" t="n">
-        <v>102.4934844970703</v>
+        <v>102.4934616088867</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1050616810609295</v>
+        <v>0.1050613433850913</v>
       </c>
     </row>
     <row r="152">
@@ -7722,7 +7722,7 @@
         <v>91.49778747558594</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.1072819123619383</v>
+        <v>-0.1072817130058509</v>
       </c>
     </row>
     <row r="153">
@@ -7730,10 +7730,10 @@
         <v>42948</v>
       </c>
       <c r="B153" t="n">
-        <v>88.48928070068359</v>
+        <v>88.48925018310547</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.03288065053709732</v>
+        <v>-0.03288098407060636</v>
       </c>
     </row>
     <row r="154">
@@ -7741,10 +7741,10 @@
         <v>42979</v>
       </c>
       <c r="B154" t="n">
-        <v>98.76463317871094</v>
+        <v>98.76464080810547</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1161197423762985</v>
+        <v>0.1161202135144976</v>
       </c>
     </row>
     <row r="155">
@@ -7752,10 +7752,10 @@
         <v>43009</v>
       </c>
       <c r="B155" t="n">
-        <v>123.2305297851562</v>
+        <v>123.2305145263672</v>
       </c>
       <c r="C155" t="n">
-        <v>0.2477192069571623</v>
+        <v>0.2477189560765742</v>
       </c>
     </row>
     <row r="156">
@@ -7763,10 +7763,10 @@
         <v>43040</v>
       </c>
       <c r="B156" t="n">
-        <v>116.3221740722656</v>
+        <v>116.3221664428711</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.05606042370291564</v>
+        <v>-0.05606036873292397</v>
       </c>
     </row>
     <row r="157">
@@ -7774,10 +7774,10 @@
         <v>43070</v>
       </c>
       <c r="B157" t="n">
-        <v>117.4234924316406</v>
+        <v>117.4235153198242</v>
       </c>
       <c r="C157" t="n">
-        <v>0.009467828194913208</v>
+        <v>0.009468091169829052</v>
       </c>
     </row>
     <row r="158">
@@ -7788,7 +7788,7 @@
         <v>155.8516845703125</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3272615329597974</v>
+        <v>0.32726127425007</v>
       </c>
     </row>
     <row r="159">
@@ -7796,10 +7796,10 @@
         <v>43132</v>
       </c>
       <c r="B159" t="n">
-        <v>151.9105987548828</v>
+        <v>151.9105529785156</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.0252874123644885</v>
+        <v>-0.02528770608198871</v>
       </c>
     </row>
     <row r="160">
@@ -7807,10 +7807,10 @@
         <v>43160</v>
       </c>
       <c r="B160" t="n">
-        <v>157.4627532958984</v>
+        <v>157.4627685546875</v>
       </c>
       <c r="C160" t="n">
-        <v>0.03654882928856318</v>
+        <v>0.03654924208561816</v>
       </c>
     </row>
     <row r="161">
@@ -7818,10 +7818,10 @@
         <v>43191</v>
       </c>
       <c r="B161" t="n">
-        <v>211.5461578369141</v>
+        <v>211.5461730957031</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3434679212002854</v>
+        <v>0.3434678879168329</v>
       </c>
     </row>
     <row r="162">
@@ -7832,7 +7832,7 @@
         <v>203.3544616699219</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.03872297304169126</v>
+        <v>-0.03872304237843782</v>
       </c>
     </row>
     <row r="163">
@@ -7862,10 +7862,10 @@
         <v>43313</v>
       </c>
       <c r="B165" t="n">
-        <v>256.0725708007812</v>
+        <v>256.0726623535156</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1465481137673863</v>
+        <v>0.1465485236887401</v>
       </c>
     </row>
     <row r="166">
@@ -7873,10 +7873,10 @@
         <v>43344</v>
       </c>
       <c r="B166" t="n">
-        <v>202.0098114013672</v>
+        <v>202.0097808837891</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.2111228048765663</v>
+        <v>-0.2111232060964446</v>
       </c>
     </row>
     <row r="167">
@@ -7887,7 +7887,7 @@
         <v>226.0296478271484</v>
       </c>
       <c r="C167" t="n">
-        <v>0.1189043059797574</v>
+        <v>0.1189044750124122</v>
       </c>
     </row>
     <row r="168">
@@ -7895,10 +7895,10 @@
         <v>43405</v>
       </c>
       <c r="B168" t="n">
-        <v>200.6656494140625</v>
+        <v>200.6656341552734</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.1122153604932505</v>
+        <v>-0.1122154280011604</v>
       </c>
     </row>
     <row r="169">
@@ -7909,7 +7909,7 @@
         <v>211.6214447021484</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0545972632589411</v>
+        <v>0.05459734345143263</v>
       </c>
     </row>
     <row r="170">
@@ -7917,10 +7917,10 @@
         <v>43466</v>
       </c>
       <c r="B170" t="n">
-        <v>241.3493041992188</v>
+        <v>241.3493194580078</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1404765927144647</v>
+        <v>0.1404766648186366</v>
       </c>
     </row>
     <row r="171">
@@ -7928,10 +7928,10 @@
         <v>43497</v>
       </c>
       <c r="B171" t="n">
-        <v>243.1814270019531</v>
+        <v>243.1814575195312</v>
       </c>
       <c r="C171" t="n">
-        <v>0.007591166706749863</v>
+        <v>0.007591229449653403</v>
       </c>
     </row>
     <row r="172">
@@ -7939,10 +7939,10 @@
         <v>43525</v>
       </c>
       <c r="B172" t="n">
-        <v>244.1297607421875</v>
+        <v>244.1297454833984</v>
       </c>
       <c r="C172" t="n">
-        <v>0.003899696419771281</v>
+        <v>0.003899507690840354</v>
       </c>
     </row>
     <row r="173">
@@ -7950,10 +7950,10 @@
         <v>43556</v>
       </c>
       <c r="B173" t="n">
-        <v>238.1731262207031</v>
+        <v>238.1731109619141</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.02439946077600452</v>
+        <v>-0.02439946230103884</v>
       </c>
     </row>
     <row r="174">
@@ -7961,10 +7961,10 @@
         <v>43586</v>
       </c>
       <c r="B174" t="n">
-        <v>240.6036071777344</v>
+        <v>240.6035766601562</v>
       </c>
       <c r="C174" t="n">
-        <v>0.01020468176069134</v>
+        <v>0.01020461834850384</v>
       </c>
     </row>
     <row r="175">
@@ -7972,10 +7972,10 @@
         <v>43617</v>
       </c>
       <c r="B175" t="n">
-        <v>247.6742553710938</v>
+        <v>247.6741638183594</v>
       </c>
       <c r="C175" t="n">
-        <v>0.02938712464163618</v>
+        <v>0.02938687469384571</v>
       </c>
     </row>
     <row r="176">
@@ -7983,10 +7983,10 @@
         <v>43647</v>
       </c>
       <c r="B176" t="n">
-        <v>221.6105041503906</v>
+        <v>221.6105804443359</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.1052339944725036</v>
+        <v>-0.1052333556807244</v>
       </c>
     </row>
     <row r="177">
@@ -7994,10 +7994,10 @@
         <v>43678</v>
       </c>
       <c r="B177" t="n">
-        <v>275.376708984375</v>
+        <v>275.3766479492188</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2426157778040035</v>
+        <v>0.2426150745920173</v>
       </c>
     </row>
     <row r="178">
@@ -8008,7 +8008,7 @@
         <v>256.843994140625</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.06729950006338969</v>
+        <v>-0.06729929333736129</v>
       </c>
     </row>
     <row r="179">
@@ -8016,10 +8016,10 @@
         <v>43739</v>
       </c>
       <c r="B179" t="n">
-        <v>285.1632995605469</v>
+        <v>285.1632080078125</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1102587799051931</v>
+        <v>0.1102584234524964</v>
       </c>
     </row>
     <row r="180">
@@ -8030,7 +8030,7 @@
         <v>276.3023071289062</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.03107339705107892</v>
+        <v>-0.03107308597350156</v>
       </c>
     </row>
     <row r="181">
@@ -8049,10 +8049,10 @@
         <v>43831</v>
       </c>
       <c r="B182" t="n">
-        <v>359.9740905761719</v>
+        <v>359.9740600585938</v>
       </c>
       <c r="C182" t="n">
-        <v>0.2217820221311462</v>
+        <v>0.2217819185519463</v>
       </c>
     </row>
     <row r="183">
@@ -8063,7 +8063,7 @@
         <v>314.8010559082031</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.1254896834260075</v>
+        <v>-0.1254896092875073</v>
       </c>
     </row>
     <row r="184">
@@ -8082,10 +8082,10 @@
         <v>43922</v>
       </c>
       <c r="B185" t="n">
-        <v>224.2032165527344</v>
+        <v>224.2031860351562</v>
       </c>
       <c r="C185" t="n">
-        <v>0.04852990908576471</v>
+        <v>0.04852976636438044</v>
       </c>
     </row>
     <row r="186">
@@ -8093,10 +8093,10 @@
         <v>43952</v>
       </c>
       <c r="B186" t="n">
-        <v>272.5648803710938</v>
+        <v>272.5647583007812</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2157045940818798</v>
+        <v>0.2157042150955055</v>
       </c>
     </row>
     <row r="187">
@@ -8104,10 +8104,10 @@
         <v>43983</v>
       </c>
       <c r="B187" t="n">
-        <v>264.5851745605469</v>
+        <v>264.5852661132812</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.02927635357747704</v>
+        <v>-0.0292755829375948</v>
       </c>
     </row>
     <row r="188">
@@ -8118,7 +8118,7 @@
         <v>361.6548461914062</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3668749460058891</v>
+        <v>0.3668744730349611</v>
       </c>
     </row>
     <row r="189">
@@ -8126,10 +8126,10 @@
         <v>44044</v>
       </c>
       <c r="B189" t="n">
-        <v>361.2418212890625</v>
+        <v>361.2418518066406</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.001142041664015658</v>
+        <v>-0.001141957280857309</v>
       </c>
     </row>
     <row r="190">
@@ -8137,10 +8137,10 @@
         <v>44075</v>
       </c>
       <c r="B190" t="n">
-        <v>436.0060119628906</v>
+        <v>436.0059814453125</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2069643830468966</v>
+        <v>0.2069641966033613</v>
       </c>
     </row>
     <row r="191">
@@ -8151,7 +8151,7 @@
         <v>414.1231384277344</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.05018938485880042</v>
+        <v>-0.05018931837824536</v>
       </c>
     </row>
     <row r="192">
@@ -8159,10 +8159,10 @@
         <v>44136</v>
       </c>
       <c r="B192" t="n">
-        <v>450.7355041503906</v>
+        <v>450.7354736328125</v>
       </c>
       <c r="C192" t="n">
-        <v>0.08840936988370007</v>
+        <v>0.08840929619166182</v>
       </c>
     </row>
     <row r="193">
@@ -8170,10 +8170,10 @@
         <v>44166</v>
       </c>
       <c r="B193" t="n">
-        <v>507.9071044921875</v>
+        <v>507.906982421875</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1268406855358819</v>
+        <v>0.1268404910052336</v>
       </c>
     </row>
     <row r="194">
@@ -8181,10 +8181,10 @@
         <v>44197</v>
       </c>
       <c r="B194" t="n">
-        <v>449.2616271972656</v>
+        <v>449.2615051269531</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.115464967463994</v>
+        <v>-0.1154649952148327</v>
       </c>
     </row>
     <row r="195">
@@ -8192,10 +8192,10 @@
         <v>44228</v>
       </c>
       <c r="B195" t="n">
-        <v>477.2841491699219</v>
+        <v>477.2841796875</v>
       </c>
       <c r="C195" t="n">
-        <v>0.06237461709666969</v>
+        <v>0.06237497368626799</v>
       </c>
     </row>
     <row r="196">
@@ -8206,7 +8206,7 @@
         <v>549.55126953125</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1514132000549628</v>
+        <v>0.1514131264335361</v>
       </c>
     </row>
     <row r="197">
@@ -8214,10 +8214,10 @@
         <v>44287</v>
       </c>
       <c r="B197" t="n">
-        <v>538.68017578125</v>
+        <v>538.6802368164062</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01978176441894619</v>
+        <v>-0.019781653355321</v>
       </c>
     </row>
     <row r="198">
@@ -8225,10 +8225,10 @@
         <v>44317</v>
       </c>
       <c r="B198" t="n">
-        <v>665.2327270507812</v>
+        <v>665.2327880859375</v>
       </c>
       <c r="C198" t="n">
-        <v>0.23493077517841</v>
+        <v>0.234930748559582</v>
       </c>
     </row>
     <row r="199">
@@ -8236,10 +8236,10 @@
         <v>44348</v>
       </c>
       <c r="B199" t="n">
-        <v>783.5814208984375</v>
+        <v>783.5813598632812</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1779056998177753</v>
+        <v>0.1779054999947702</v>
       </c>
     </row>
     <row r="200">
@@ -8247,10 +8247,10 @@
         <v>44378</v>
       </c>
       <c r="B200" t="n">
-        <v>958.2300415039062</v>
+        <v>958.2301635742188</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2228850964909561</v>
+        <v>0.2228853475297192</v>
       </c>
     </row>
     <row r="201">
@@ -8261,7 +8261,7 @@
         <v>984.4340209960938</v>
       </c>
       <c r="C201" t="n">
-        <v>0.02734623040106454</v>
+        <v>0.02734609952595735</v>
       </c>
     </row>
     <row r="202">
@@ -8269,10 +8269,10 @@
         <v>44440</v>
       </c>
       <c r="B202" t="n">
-        <v>990.5855712890625</v>
+        <v>990.585693359375</v>
       </c>
       <c r="C202" t="n">
-        <v>0.006248819282722806</v>
+        <v>0.006248943283224451</v>
       </c>
     </row>
     <row r="203">
@@ -8280,10 +8280,10 @@
         <v>44470</v>
       </c>
       <c r="B203" t="n">
-        <v>920.4965209960938</v>
+        <v>920.49658203125</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.07075516979493346</v>
+        <v>-0.07075522269096346</v>
       </c>
     </row>
     <row r="204">
@@ -8294,7 +8294,7 @@
         <v>1029.20458984375</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1180972077222198</v>
+        <v>0.118097133584804</v>
       </c>
     </row>
     <row r="205">
@@ -8302,10 +8302,10 @@
         <v>44531</v>
       </c>
       <c r="B205" t="n">
-        <v>1116.130615234375</v>
+        <v>1116.13037109375</v>
       </c>
       <c r="C205" t="n">
-        <v>0.08445942259528971</v>
+        <v>0.08445918538237063</v>
       </c>
     </row>
     <row r="206">
@@ -8316,7 +8316,7 @@
         <v>912.084228515625</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.1828158675460242</v>
+        <v>-0.1828156887964354</v>
       </c>
     </row>
     <row r="207">
@@ -8324,10 +8324,10 @@
         <v>44593</v>
       </c>
       <c r="B207" t="n">
-        <v>861.7936401367188</v>
+        <v>861.7935180664062</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.05513809668735514</v>
+        <v>-0.05513823052402145</v>
       </c>
     </row>
     <row r="208">
@@ -8335,10 +8335,10 @@
         <v>44621</v>
       </c>
       <c r="B208" t="n">
-        <v>846.972900390625</v>
+        <v>846.9728393554688</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.01719755061518269</v>
+        <v>-0.01719748222775042</v>
       </c>
     </row>
     <row r="209">
@@ -8346,10 +8346,10 @@
         <v>44652</v>
       </c>
       <c r="B209" t="n">
-        <v>798.0829467773438</v>
+        <v>798.0831298828125</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.05772316161559965</v>
+        <v>-0.05772287752445571</v>
       </c>
     </row>
     <row r="210">
@@ -8357,10 +8357,10 @@
         <v>44682</v>
       </c>
       <c r="B210" t="n">
-        <v>745.7869873046875</v>
+        <v>745.7871704101562</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.06552697270857266</v>
+        <v>-0.06552695767461614</v>
       </c>
     </row>
     <row r="211">
@@ -8371,7 +8371,7 @@
         <v>674.8214721679688</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.09515520697564295</v>
+        <v>-0.0951554291328971</v>
       </c>
     </row>
     <row r="212">
@@ -8379,10 +8379,10 @@
         <v>44743</v>
       </c>
       <c r="B212" t="n">
-        <v>753.9474487304688</v>
+        <v>753.9476928710938</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1172546811652206</v>
+        <v>0.1172550429507226</v>
       </c>
     </row>
     <row r="213">
@@ -8390,10 +8390,10 @@
         <v>44774</v>
       </c>
       <c r="B213" t="n">
-        <v>681.1530151367188</v>
+        <v>681.1531372070312</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.09655107092188531</v>
+        <v>-0.09655120156526364</v>
       </c>
     </row>
     <row r="214">
@@ -8401,10 +8401,10 @@
         <v>44805</v>
       </c>
       <c r="B214" t="n">
-        <v>643.1959838867188</v>
+        <v>643.1961059570312</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.05572467625703958</v>
+        <v>-0.05572466627055006</v>
       </c>
     </row>
     <row r="215">
@@ -8415,7 +8415,7 @@
         <v>728.8387451171875</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1331518905216802</v>
+        <v>0.1331516754640887</v>
       </c>
     </row>
     <row r="216">
@@ -8423,10 +8423,10 @@
         <v>44866</v>
       </c>
       <c r="B216" t="n">
-        <v>774.8348388671875</v>
+        <v>774.8346557617188</v>
       </c>
       <c r="C216" t="n">
-        <v>0.06310873846670217</v>
+        <v>0.06310848723764773</v>
       </c>
     </row>
     <row r="217">
@@ -8437,7 +8437,7 @@
         <v>745.6176147460938</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.03770767995384605</v>
+        <v>-0.03770745254921837</v>
       </c>
     </row>
     <row r="218">
@@ -8445,10 +8445,10 @@
         <v>44927</v>
       </c>
       <c r="B218" t="n">
-        <v>840.6025390625</v>
+        <v>840.6026611328125</v>
       </c>
       <c r="C218" t="n">
-        <v>0.1273909339558075</v>
+        <v>0.1273910976728523</v>
       </c>
     </row>
     <row r="219">
@@ -8459,7 +8459,7 @@
         <v>828.7486572265625</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.01410164885911214</v>
+        <v>-0.01410179202891804</v>
       </c>
     </row>
     <row r="220">
@@ -8467,10 +8467,10 @@
         <v>44986</v>
       </c>
       <c r="B220" t="n">
-        <v>735.3308715820312</v>
+        <v>735.3309326171875</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1127214926141266</v>
+        <v>-0.1127214189667598</v>
       </c>
     </row>
     <row r="221">
@@ -8481,7 +8481,7 @@
         <v>806.7413940429688</v>
       </c>
       <c r="C221" t="n">
-        <v>0.09711345629662049</v>
+        <v>0.09711336523219183</v>
       </c>
     </row>
     <row r="222">
@@ -8489,10 +8489,10 @@
         <v>45047</v>
       </c>
       <c r="B222" t="n">
-        <v>882.2539672851562</v>
+        <v>882.2540893554688</v>
       </c>
       <c r="C222" t="n">
-        <v>0.09360195695891793</v>
+        <v>0.09360210827173443</v>
       </c>
     </row>
     <row r="223">
@@ -8500,10 +8500,10 @@
         <v>45078</v>
       </c>
       <c r="B223" t="n">
-        <v>912.507568359375</v>
+        <v>912.5075073242188</v>
       </c>
       <c r="C223" t="n">
-        <v>0.0342912610155941</v>
+        <v>0.03429104872820887</v>
       </c>
     </row>
     <row r="224">
@@ -8514,7 +8514,7 @@
         <v>911.0355834960938</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.001613120717374183</v>
+        <v>-0.001613053937979281</v>
       </c>
     </row>
     <row r="225">
@@ -8522,10 +8522,10 @@
         <v>45139</v>
       </c>
       <c r="B225" t="n">
-        <v>1063.014526367188</v>
+        <v>1063.014404296875</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1668199855464212</v>
+        <v>0.1668198515557027</v>
       </c>
     </row>
     <row r="226">
@@ -8533,10 +8533,10 @@
         <v>45170</v>
       </c>
       <c r="B226" t="n">
-        <v>992.6193237304688</v>
+        <v>992.619384765625</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.06622223957493012</v>
+        <v>-0.06622207492833776</v>
       </c>
     </row>
     <row r="227">
@@ -8547,7 +8547,7 @@
         <v>969.2450561523438</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.02354806824662614</v>
+        <v>-0.02354812828766217</v>
       </c>
     </row>
     <row r="228">
@@ -8588,10 +8588,10 @@
         <v>45323</v>
       </c>
       <c r="B231" t="n">
-        <v>1283.140991210938</v>
+        <v>1283.14111328125</v>
       </c>
       <c r="C231" t="n">
-        <v>0.05174112507930717</v>
+        <v>0.05174122513562884</v>
       </c>
     </row>
     <row r="232">
@@ -8599,10 +8599,10 @@
         <v>45352</v>
       </c>
       <c r="B232" t="n">
-        <v>1077.260498046875</v>
+        <v>1077.260375976562</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.1604504061317277</v>
+        <v>-0.1604505811353897</v>
       </c>
     </row>
     <row r="233">
@@ -8613,7 +8613,7 @@
         <v>999.1058349609375</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.07254945598361362</v>
+        <v>-0.07254935088907921</v>
       </c>
     </row>
     <row r="234">
@@ -8621,10 +8621,10 @@
         <v>45413</v>
       </c>
       <c r="B234" t="n">
-        <v>977.2866821289062</v>
+        <v>977.2867431640625</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.02183868021638002</v>
+        <v>-0.02183861912659946</v>
       </c>
     </row>
     <row r="235">
@@ -8635,7 +8635,7 @@
         <v>1073.18701171875</v>
       </c>
       <c r="C235" t="n">
-        <v>0.09812916858841869</v>
+        <v>0.09812910000620789</v>
       </c>
     </row>
     <row r="236">
@@ -8643,10 +8643,10 @@
         <v>45474</v>
       </c>
       <c r="B236" t="n">
-        <v>1239.646118164062</v>
+        <v>1239.64599609375</v>
       </c>
       <c r="C236" t="n">
-        <v>0.155107268936028</v>
+        <v>0.1551071551904171</v>
       </c>
     </row>
     <row r="237">
@@ -8657,7 +8657,7 @@
         <v>1251.006103515625</v>
       </c>
       <c r="C237" t="n">
-        <v>0.009163893779933652</v>
+        <v>0.009163993154232664</v>
       </c>
     </row>
     <row r="238">
@@ -8665,10 +8665,10 @@
         <v>45536</v>
       </c>
       <c r="B238" t="n">
-        <v>1383.59912109375</v>
+        <v>1383.598999023438</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1059891052533692</v>
+        <v>0.105989007675658</v>
       </c>
     </row>
     <row r="239">
@@ -8676,10 +8676,10 @@
         <v>45566</v>
       </c>
       <c r="B239" t="n">
-        <v>1507.357177734375</v>
+        <v>1507.35693359375</v>
       </c>
       <c r="C239" t="n">
-        <v>0.08944646954010271</v>
+        <v>0.08944638920500991</v>
       </c>
     </row>
     <row r="240">
@@ -8687,10 +8687,10 @@
         <v>45597</v>
       </c>
       <c r="B240" t="n">
-        <v>1717.275146484375</v>
+        <v>1717.275268554688</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1392622610292777</v>
+        <v>0.1392625265340857</v>
       </c>
     </row>
     <row r="241">
@@ -8698,10 +8698,10 @@
         <v>45627</v>
       </c>
       <c r="B241" t="n">
-        <v>1910.45703125</v>
+        <v>1910.457153320312</v>
       </c>
       <c r="C241" t="n">
-        <v>0.1124932630400604</v>
+        <v>0.1124932550436208</v>
       </c>
     </row>
     <row r="242">
@@ -8709,10 +8709,10 @@
         <v>45658</v>
       </c>
       <c r="B242" t="n">
-        <v>1637.398559570312</v>
+        <v>1637.398681640625</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.1429283502393284</v>
+        <v>-0.1429283411067978</v>
       </c>
     </row>
     <row r="243">
@@ -8720,10 +8720,10 @@
         <v>45689</v>
       </c>
       <c r="B243" t="n">
-        <v>1458.73583984375</v>
+        <v>1458.735961914062</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1091137638312368</v>
+        <v>-0.1091137556966565</v>
       </c>
     </row>
     <row r="244">
@@ -8731,10 +8731,10 @@
         <v>45717</v>
       </c>
       <c r="B244" t="n">
-        <v>1606.75634765625</v>
+        <v>1606.756225585938</v>
       </c>
       <c r="C244" t="n">
-        <v>0.101471770124161</v>
+        <v>0.1014715942682678</v>
       </c>
     </row>
     <row r="245">
@@ -8745,7 +8745,7 @@
         <v>1447.412231445312</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.0991713002680028</v>
+        <v>-0.09917123182921972</v>
       </c>
     </row>
     <row r="246">
@@ -8764,10 +8764,10 @@
         <v>45809</v>
       </c>
       <c r="B247" t="n">
-        <v>1911.284545898438</v>
+        <v>1911.284423828125</v>
       </c>
       <c r="C247" t="n">
-        <v>0.1253728723580885</v>
+        <v>0.1253728004825436</v>
       </c>
     </row>
     <row r="248">
@@ -8778,7 +8778,7 @@
         <v>1740.173706054688</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.08952661717008548</v>
+        <v>-0.08952655901978135</v>
       </c>
     </row>
     <row r="249">
